--- a/outputs/validation_frame_temperature.xlsx
+++ b/outputs/validation_frame_temperature.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>119.8844950930915</v>
+        <v>119.8844950930664</v>
       </c>
       <c r="F6" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="G6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-13.24983693095458</v>
+        <v>-13.2498369309509</v>
       </c>
       <c r="I6" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="J6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>247.2743098816821</v>
+        <v>247.2743098816599</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>119.8844950930244</v>
+        <v>119.8844950930735</v>
       </c>
       <c r="F7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="G7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="I7" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="J7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="K7" t="n">
-        <v>247.2743098815926</v>
+        <v>247.2743098816265</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="F8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="G8" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="H8" t="n">
-        <v>13.24983693092235</v>
+        <v>13.24983693093862</v>
       </c>
       <c r="I8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="J8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="K8" t="n">
-        <v>247.2743098816123</v>
+        <v>247.2743098816334</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-119.8844950930671</v>
+        <v>-119.8844950930922</v>
       </c>
       <c r="F9" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="G9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="J9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="K9" t="n">
-        <v>247.2743098817037</v>
+        <v>247.2743098816708</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>120.039098701767</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="F10" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="G10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="H10" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071110052</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="J10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="K10" t="n">
-        <v>398.0185553894356</v>
+        <v>398.018555389402</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>120.0390987015889</v>
+        <v>120.0390987017214</v>
       </c>
       <c r="F11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="G11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="J11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="K11" t="n">
-        <v>398.0185553892941</v>
+        <v>398.0185553893489</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="F12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="G12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="I12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="J12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="K12" t="n">
-        <v>398.0185553893306</v>
+        <v>398.0185553893626</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="F13" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="G13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="H13" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="I13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="J13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="K13" t="n">
-        <v>398.0185553894707</v>
+        <v>398.018555389417</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>119.9916951661322</v>
+        <v>119.9916951660409</v>
       </c>
       <c r="F14" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="G14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-0.6603494433671542</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="J14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="K14" t="n">
-        <v>566.0353467918085</v>
+        <v>566.0353467917755</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="F15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="G15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="J15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="K15" t="n">
-        <v>566.0353467916591</v>
+        <v>566.0353467917176</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="F16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="G16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="H16" t="n">
-        <v>0.660349443347221</v>
+        <v>0.6603494433643113</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="J16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="K16" t="n">
-        <v>566.0353467917012</v>
+        <v>566.0353467917382</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-119.9916951660405</v>
+        <v>-119.9916951661319</v>
       </c>
       <c r="F17" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="G17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="J17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="K17" t="n">
-        <v>566.0353467918502</v>
+        <v>566.0353467917868</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>120.001307539296</v>
+        <v>120.0013075391888</v>
       </c>
       <c r="F18" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="G18" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2383793660995245</v>
+        <v>0.2383793661006169</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="J18" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="K18" t="n">
-        <v>739.7301045802632</v>
+        <v>739.730104580234</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075392201</v>
       </c>
       <c r="F19" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="G19" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-0.2383793661002568</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="J19" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="K19" t="n">
-        <v>739.7301045801347</v>
+        <v>739.7301045801898</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="F20" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="G20" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="J20" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="K20" t="n">
-        <v>739.7301045801756</v>
+        <v>739.7301045802139</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="F21" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="G21" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="H21" t="n">
-        <v>0.238379366093001</v>
+        <v>0.2383793661030328</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="J21" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="K21" t="n">
-        <v>739.7301045803122</v>
+        <v>739.7301045802469</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1245,16 @@
         <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>739.7301045803122</v>
+        <v>739.7301045802469</v>
       </c>
       <c r="D2" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="E2" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="F2" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
     </row>
     <row r="3">
@@ -1264,19 +1264,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="D3" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="E3" t="n">
-        <v>-120.0390987014159</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="F3" t="n">
-        <v>-360.0000000000001</v>
+        <v>-360</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="D4" t="n">
-        <v>-120.0390987017087</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="E4" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="F4" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360.0000000000002</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>-720.0000000000006</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075391888</v>
       </c>
       <c r="E5" t="n">
-        <v>-120.0013075390368</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="F5" t="n">
-        <v>-720.0000000000006</v>
+        <v>-720.0000000000007</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-19766.6294607259</v>
       </c>
       <c r="C2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-19766.62946073191</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>69104.76771110963</v>
+        <v>69104.76771109938</v>
       </c>
       <c r="F2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-69104.76771107486</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>1.792584007606996e-12</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-19766.62946072676</v>
       </c>
       <c r="C3" t="n">
-        <v>19766.62946072038</v>
+        <v>19766.6294607229</v>
       </c>
       <c r="D3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>-69104.76771105242</v>
+        <v>-69104.76771106271</v>
       </c>
       <c r="F3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-69104.76771107831</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>1.782190697250626e-12</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>19766.62946073354</v>
+        <v>19766.62946072804</v>
       </c>
       <c r="C4" t="n">
-        <v>19766.62946071211</v>
+        <v>19766.62946072307</v>
       </c>
       <c r="D4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-3.352761268615723e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>-69104.76771101885</v>
+        <v>-69104.76771106376</v>
       </c>
       <c r="F4" t="n">
-        <v>69104.76771110686</v>
+        <v>69104.76771108374</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>1.790573049363477e-12</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>19766.62946072584</v>
+        <v>19766.62946072889</v>
       </c>
       <c r="C5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-19766.62946073172</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>1.117587089538574e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>69104.76771114318</v>
+        <v>69104.76771109828</v>
       </c>
       <c r="F5" t="n">
-        <v>69104.76771107491</v>
+        <v>69104.7677110872</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>1.803065637637907e-12</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I2" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-19766.62946073191</v>
       </c>
       <c r="L2" t="n">
-        <v>19766.62946072896</v>
+        <v>19766.6294607259</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>1.792584007606996e-12</v>
       </c>
       <c r="N2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-69104.76771107486</v>
       </c>
       <c r="O2" t="n">
-        <v>-69104.76771110963</v>
+        <v>-69104.76771109937</v>
       </c>
       <c r="P2" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>19766.62946073442</v>
+        <v>19766.62946073191</v>
       </c>
       <c r="R2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-19766.6294607259</v>
       </c>
       <c r="S2" t="n">
-        <v>2.421003440282873e-11</v>
+        <v>-1.792584007606996e-12</v>
       </c>
       <c r="T2" t="n">
-        <v>-49495.00905328659</v>
+        <v>-49495.00905328055</v>
       </c>
       <c r="U2" t="n">
-        <v>-49495.00905329685</v>
+        <v>-49495.00905329204</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-30.00000000000005</v>
+        <v>-29.99999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28439999.99999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-6000000000.00001</v>
+        <v>-5999999999.999996</v>
       </c>
       <c r="J3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>19766.62946072038</v>
+        <v>19766.6294607229</v>
       </c>
       <c r="L3" t="n">
-        <v>19766.62946072127</v>
+        <v>19766.62946072676</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>1.782190697250626e-12</v>
       </c>
       <c r="N3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-69104.76771107831</v>
       </c>
       <c r="O3" t="n">
-        <v>69104.76771105242</v>
+        <v>69104.76771106271</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>-19766.62946072038</v>
+        <v>-19766.6294607229</v>
       </c>
       <c r="R3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-19766.62946072676</v>
       </c>
       <c r="S3" t="n">
-        <v>2.423009033885211e-11</v>
+        <v>-1.782190697250626e-12</v>
       </c>
       <c r="T3" t="n">
-        <v>-49495.00905327238</v>
+        <v>-49495.00905328222</v>
       </c>
       <c r="U3" t="n">
-        <v>49495.00905326986</v>
+        <v>49495.0090532747</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="G4" t="n">
-        <v>-30</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H4" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I4" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-3.352761268615723e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>19766.62946071211</v>
+        <v>19766.62946072307</v>
       </c>
       <c r="L4" t="n">
-        <v>-19766.62946073354</v>
+        <v>-19766.62946072804</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>1.790573049363477e-12</v>
       </c>
       <c r="N4" t="n">
-        <v>69104.76771110686</v>
+        <v>69104.76771108374</v>
       </c>
       <c r="O4" t="n">
-        <v>69104.76771101885</v>
+        <v>69104.76771106377</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>3.352761268615723e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>-19766.62946071211</v>
+        <v>-19766.62946072307</v>
       </c>
       <c r="R4" t="n">
-        <v>19766.62946073354</v>
+        <v>19766.62946072804</v>
       </c>
       <c r="S4" t="n">
-        <v>2.422151369217067e-11</v>
+        <v>-1.790573049363477e-12</v>
       </c>
       <c r="T4" t="n">
-        <v>49495.00905329436</v>
+        <v>49495.00905328447</v>
       </c>
       <c r="U4" t="n">
-        <v>49495.00905325378</v>
+        <v>49495.00905327461</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="G5" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30</v>
       </c>
       <c r="H5" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>1.117587089538574e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-19766.62946073173</v>
       </c>
       <c r="L5" t="n">
-        <v>-19766.62946072584</v>
+        <v>-19766.62946072889</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>1.803065637637907e-12</v>
       </c>
       <c r="N5" t="n">
-        <v>69104.76771107491</v>
+        <v>69104.7677110872</v>
       </c>
       <c r="O5" t="n">
-        <v>-69104.76771114318</v>
+        <v>-69104.76771109828</v>
       </c>
       <c r="P5" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-1.117587089538574e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>19766.62946074268</v>
+        <v>19766.62946073173</v>
       </c>
       <c r="R5" t="n">
-        <v>19766.62946072584</v>
+        <v>19766.62946072889</v>
       </c>
       <c r="S5" t="n">
-        <v>2.422188588688456e-11</v>
+        <v>-1.803065637637907e-12</v>
       </c>
       <c r="T5" t="n">
-        <v>49495.00905328012</v>
+        <v>49495.00905328616</v>
       </c>
       <c r="U5" t="n">
-        <v>-49495.0090533129</v>
+        <v>-49495.00905329208</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I6" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>7608.033479463036</v>
+        <v>7608.03347946563</v>
       </c>
       <c r="L6" t="n">
-        <v>-7608.033479468945</v>
+        <v>-7608.033479471618</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.867834873910378e-11</v>
+        <v>3.393530821440233e-12</v>
       </c>
       <c r="N6" t="n">
-        <v>34787.69005993183</v>
+        <v>34787.69005993984</v>
       </c>
       <c r="O6" t="n">
-        <v>34787.69005991481</v>
+        <v>34787.690059922</v>
       </c>
       <c r="P6" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7608.033479463036</v>
+        <v>-7608.03347946563</v>
       </c>
       <c r="R6" t="n">
-        <v>7608.033479468945</v>
+        <v>7608.033479471618</v>
       </c>
       <c r="S6" t="n">
-        <v>3.867834873910378e-11</v>
+        <v>-3.393530821440233e-12</v>
       </c>
       <c r="T6" t="n">
-        <v>10860.51081688182</v>
+        <v>10860.51081688989</v>
       </c>
       <c r="U6" t="n">
-        <v>10860.51081686339</v>
+        <v>10860.51081687179</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-180.0000000000002</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-30.00000000000004</v>
+        <v>-29.99999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28439999.99999998</v>
       </c>
       <c r="I7" t="n">
-        <v>-6000000000.000008</v>
+        <v>-5999999999.999995</v>
       </c>
       <c r="J7" t="n">
-        <v>4.097819328308105e-08</v>
+        <v>-1.490116119384766e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>-7608.033479476842</v>
+        <v>-7608.033479474256</v>
       </c>
       <c r="L7" t="n">
-        <v>-7608.033479476904</v>
+        <v>-7608.033479470603</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.867545858883965e-11</v>
+        <v>3.450695314746986e-12</v>
       </c>
       <c r="N7" t="n">
-        <v>34787.69005995742</v>
+        <v>34787.69005993747</v>
       </c>
       <c r="O7" t="n">
-        <v>-34787.69005995538</v>
+        <v>-34787.69005994825</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.097819328308105e-08</v>
+        <v>1.490116119384766e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>7608.033479476842</v>
+        <v>7608.033479474256</v>
       </c>
       <c r="R7" t="n">
-        <v>7608.033479476904</v>
+        <v>7608.033479470603</v>
       </c>
       <c r="S7" t="n">
-        <v>3.867545858883965e-11</v>
+        <v>-3.450695314746986e-12</v>
       </c>
       <c r="T7" t="n">
-        <v>10860.51081690402</v>
+        <v>10860.51081688613</v>
       </c>
       <c r="U7" t="n">
-        <v>-10860.51081690566</v>
+        <v>-10860.51081689728</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-30</v>
+        <v>-29.99999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999995</v>
       </c>
       <c r="I8" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.99999</v>
       </c>
       <c r="J8" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-4.842877388000488e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>-7608.033479484184</v>
+        <v>-7608.03347947371</v>
       </c>
       <c r="L8" t="n">
-        <v>7608.03347946298</v>
+        <v>7608.033479469254</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.868580190546846e-11</v>
+        <v>3.346394768910892e-12</v>
       </c>
       <c r="N8" t="n">
-        <v>-34787.6900599128</v>
+        <v>-34787.69005993268</v>
       </c>
       <c r="O8" t="n">
-        <v>-34787.69005997882</v>
+        <v>-34787.69005994567</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>4.842877388000488e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>7608.033479484184</v>
+        <v>7608.03347947371</v>
       </c>
       <c r="R8" t="n">
-        <v>-7608.03347946298</v>
+        <v>-7608.033479469254</v>
       </c>
       <c r="S8" t="n">
-        <v>3.868580190546846e-11</v>
+        <v>-3.346394768910892e-12</v>
       </c>
       <c r="T8" t="n">
-        <v>-10860.51081686508</v>
+        <v>-10860.51081688284</v>
       </c>
       <c r="U8" t="n">
-        <v>-10860.51081692625</v>
+        <v>-10860.51081689657</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-179.9999999999998</v>
+        <v>-180</v>
       </c>
       <c r="G9" t="n">
-        <v>-29.99999999999997</v>
+        <v>-30</v>
       </c>
       <c r="H9" t="n">
-        <v>-28439999.99999997</v>
+        <v>-28440000</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999993</v>
+        <v>-5999999999.999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>7608.03347945568</v>
+        <v>7608.033479466165</v>
       </c>
       <c r="L9" t="n">
-        <v>7608.033479470957</v>
+        <v>7608.033479468249</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.869313251766919e-11</v>
+        <v>3.392131079729449e-12</v>
       </c>
       <c r="N9" t="n">
-        <v>-34787.69005993844</v>
+        <v>-34787.69005993038</v>
       </c>
       <c r="O9" t="n">
-        <v>34787.69005989138</v>
+        <v>34787.69005992453</v>
       </c>
       <c r="P9" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7608.03347945568</v>
+        <v>-7608.033479466165</v>
       </c>
       <c r="R9" t="n">
-        <v>-7608.033479470957</v>
+        <v>-7608.033479468249</v>
       </c>
       <c r="S9" t="n">
-        <v>3.869313251766919e-11</v>
+        <v>-3.392131079729449e-12</v>
       </c>
       <c r="T9" t="n">
-        <v>-10860.51081688729</v>
+        <v>-10860.51081687913</v>
       </c>
       <c r="U9" t="n">
-        <v>10860.51081684273</v>
+        <v>10860.51081687245</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180</v>
+        <v>-180.0000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30</v>
+        <v>-30.00000000000004</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000</v>
+        <v>-28440000.00000004</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000</v>
+        <v>-6000000000.000008</v>
       </c>
       <c r="J10" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>4.470348358154297e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>-1658.358832414433</v>
+        <v>-1658.358832413913</v>
       </c>
       <c r="L10" t="n">
-        <v>1658.358832411864</v>
+        <v>1658.358832409609</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.010927424673966e-11</v>
+        <v>3.927541217236775e-12</v>
       </c>
       <c r="N10" t="n">
-        <v>-7622.445377949901</v>
+        <v>-7622.445377944154</v>
       </c>
       <c r="O10" t="n">
-        <v>-7622.445377955475</v>
+        <v>-7622.445377954864</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-4.470348358154297e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1658.358832414433</v>
+        <v>1658.358832413913</v>
       </c>
       <c r="R10" t="n">
-        <v>-1658.358832411864</v>
+        <v>-1658.358832409609</v>
       </c>
       <c r="S10" t="n">
-        <v>4.010927424673966e-11</v>
+        <v>-3.927541217236775e-12</v>
       </c>
       <c r="T10" t="n">
-        <v>-2327.707616521262</v>
+        <v>-2327.707616513508</v>
       </c>
       <c r="U10" t="n">
-        <v>-2327.70761653113</v>
+        <v>-2327.707616528598</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-180.0000000000001</v>
+        <v>-179.9999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>-30.00000000000001</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H11" t="n">
-        <v>-28440000.00000001</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I11" t="n">
-        <v>-6000000000.000001</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J11" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>-3.725290298461914e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>1658.358832404872</v>
+        <v>1658.358832405404</v>
       </c>
       <c r="L11" t="n">
-        <v>1658.358832402486</v>
+        <v>1658.358832408467</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.012493149746856e-11</v>
+        <v>3.882815524963767e-12</v>
       </c>
       <c r="N11" t="n">
-        <v>-7622.445377924581</v>
+        <v>-7622.445377941214</v>
       </c>
       <c r="O11" t="n">
-        <v>7622.445377934186</v>
+        <v>7622.445377934841</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>3.725290298461914e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1658.358832404872</v>
+        <v>-1658.358832405404</v>
       </c>
       <c r="R11" t="n">
-        <v>-1658.358832402486</v>
+        <v>-1658.358832408467</v>
       </c>
       <c r="S11" t="n">
-        <v>4.012493149746856e-11</v>
+        <v>-3.882815524963767e-12</v>
       </c>
       <c r="T11" t="n">
-        <v>-2327.707616490355</v>
+        <v>-2327.707616509579</v>
       </c>
       <c r="U11" t="n">
-        <v>2327.707616495056</v>
+        <v>2327.707616497588</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-180.0000000000001</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-30.00000000000001</v>
+        <v>-29.99999999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-28440000.00000001</v>
+        <v>-28439999.99999998</v>
       </c>
       <c r="I12" t="n">
-        <v>-6000000000.000001</v>
+        <v>-5999999999.999995</v>
       </c>
       <c r="J12" t="n">
+        <v>-7.450580596923828e-09</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1658.358832407139</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1658.35883241082</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.023333503681037e-12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7622.445377948388</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7622.445377940967</v>
+      </c>
+      <c r="P12" t="n">
         <v>7.450580596923828e-09</v>
       </c>
-      <c r="K12" t="n">
-        <v>1658.358832396134</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-1658.358832416807</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-4.012638059121664e-11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7622.445377965032</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7622.445377909098</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-7.450580596923828e-09</v>
-      </c>
       <c r="Q12" t="n">
-        <v>-1658.358832396134</v>
+        <v>-1658.358832407139</v>
       </c>
       <c r="R12" t="n">
-        <v>1658.358832416807</v>
+        <v>1658.35883241082</v>
       </c>
       <c r="S12" t="n">
-        <v>4.012638059121664e-11</v>
+        <v>-4.023333503681037e-12</v>
       </c>
       <c r="T12" t="n">
-        <v>2327.707616535823</v>
+        <v>2327.707616516534</v>
       </c>
       <c r="U12" t="n">
-        <v>2327.707616467713</v>
+        <v>2327.707616501837</v>
       </c>
     </row>
     <row r="13">
@@ -2355,40 +2355,40 @@
         <v>-6000000000.000004</v>
       </c>
       <c r="J13" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>-1658.358832423168</v>
+        <v>-1658.358832412167</v>
       </c>
       <c r="L13" t="n">
-        <v>-1658.358832407449</v>
+        <v>-1658.358832409711</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.011772803527846e-11</v>
+        <v>3.889027553857218e-12</v>
       </c>
       <c r="N13" t="n">
-        <v>7622.445377939776</v>
+        <v>7622.445377945551</v>
       </c>
       <c r="O13" t="n">
-        <v>-7622.445377980606</v>
+        <v>-7622.445377948679</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="Q13" t="n">
-        <v>1658.358832423168</v>
+        <v>1658.358832412167</v>
       </c>
       <c r="R13" t="n">
-        <v>1658.358832407449</v>
+        <v>1658.358832409711</v>
       </c>
       <c r="S13" t="n">
-        <v>4.011772803527846e-11</v>
+        <v>-3.889027553857218e-12</v>
       </c>
       <c r="T13" t="n">
-        <v>2327.707616504927</v>
+        <v>2327.707616512693</v>
       </c>
       <c r="U13" t="n">
-        <v>-2327.7076165584</v>
+        <v>-2327.707616524305</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000001</v>
+        <v>-180.0000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000002</v>
+        <v>-30.00000000000004</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000002</v>
+        <v>-28440000.00000004</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000004</v>
+        <v>-6000000000.000008</v>
       </c>
       <c r="J14" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>4.470348358154297e-08</v>
       </c>
       <c r="K14" t="n">
-        <v>309.8868051251302</v>
+        <v>309.8868051258833</v>
       </c>
       <c r="L14" t="n">
-        <v>-309.8868051271218</v>
+        <v>-309.8868051280224</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.410522176876903e-11</v>
+        <v>7.834545089346882e-12</v>
       </c>
       <c r="N14" t="n">
-        <v>1594.71973438634</v>
+        <v>1594.719734387909</v>
       </c>
       <c r="O14" t="n">
-        <v>1594.719734381884</v>
+        <v>1594.719734383805</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-4.470348358154297e-08</v>
       </c>
       <c r="Q14" t="n">
-        <v>-309.8868051251302</v>
+        <v>-309.8868051258833</v>
       </c>
       <c r="R14" t="n">
-        <v>309.8868051271218</v>
+        <v>309.8868051280224</v>
       </c>
       <c r="S14" t="n">
-        <v>2.410522176876903e-11</v>
+        <v>-7.834545089346882e-12</v>
       </c>
       <c r="T14" t="n">
-        <v>264.6010963763609</v>
+        <v>264.6010963802401</v>
       </c>
       <c r="U14" t="n">
-        <v>264.6010963688896</v>
+        <v>264.6010963715089</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-180</v>
+        <v>-179.9999999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>-30</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H15" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I15" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-2.980232238769531e-08</v>
       </c>
       <c r="K15" t="n">
-        <v>-309.8868051250465</v>
+        <v>-309.8868051242753</v>
       </c>
       <c r="L15" t="n">
-        <v>-309.8868051299721</v>
+        <v>-309.8868051258978</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.409488232592988e-11</v>
+        <v>7.819979700184162e-12</v>
       </c>
       <c r="N15" t="n">
-        <v>1594.719734390186</v>
+        <v>1594.719734380909</v>
       </c>
       <c r="O15" t="n">
-        <v>-1594.719734376107</v>
+        <v>-1594.719734374157</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.980232238769531e-08</v>
       </c>
       <c r="Q15" t="n">
-        <v>309.8868051250465</v>
+        <v>309.8868051242753</v>
       </c>
       <c r="R15" t="n">
-        <v>309.8868051299721</v>
+        <v>309.8868051258978</v>
       </c>
       <c r="S15" t="n">
-        <v>2.409488232592988e-11</v>
+        <v>-7.819979700184162e-12</v>
       </c>
       <c r="T15" t="n">
-        <v>264.6010963896686</v>
+        <v>264.6010963744775</v>
       </c>
       <c r="U15" t="n">
-        <v>-264.6010963741574</v>
+        <v>-264.6010963714798</v>
       </c>
     </row>
     <row r="16">
@@ -2556,40 +2556,40 @@
         <v>-6000000000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-309.8868051309946</v>
+        <v>-309.8868051217396</v>
       </c>
       <c r="L16" t="n">
-        <v>309.8868051201698</v>
+        <v>309.8868051242207</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.411927784824087e-11</v>
+        <v>7.783451216547496e-12</v>
       </c>
       <c r="N16" t="n">
-        <v>-1594.719734367751</v>
+        <v>-1594.719734376951</v>
       </c>
       <c r="O16" t="n">
-        <v>-1594.719734389742</v>
+        <v>-1594.719734367216</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>309.8868051309946</v>
+        <v>309.8868051217396</v>
       </c>
       <c r="R16" t="n">
-        <v>-309.8868051201698</v>
+        <v>-309.8868051242207</v>
       </c>
       <c r="S16" t="n">
-        <v>2.411927784824087e-11</v>
+        <v>-7.783451216547496e-12</v>
       </c>
       <c r="T16" t="n">
-        <v>-264.6010963532681</v>
+        <v>-264.6010963683948</v>
       </c>
       <c r="U16" t="n">
-        <v>-264.601096396189</v>
+        <v>-264.6010963631998</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000002</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000004</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000008</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J17" t="n">
         <v>2.980232238769531e-08</v>
       </c>
       <c r="K17" t="n">
-        <v>309.8868051191603</v>
+        <v>309.8868051283935</v>
       </c>
       <c r="L17" t="n">
-        <v>309.886805123052</v>
+        <v>309.8868051221543</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.409387806605927e-11</v>
+        <v>7.860845011439737e-12</v>
       </c>
       <c r="N17" t="n">
-        <v>-1594.719734371638</v>
+        <v>-1594.719734370112</v>
       </c>
       <c r="O17" t="n">
-        <v>1594.719734368206</v>
+        <v>1594.719734390674</v>
       </c>
       <c r="P17" t="n">
         <v>-2.980232238769531e-08</v>
       </c>
       <c r="Q17" t="n">
-        <v>-309.8868051191603</v>
+        <v>-309.8868051283935</v>
       </c>
       <c r="R17" t="n">
-        <v>-309.886805123052</v>
+        <v>-309.8868051221543</v>
       </c>
       <c r="S17" t="n">
-        <v>2.409387806605927e-11</v>
+        <v>-7.860845011439737e-12</v>
       </c>
       <c r="T17" t="n">
-        <v>-264.6010963666739</v>
+        <v>-264.6010963628069</v>
       </c>
       <c r="U17" t="n">
-        <v>264.6010963467415</v>
+        <v>264.6010963796871</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861586</v>
+        <v>-239.7689901861587</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326983</v>
+        <v>-29.97112377326984</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.3370598</v>
+        <v>-28412625.33705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653966</v>
+        <v>-5994224754.653967</v>
       </c>
       <c r="J18" t="n">
-        <v>-27374.66294020042</v>
+        <v>-27374.66294019669</v>
       </c>
       <c r="K18" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>2.146407496184111e-10</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.45739123178646e-09</v>
+        <v>-5.453330231830478e-09</v>
       </c>
       <c r="M18" t="n">
-        <v>2.558309120104241e-11</v>
+        <v>-2.561506562415161e-12</v>
       </c>
       <c r="N18" t="n">
-        <v>14707.31899338208</v>
+        <v>14707.31899337007</v>
       </c>
       <c r="O18" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>8.512870408594608e-10</v>
       </c>
       <c r="P18" t="n">
-        <v>27374.66294020042</v>
+        <v>27374.66294019669</v>
       </c>
       <c r="Q18" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-2.146407496184111e-10</v>
       </c>
       <c r="R18" t="n">
-        <v>8.45739123178646e-09</v>
+        <v>5.453330231830478e-09</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.558309120104241e-11</v>
+        <v>2.561506562415161e-12</v>
       </c>
       <c r="T18" t="n">
-        <v>-14707.31899331443</v>
+        <v>-14707.31899332644</v>
       </c>
       <c r="U18" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>8.585629984736443e-10</v>
       </c>
     </row>
     <row r="19">
@@ -2745,7 +2745,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861587</v>
+        <v>-239.7689901861586</v>
       </c>
       <c r="G19" t="n">
         <v>-29.97112377326983</v>
@@ -2754,43 +2754,43 @@
         <v>-28412625.3370598</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653967</v>
+        <v>-5994224754.653966</v>
       </c>
       <c r="J19" t="n">
         <v>-27374.66294019669</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.276845958083868e-11</v>
+        <v>-2.128217602148652e-10</v>
       </c>
       <c r="L19" t="n">
-        <v>8.317329047713429e-09</v>
+        <v>8.74933903105557e-10</v>
       </c>
       <c r="M19" t="n">
-        <v>2.521716169212596e-11</v>
+        <v>-1.644906433284632e-12</v>
       </c>
       <c r="N19" t="n">
-        <v>14707.31899331497</v>
+        <v>14707.31899334475</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-8.512870408594608e-10</v>
       </c>
       <c r="P19" t="n">
         <v>27374.66294019669</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.276845958083868e-11</v>
+        <v>2.128217602148652e-10</v>
       </c>
       <c r="R19" t="n">
-        <v>-8.317329047713429e-09</v>
+        <v>-8.74933903105557e-10</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.521716169212596e-11</v>
+        <v>1.644906433284632e-12</v>
       </c>
       <c r="T19" t="n">
-        <v>-14707.31899338152</v>
+        <v>-14707.31899335176</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-8.585629984736443e-10</v>
       </c>
     </row>
     <row r="20">
@@ -2824,40 +2824,40 @@
         <v>-5994224754.653966</v>
       </c>
       <c r="J20" t="n">
-        <v>-27374.66294019669</v>
+        <v>-27374.66294020042</v>
       </c>
       <c r="K20" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>2.110027708113194e-10</v>
       </c>
       <c r="L20" t="n">
-        <v>1.831995177781209e-08</v>
+        <v>4.825778887607157e-09</v>
       </c>
       <c r="M20" t="n">
-        <v>2.55582222052908e-11</v>
+        <v>-2.561506562415161e-12</v>
       </c>
       <c r="N20" t="n">
-        <v>14707.31899327498</v>
+        <v>14707.31899332895</v>
       </c>
       <c r="O20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
       <c r="P20" t="n">
-        <v>27374.66294019669</v>
+        <v>27374.66294020042</v>
       </c>
       <c r="Q20" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-2.110027708113194e-10</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.831995177781209e-08</v>
+        <v>-4.825778887607157e-09</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.55582222052908e-11</v>
+        <v>2.561506562415161e-12</v>
       </c>
       <c r="T20" t="n">
-        <v>-14707.31899342155</v>
+        <v>-14707.31899336755</v>
       </c>
       <c r="U20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861587</v>
+        <v>-239.7689901861586</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326984</v>
+        <v>-29.97112377326983</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.33705981</v>
+        <v>-28412625.3370598</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653967</v>
+        <v>-5994224754.653966</v>
       </c>
       <c r="J21" t="n">
         <v>-27374.66294019669</v>
       </c>
       <c r="K21" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>2.110027708113194e-10</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.627086021471769e-09</v>
+        <v>1.886292011477053e-09</v>
       </c>
       <c r="M21" t="n">
-        <v>2.524203068787756e-11</v>
+        <v>-1.63424829224823e-12</v>
       </c>
       <c r="N21" t="n">
-        <v>-14707.31899334175</v>
+        <v>-14707.3189933558</v>
       </c>
       <c r="O21" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
       <c r="P21" t="n">
         <v>27374.66294019669</v>
       </c>
       <c r="Q21" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-2.110027708113194e-10</v>
       </c>
       <c r="R21" t="n">
-        <v>1.627086021471769e-09</v>
+        <v>-1.886292011477053e-09</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.524203068787756e-11</v>
+        <v>1.63424829224823e-12</v>
       </c>
       <c r="T21" t="n">
-        <v>14707.31899335478</v>
+        <v>14707.31899334072</v>
       </c>
       <c r="U21" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
     </row>
     <row r="22">
@@ -2955,43 +2955,43 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086895</v>
+        <v>-6001954935.086894</v>
       </c>
       <c r="J22" t="n">
-        <v>9266.392311882228</v>
+        <v>9266.392311878502</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>9.640643838793039e-11</v>
       </c>
       <c r="L22" t="n">
-        <v>-7.940798241179436e-09</v>
+        <v>-5.697074811905622e-09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.044675622732029e-11</v>
+        <v>-5.53335155473178e-13</v>
       </c>
       <c r="N22" t="n">
-        <v>-3238.065438907926</v>
+        <v>-3238.065438916907</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>4.001776687800884e-10</v>
       </c>
       <c r="P22" t="n">
-        <v>-9266.392311882228</v>
+        <v>-9266.392311878502</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>-9.640643838793039e-11</v>
       </c>
       <c r="R22" t="n">
-        <v>7.940798241179436e-09</v>
+        <v>5.697074811905622e-09</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.044675622732029e-11</v>
+        <v>5.53335155473178e-13</v>
       </c>
       <c r="T22" t="n">
-        <v>3238.065438971422</v>
+        <v>3238.065438962483</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>3.783497959375381e-10</v>
       </c>
     </row>
     <row r="23">
@@ -3028,37 +3028,37 @@
         <v>9266.392311885953</v>
       </c>
       <c r="K23" t="n">
-        <v>1.473381416872144e-10</v>
+        <v>-1.01863406598568e-10</v>
       </c>
       <c r="L23" t="n">
-        <v>9.896666597342119e-09</v>
+        <v>1.280568540096283e-09</v>
       </c>
       <c r="M23" t="n">
-        <v>2.933653320269514e-11</v>
+        <v>-4.352962434950314e-12</v>
       </c>
       <c r="N23" t="n">
-        <v>-3238.065438979261</v>
+        <v>-3238.065438944817</v>
       </c>
       <c r="O23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>-4.220055416226387e-10</v>
       </c>
       <c r="P23" t="n">
         <v>-9266.392311885953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.473381416872144e-10</v>
+        <v>1.01863406598568e-10</v>
       </c>
       <c r="R23" t="n">
-        <v>-9.896666597342119e-09</v>
+        <v>-1.280568540096283e-09</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.933653320269514e-11</v>
+        <v>4.352962434950314e-12</v>
       </c>
       <c r="T23" t="n">
-        <v>3238.065438900087</v>
+        <v>3238.065438934573</v>
       </c>
       <c r="U23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>-3.856257535517216e-10</v>
       </c>
     </row>
     <row r="24">
@@ -3089,43 +3089,43 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086894</v>
+        <v>-6001954935.086895</v>
       </c>
       <c r="J24" t="n">
-        <v>9266.392311878502</v>
+        <v>9266.392311882228</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>1.036823960021138e-10</v>
       </c>
       <c r="L24" t="n">
-        <v>1.939906724146567e-08</v>
+        <v>4.009052645415068e-09</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04991587540826e-11</v>
+        <v>-5.568878691519785e-13</v>
       </c>
       <c r="N24" t="n">
-        <v>-3238.065439017271</v>
+        <v>-3238.065438955702</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>4.292814992368221e-10</v>
       </c>
       <c r="P24" t="n">
-        <v>-9266.392311878502</v>
+        <v>-9266.392311882228</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>-1.036823960021138e-10</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.939906724146567e-08</v>
+        <v>-4.009052645415068e-09</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.04991587540826e-11</v>
+        <v>5.568878691519785e-13</v>
       </c>
       <c r="T24" t="n">
-        <v>3238.065438862105</v>
+        <v>3238.065438923659</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>4.074536263942719e-10</v>
       </c>
     </row>
     <row r="25">
@@ -3156,43 +3156,43 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086894</v>
+        <v>-6001954935.086895</v>
       </c>
       <c r="J25" t="n">
-        <v>9266.392311878502</v>
+        <v>9266.392311882228</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.491571310907602e-10</v>
+        <v>1.073203748092055e-10</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.949956640601158e-09</v>
+        <v>1.506123226135969e-09</v>
       </c>
       <c r="M25" t="n">
-        <v>2.923972175494782e-11</v>
+        <v>-4.338751580235112e-12</v>
       </c>
       <c r="N25" t="n">
-        <v>3238.065438947485</v>
+        <v>3238.065438933641</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.111804395914078e-10</v>
+        <v>4.292814992368221e-10</v>
       </c>
       <c r="P25" t="n">
-        <v>-9266.392311878502</v>
+        <v>-9266.392311882228</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.491571310907602e-10</v>
+        <v>-1.073203748092055e-10</v>
       </c>
       <c r="R25" t="n">
-        <v>1.949956640601158e-09</v>
+        <v>-1.506123226135969e-09</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.923972175494782e-11</v>
+        <v>4.338751580235112e-12</v>
       </c>
       <c r="T25" t="n">
-        <v>-3238.065438931885</v>
+        <v>-3238.06543894572</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.966285243630409e-10</v>
+        <v>4.220055416226387e-10</v>
       </c>
     </row>
     <row r="26">
@@ -3220,46 +3220,46 @@
         <v>-29.99792379152159</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436247</v>
+        <v>-28438031.75436246</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304318</v>
+        <v>-5999584758.304317</v>
       </c>
       <c r="J26" t="n">
-        <v>-1968.245637528598</v>
+        <v>-1968.245637536049</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.094947017729282e-11</v>
+        <v>-1.153239281848073e-09</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.78480535800918e-09</v>
+        <v>-2.65572452917695e-09</v>
       </c>
       <c r="M26" t="n">
-        <v>2.237432461527078e-11</v>
+        <v>-1.999733711954832e-12</v>
       </c>
       <c r="N26" t="n">
-        <v>732.9878821492639</v>
+        <v>732.9878821447492</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
       <c r="P26" t="n">
-        <v>1968.245637528598</v>
+        <v>1968.245637536049</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.094947017729282e-11</v>
+        <v>1.153239281848073e-09</v>
       </c>
       <c r="R26" t="n">
-        <v>3.78480535800918e-09</v>
+        <v>2.65572452917695e-09</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.237432461527078e-11</v>
+        <v>1.999733711954832e-12</v>
       </c>
       <c r="T26" t="n">
-        <v>-732.987882118985</v>
+        <v>-732.9878821235034</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321727</v>
+        <v>-239.9833903321726</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152159</v>
+        <v>-29.99792379152158</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436247</v>
+        <v>-28438031.75436246</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304318</v>
+        <v>-5999584758.304316</v>
       </c>
       <c r="J27" t="n">
-        <v>-1968.245637528598</v>
+        <v>-1968.245637543499</v>
       </c>
       <c r="K27" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>1.142325345426798e-09</v>
       </c>
       <c r="L27" t="n">
-        <v>8.479389634885592e-09</v>
+        <v>1.346052158623934e-09</v>
       </c>
       <c r="M27" t="n">
-        <v>2.60691468412233e-11</v>
+        <v>-7.044365091246618e-12</v>
       </c>
       <c r="N27" t="n">
-        <v>732.987882100203</v>
+        <v>732.9878821287421</v>
       </c>
       <c r="O27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>4.583853296935558e-09</v>
       </c>
       <c r="P27" t="n">
-        <v>1968.245637528598</v>
+        <v>1968.245637543499</v>
       </c>
       <c r="Q27" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-1.142325345426798e-09</v>
       </c>
       <c r="R27" t="n">
-        <v>-8.479389634885592e-09</v>
+        <v>-1.346052158623934e-09</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.60691468412233e-11</v>
+        <v>7.044365091246618e-12</v>
       </c>
       <c r="T27" t="n">
-        <v>-732.9878821680668</v>
+        <v>-732.9878821395105</v>
       </c>
       <c r="U27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>4.562025424093008e-09</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321726</v>
+        <v>-239.9833903321727</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152158</v>
+        <v>-29.99792379152159</v>
       </c>
       <c r="H28" t="n">
         <v>-28438031.75436246</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304316</v>
+        <v>-5999584758.304317</v>
       </c>
       <c r="J28" t="n">
-        <v>-1968.245637543499</v>
+        <v>-1968.245637536049</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.913048077374697e-11</v>
+        <v>-1.144144334830344e-09</v>
       </c>
       <c r="L28" t="n">
-        <v>1.400917426508386e-08</v>
+        <v>-1.091393642127514e-10</v>
       </c>
       <c r="M28" t="n">
-        <v>2.236144602818513e-11</v>
+        <v>-2.008393451546908e-12</v>
       </c>
       <c r="N28" t="n">
-        <v>732.9878820781033</v>
+        <v>732.9878821345628</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.591129254549742e-09</v>
       </c>
       <c r="P28" t="n">
-        <v>1968.245637543499</v>
+        <v>1968.245637536049</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.913048077374697e-11</v>
+        <v>1.144144334830344e-09</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.400917426508386e-08</v>
+        <v>1.091393642127514e-10</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.236144602818513e-11</v>
+        <v>2.008393451546908e-12</v>
       </c>
       <c r="T28" t="n">
-        <v>-732.9878821901764</v>
+        <v>-732.9878821336897</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.562025424093008e-09</v>
       </c>
     </row>
     <row r="29">
@@ -3424,43 +3424,43 @@
         <v>-28438031.75436247</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304317</v>
+        <v>-5999584758.304318</v>
       </c>
       <c r="J29" t="n">
-        <v>-1968.245637532324</v>
+        <v>-1968.245637528598</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-1.153239281848073e-09</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.980993147299159e-10</v>
+        <v>2.117303665727377e-09</v>
       </c>
       <c r="M29" t="n">
-        <v>2.612554617087426e-11</v>
+        <v>-7.068345908578522e-12</v>
       </c>
       <c r="N29" t="n">
-        <v>-732.9878821333361</v>
+        <v>-732.9878821425955</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.001776687800884e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
       <c r="P29" t="n">
-        <v>1968.245637532324</v>
+        <v>1968.245637528598</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>1.153239281848073e-09</v>
       </c>
       <c r="R29" t="n">
-        <v>1.980993147299159e-10</v>
+        <v>-2.117303665727377e-09</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.612554617087426e-11</v>
+        <v>7.068345908578522e-12</v>
       </c>
       <c r="T29" t="n">
-        <v>732.9878821349207</v>
+        <v>732.9878821256571</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.92901711165905e-10</v>
+        <v>-4.605681169778109e-09</v>
       </c>
     </row>
     <row r="30">
@@ -3485,49 +3485,49 @@
         <v>-240.0026150785242</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481552</v>
+        <v>-30.00032688481553</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680511</v>
+        <v>-28440309.88680512</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963103</v>
+        <v>-6000065376.963104</v>
       </c>
       <c r="J30" t="n">
         <v>309.8868051171303</v>
       </c>
       <c r="K30" t="n">
-        <v>1.205989974550903e-09</v>
+        <v>-1.702574081718922e-09</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.750866532456712e-10</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="M30" t="n">
-        <v>8.726019906646343e-12</v>
+        <v>-3.771205570046732e-12</v>
       </c>
       <c r="N30" t="n">
-        <v>-264.6010963687289</v>
+        <v>-264.6010963714798</v>
       </c>
       <c r="O30" t="n">
-        <v>4.823959898203611e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
       <c r="P30" t="n">
         <v>-309.8868051171303</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.205989974550903e-09</v>
+        <v>1.702574081718922e-09</v>
       </c>
       <c r="R30" t="n">
-        <v>6.750866532456712e-10</v>
+        <v>-1.455191522836685e-11</v>
       </c>
       <c r="S30" t="n">
-        <v>-8.726019906646343e-12</v>
+        <v>3.771205570046732e-12</v>
       </c>
       <c r="T30" t="n">
-        <v>264.6010963741877</v>
+        <v>264.6010963714798</v>
       </c>
       <c r="U30" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-6.803020369261503e-09</v>
       </c>
     </row>
     <row r="31">
@@ -3549,7 +3549,7 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785243</v>
+        <v>-240.0026150785242</v>
       </c>
       <c r="G31" t="n">
         <v>-30.00032688481553</v>
@@ -3558,43 +3558,43 @@
         <v>-28440309.88680512</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963106</v>
+        <v>-6000065376.963105</v>
       </c>
       <c r="J31" t="n">
-        <v>309.8868051245809</v>
+        <v>309.8868051208556</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.218722900375724e-09</v>
+        <v>1.709850039333105e-09</v>
       </c>
       <c r="L31" t="n">
-        <v>4.557804800242593e-09</v>
+        <v>7.712515071034431e-10</v>
       </c>
       <c r="M31" t="n">
-        <v>1.397171267569774e-11</v>
+        <v>-5.13833420257015e-12</v>
       </c>
       <c r="N31" t="n">
-        <v>-264.601096389707</v>
+        <v>-264.6010963745648</v>
       </c>
       <c r="O31" t="n">
-        <v>-4.874891601502895e-09</v>
+        <v>6.83940015733242e-09</v>
       </c>
       <c r="P31" t="n">
-        <v>-309.8868051245809</v>
+        <v>-309.8868051208556</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.218722900375724e-09</v>
+        <v>-1.709850039333105e-09</v>
       </c>
       <c r="R31" t="n">
-        <v>-4.557804800242593e-09</v>
+        <v>-7.712515071034431e-10</v>
       </c>
       <c r="S31" t="n">
-        <v>-1.397171267569774e-11</v>
+        <v>5.13833420257015e-12</v>
       </c>
       <c r="T31" t="n">
-        <v>264.6010963532444</v>
+        <v>264.6010963683948</v>
       </c>
       <c r="U31" t="n">
-        <v>-4.867615643888712e-09</v>
+        <v>6.83940015733242e-09</v>
       </c>
     </row>
     <row r="32">
@@ -3628,40 +3628,40 @@
         <v>-6000065376.963105</v>
       </c>
       <c r="J32" t="n">
-        <v>309.8868051208556</v>
+        <v>309.8868051245809</v>
       </c>
       <c r="K32" t="n">
-        <v>1.207808963954449e-09</v>
+        <v>-1.704393071122468e-09</v>
       </c>
       <c r="L32" t="n">
-        <v>6.185530310176546e-09</v>
+        <v>-2.066371962428093e-09</v>
       </c>
       <c r="M32" t="n">
-        <v>8.644529536638856e-12</v>
+        <v>-3.82671672127799e-12</v>
       </c>
       <c r="N32" t="n">
-        <v>-264.6010963962013</v>
+        <v>-264.6010963632143</v>
       </c>
       <c r="O32" t="n">
-        <v>4.838511813431978e-09</v>
+        <v>-6.81757228448987e-09</v>
       </c>
       <c r="P32" t="n">
-        <v>-309.8868051208556</v>
+        <v>-309.8868051245809</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.207808963954449e-09</v>
+        <v>1.704393071122468e-09</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.185530310176546e-09</v>
+        <v>2.066371962428093e-09</v>
       </c>
       <c r="S32" t="n">
-        <v>-8.644529536638856e-12</v>
+        <v>3.82671672127799e-12</v>
       </c>
       <c r="T32" t="n">
-        <v>264.6010963467751</v>
+        <v>264.6010963797453</v>
       </c>
       <c r="U32" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-6.824848242104053e-09</v>
       </c>
     </row>
     <row r="33">
@@ -3692,43 +3692,43 @@
         <v>-28440309.88680512</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963105</v>
+        <v>-6000065376.963104</v>
       </c>
       <c r="J33" t="n">
         <v>309.8868051171303</v>
       </c>
       <c r="K33" t="n">
-        <v>1.229636836796999e-09</v>
+        <v>-1.702574081718922e-09</v>
       </c>
       <c r="L33" t="n">
-        <v>1.223313006448734e-09</v>
+        <v>2.197339199483395e-09</v>
       </c>
       <c r="M33" t="n">
-        <v>1.392519433096595e-11</v>
+        <v>-5.157096971686315e-12</v>
       </c>
       <c r="N33" t="n">
-        <v>264.6010963665491</v>
+        <v>264.6010963626322</v>
       </c>
       <c r="O33" t="n">
-        <v>4.911271389573812e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
       <c r="P33" t="n">
         <v>-309.8868051171303</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.229636836796999e-09</v>
+        <v>1.702574081718922e-09</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.223313006448734e-09</v>
+        <v>-2.197339199483395e-09</v>
       </c>
       <c r="S33" t="n">
-        <v>-1.392519433096595e-11</v>
+        <v>5.157096971686315e-12</v>
       </c>
       <c r="T33" t="n">
-        <v>-264.6010963763936</v>
+        <v>-264.6010963802692</v>
       </c>
       <c r="U33" t="n">
-        <v>4.918547347187996e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I2" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>119.8844950930915</v>
+        <v>119.8844950930664</v>
       </c>
       <c r="Q2" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="R2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.24983693095458</v>
+        <v>-13.2498369309509</v>
       </c>
       <c r="T2" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="U2" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="AD2" t="n">
-        <v>-119.8844950930915</v>
+        <v>-119.8844950930664</v>
       </c>
       <c r="AE2" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.24983693095458</v>
+        <v>13.2498369309509</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="AI2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-19766.62946073191</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19766.62946072896</v>
+        <v>19766.6294607259</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>1.792584007606996e-12</v>
       </c>
       <c r="AL2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-69104.76771107486</v>
       </c>
       <c r="AM2" t="n">
-        <v>-69104.76771110963</v>
+        <v>-69104.76771109937</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="AO2" t="n">
-        <v>19766.62946073442</v>
+        <v>19766.62946073191</v>
       </c>
       <c r="AP2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-19766.6294607259</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.421003440282873e-11</v>
+        <v>-1.792584007606996e-12</v>
       </c>
       <c r="AR2" t="n">
-        <v>-49495.00905328659</v>
+        <v>-49495.00905328055</v>
       </c>
       <c r="AS2" t="n">
-        <v>-49495.00905329685</v>
+        <v>-49495.00905329204</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-30.00000000000005</v>
+        <v>-29.99999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28439999.99999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-6000000000.00001</v>
+        <v>-5999999999.999996</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>119.8844950930244</v>
+        <v>119.8844950930735</v>
       </c>
       <c r="Q3" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="R3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="T3" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="U3" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="AD3" t="n">
-        <v>-119.8844950930244</v>
+        <v>-119.8844950930735</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="AG3" t="n">
-        <v>-13.24983693093416</v>
+        <v>-13.24983693093785</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.450580596923828e-09</v>
       </c>
       <c r="AI3" t="n">
-        <v>19766.62946072038</v>
+        <v>19766.6294607229</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19766.62946072127</v>
+        <v>19766.62946072676</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>1.782190697250626e-12</v>
       </c>
       <c r="AL3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-69104.76771107831</v>
       </c>
       <c r="AM3" t="n">
-        <v>69104.76771105242</v>
+        <v>69104.76771106271</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>7.450580596923828e-09</v>
       </c>
       <c r="AO3" t="n">
-        <v>-19766.62946072038</v>
+        <v>-19766.6294607229</v>
       </c>
       <c r="AP3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-19766.62946072676</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.423009033885211e-11</v>
+        <v>-1.782190697250626e-12</v>
       </c>
       <c r="AR3" t="n">
-        <v>-49495.00905327238</v>
+        <v>-49495.00905328222</v>
       </c>
       <c r="AS3" t="n">
-        <v>49495.00905326986</v>
+        <v>49495.0090532747</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="G4" t="n">
-        <v>-30</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H4" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I4" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="Q4" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="R4" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="S4" t="n">
-        <v>13.24983693092235</v>
+        <v>13.24983693093862</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="U4" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="AC4" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="AD4" t="n">
-        <v>119.8844950931343</v>
+        <v>119.8844950930851</v>
       </c>
       <c r="AE4" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="AG4" t="n">
-        <v>-13.24983693092235</v>
+        <v>-13.24983693093862</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-3.352761268615723e-08</v>
       </c>
       <c r="AI4" t="n">
-        <v>19766.62946071211</v>
+        <v>19766.62946072307</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-19766.62946073354</v>
+        <v>-19766.62946072804</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>1.790573049363477e-12</v>
       </c>
       <c r="AL4" t="n">
-        <v>69104.76771110686</v>
+        <v>69104.76771108374</v>
       </c>
       <c r="AM4" t="n">
-        <v>69104.76771101885</v>
+        <v>69104.76771106377</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>3.352761268615723e-08</v>
       </c>
       <c r="AO4" t="n">
-        <v>-19766.62946071211</v>
+        <v>-19766.62946072307</v>
       </c>
       <c r="AP4" t="n">
-        <v>19766.62946073354</v>
+        <v>19766.62946072804</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.422151369217067e-11</v>
+        <v>-1.790573049363477e-12</v>
       </c>
       <c r="AR4" t="n">
-        <v>49495.00905329436</v>
+        <v>49495.00905328447</v>
       </c>
       <c r="AS4" t="n">
-        <v>49495.00905325378</v>
+        <v>49495.00905327461</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="G5" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30</v>
       </c>
       <c r="H5" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-119.8844950930671</v>
+        <v>-119.8844950930922</v>
       </c>
       <c r="Q5" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="R5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="S5" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="U5" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="AC5" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="AD5" t="n">
-        <v>119.8844950930671</v>
+        <v>119.8844950930922</v>
       </c>
       <c r="AE5" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="AF5" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.24983693096641</v>
+        <v>13.24983693095013</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>1.117587089538574e-08</v>
       </c>
       <c r="AI5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-19766.62946073173</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19766.62946072584</v>
+        <v>-19766.62946072889</v>
       </c>
       <c r="AK5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>1.803065637637907e-12</v>
       </c>
       <c r="AL5" t="n">
-        <v>69104.76771107491</v>
+        <v>69104.7677110872</v>
       </c>
       <c r="AM5" t="n">
-        <v>-69104.76771114318</v>
+        <v>-69104.76771109828</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-1.117587089538574e-08</v>
       </c>
       <c r="AO5" t="n">
-        <v>19766.62946074268</v>
+        <v>19766.62946073173</v>
       </c>
       <c r="AP5" t="n">
-        <v>19766.62946072584</v>
+        <v>19766.62946072889</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.422188588688456e-11</v>
+        <v>-1.803065637637907e-12</v>
       </c>
       <c r="AR5" t="n">
-        <v>49495.00905328012</v>
+        <v>49495.00905328616</v>
       </c>
       <c r="AS5" t="n">
-        <v>-49495.0090533129</v>
+        <v>-49495.00905329208</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-29.99999999999998</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H6" t="n">
-        <v>-28439999.99999998</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I6" t="n">
-        <v>-5999999999.999995</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J6" t="n">
-        <v>119.8844950930915</v>
+        <v>119.8844950930664</v>
       </c>
       <c r="K6" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="L6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.24983693095458</v>
+        <v>-13.2498369309509</v>
       </c>
       <c r="N6" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="O6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>120.039098701767</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="Q6" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="R6" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="S6" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071110052</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="U6" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="V6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="X6" t="n">
-        <v>-119.8844950930915</v>
+        <v>-119.8844950930664</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.24983693095458</v>
+        <v>13.2498369309509</v>
       </c>
       <c r="AB6" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="AC6" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="AD6" t="n">
-        <v>-120.039098701767</v>
+        <v>-120.0390987017059</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071110052</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="AI6" t="n">
-        <v>7608.033479463036</v>
+        <v>7608.03347946563</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-7608.033479468945</v>
+        <v>-7608.033479471618</v>
       </c>
       <c r="AK6" t="n">
-        <v>-3.867834873910378e-11</v>
+        <v>3.393530821440233e-12</v>
       </c>
       <c r="AL6" t="n">
-        <v>34787.69005993183</v>
+        <v>34787.69005993984</v>
       </c>
       <c r="AM6" t="n">
-        <v>34787.69005991481</v>
+        <v>34787.690059922</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="AO6" t="n">
-        <v>-7608.033479463036</v>
+        <v>-7608.03347946563</v>
       </c>
       <c r="AP6" t="n">
-        <v>7608.033479468945</v>
+        <v>7608.033479471618</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.867834873910378e-11</v>
+        <v>-3.393530821440233e-12</v>
       </c>
       <c r="AR6" t="n">
-        <v>10860.51081688182</v>
+        <v>10860.51081688989</v>
       </c>
       <c r="AS6" t="n">
-        <v>10860.51081686339</v>
+        <v>10860.51081687179</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-180.0000000000002</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-30.00000000000004</v>
+        <v>-29.99999999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28439999.99999998</v>
       </c>
       <c r="I7" t="n">
-        <v>-6000000000.000008</v>
+        <v>-5999999999.999995</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8844950930244</v>
+        <v>119.8844950930735</v>
       </c>
       <c r="K7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="L7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="N7" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="O7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="P7" t="n">
-        <v>120.0390987015889</v>
+        <v>120.0390987017214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="R7" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="U7" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="V7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="X7" t="n">
-        <v>-119.8844950930244</v>
+        <v>-119.8844950930735</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="AA7" t="n">
-        <v>-13.24983693093416</v>
+        <v>-13.24983693093785</v>
       </c>
       <c r="AB7" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="AC7" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="AD7" t="n">
-        <v>-120.0390987015889</v>
+        <v>-120.0390987017214</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071123615</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.097819328308105e-08</v>
+        <v>-1.490116119384766e-08</v>
       </c>
       <c r="AI7" t="n">
-        <v>-7608.033479476842</v>
+        <v>-7608.033479474256</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-7608.033479476904</v>
+        <v>-7608.033479470603</v>
       </c>
       <c r="AK7" t="n">
-        <v>-3.867545858883965e-11</v>
+        <v>3.450695314746986e-12</v>
       </c>
       <c r="AL7" t="n">
-        <v>34787.69005995742</v>
+        <v>34787.69005993747</v>
       </c>
       <c r="AM7" t="n">
-        <v>-34787.69005995538</v>
+        <v>-34787.69005994825</v>
       </c>
       <c r="AN7" t="n">
-        <v>-4.097819328308105e-08</v>
+        <v>1.490116119384766e-08</v>
       </c>
       <c r="AO7" t="n">
-        <v>7608.033479476842</v>
+        <v>7608.033479474256</v>
       </c>
       <c r="AP7" t="n">
-        <v>7608.033479476904</v>
+        <v>7608.033479470603</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.867545858883965e-11</v>
+        <v>-3.450695314746986e-12</v>
       </c>
       <c r="AR7" t="n">
-        <v>10860.51081690402</v>
+        <v>10860.51081688613</v>
       </c>
       <c r="AS7" t="n">
-        <v>-10860.51081690566</v>
+        <v>-10860.51081689728</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-30</v>
+        <v>-29.99999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999995</v>
       </c>
       <c r="I8" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.99999</v>
       </c>
       <c r="J8" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="K8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="L8" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="M8" t="n">
-        <v>13.24983693092235</v>
+        <v>13.24983693093862</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="O8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="P8" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="Q8" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="R8" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="T8" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="U8" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="V8" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="W8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="X8" t="n">
-        <v>119.8844950931343</v>
+        <v>119.8844950930851</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="AA8" t="n">
-        <v>-13.24983693092235</v>
+        <v>-13.24983693093862</v>
       </c>
       <c r="AB8" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="AC8" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="AD8" t="n">
-        <v>120.039098701887</v>
+        <v>120.0390987017544</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.917176071140197</v>
+        <v>2.917176071121575</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-4.842877388000488e-08</v>
       </c>
       <c r="AI8" t="n">
-        <v>-7608.033479484184</v>
+        <v>-7608.03347947371</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7608.03347946298</v>
+        <v>7608.033479469254</v>
       </c>
       <c r="AK8" t="n">
-        <v>-3.868580190546846e-11</v>
+        <v>3.346394768910892e-12</v>
       </c>
       <c r="AL8" t="n">
-        <v>-34787.6900599128</v>
+        <v>-34787.69005993268</v>
       </c>
       <c r="AM8" t="n">
-        <v>-34787.69005997882</v>
+        <v>-34787.69005994567</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>4.842877388000488e-08</v>
       </c>
       <c r="AO8" t="n">
-        <v>7608.033479484184</v>
+        <v>7608.03347947371</v>
       </c>
       <c r="AP8" t="n">
-        <v>-7608.03347946298</v>
+        <v>-7608.033479469254</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.868580190546846e-11</v>
+        <v>-3.346394768910892e-12</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10860.51081686508</v>
+        <v>-10860.51081688284</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10860.51081692625</v>
+        <v>-10860.51081689657</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-179.9999999999998</v>
+        <v>-180</v>
       </c>
       <c r="G9" t="n">
-        <v>-29.99999999999997</v>
+        <v>-30</v>
       </c>
       <c r="H9" t="n">
-        <v>-28439999.99999997</v>
+        <v>-28440000</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999993</v>
+        <v>-5999999999.999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-119.8844950930671</v>
+        <v>-119.8844950930922</v>
       </c>
       <c r="K9" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="L9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="O9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="P9" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="Q9" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="R9" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="S9" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="T9" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="U9" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="V9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="W9" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="X9" t="n">
-        <v>119.8844950930671</v>
+        <v>119.8844950930922</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="Z9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.24983693096641</v>
+        <v>13.24983693095013</v>
       </c>
       <c r="AB9" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="AC9" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="AD9" t="n">
-        <v>120.0390987017087</v>
+        <v>120.0390987017699</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="AG9" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071112084</v>
       </c>
       <c r="AH9" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>-3.725290298461914e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>7608.03347945568</v>
+        <v>7608.033479466165</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7608.033479470957</v>
+        <v>7608.033479468249</v>
       </c>
       <c r="AK9" t="n">
-        <v>-3.869313251766919e-11</v>
+        <v>3.392131079729449e-12</v>
       </c>
       <c r="AL9" t="n">
-        <v>-34787.69005993844</v>
+        <v>-34787.69005993038</v>
       </c>
       <c r="AM9" t="n">
-        <v>34787.69005989138</v>
+        <v>34787.69005992453</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>3.725290298461914e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>-7608.03347945568</v>
+        <v>-7608.033479466165</v>
       </c>
       <c r="AP9" t="n">
-        <v>-7608.033479470957</v>
+        <v>-7608.033479468249</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.869313251766919e-11</v>
+        <v>-3.392131079729449e-12</v>
       </c>
       <c r="AR9" t="n">
-        <v>-10860.51081688729</v>
+        <v>-10860.51081687913</v>
       </c>
       <c r="AS9" t="n">
-        <v>10860.51081684273</v>
+        <v>10860.51081687245</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180</v>
+        <v>-180.0000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30</v>
+        <v>-30.00000000000004</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000</v>
+        <v>-28440000.00000004</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000</v>
+        <v>-6000000000.000008</v>
       </c>
       <c r="J10" t="n">
-        <v>120.039098701767</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="K10" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="L10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="M10" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071110052</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="O10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="P10" t="n">
-        <v>119.9916951661322</v>
+        <v>119.9916951660409</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="R10" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-0.6603494433671542</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="U10" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="V10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="W10" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="X10" t="n">
-        <v>-120.039098701767</v>
+        <v>-120.0390987017059</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071110052</v>
       </c>
       <c r="AB10" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="AC10" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="AD10" t="n">
-        <v>-119.9916951661322</v>
+        <v>-119.9916951660409</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6603494433687225</v>
+        <v>0.6603494433671542</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>4.470348358154297e-08</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1658.358832414433</v>
+        <v>-1658.358832413913</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1658.358832411864</v>
+        <v>1658.358832409609</v>
       </c>
       <c r="AK10" t="n">
-        <v>-4.010927424673966e-11</v>
+        <v>3.927541217236775e-12</v>
       </c>
       <c r="AL10" t="n">
-        <v>-7622.445377949901</v>
+        <v>-7622.445377944154</v>
       </c>
       <c r="AM10" t="n">
-        <v>-7622.445377955475</v>
+        <v>-7622.445377954864</v>
       </c>
       <c r="AN10" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-4.470348358154297e-08</v>
       </c>
       <c r="AO10" t="n">
-        <v>1658.358832414433</v>
+        <v>1658.358832413913</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1658.358832411864</v>
+        <v>-1658.358832409609</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.010927424673966e-11</v>
+        <v>-3.927541217236775e-12</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2327.707616521262</v>
+        <v>-2327.707616513508</v>
       </c>
       <c r="AS10" t="n">
-        <v>-2327.70761653113</v>
+        <v>-2327.707616528598</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-180.0000000000001</v>
+        <v>-179.9999999999998</v>
       </c>
       <c r="G11" t="n">
-        <v>-30.00000000000001</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H11" t="n">
-        <v>-28440000.00000001</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I11" t="n">
-        <v>-6000000000.000001</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J11" t="n">
-        <v>120.0390987015889</v>
+        <v>120.0390987017214</v>
       </c>
       <c r="K11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="L11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="O11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="P11" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="Q11" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="R11" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="U11" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="V11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="W11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="X11" t="n">
-        <v>-120.0390987015889</v>
+        <v>-120.0390987017214</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="Z11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071123615</v>
       </c>
       <c r="AB11" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="AC11" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="AD11" t="n">
-        <v>-119.9916951658417</v>
+        <v>-119.9916951660554</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-0.6603494433610113</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>-3.725290298461914e-08</v>
       </c>
       <c r="AI11" t="n">
-        <v>1658.358832404872</v>
+        <v>1658.358832405404</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1658.358832402486</v>
+        <v>1658.358832408467</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.012493149746856e-11</v>
+        <v>3.882815524963767e-12</v>
       </c>
       <c r="AL11" t="n">
-        <v>-7622.445377924581</v>
+        <v>-7622.445377941214</v>
       </c>
       <c r="AM11" t="n">
-        <v>7622.445377934186</v>
+        <v>7622.445377934841</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>3.725290298461914e-08</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1658.358832404872</v>
+        <v>-1658.358832405404</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1658.358832402486</v>
+        <v>-1658.358832408467</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.012493149746856e-11</v>
+        <v>-3.882815524963767e-12</v>
       </c>
       <c r="AR11" t="n">
-        <v>-2327.707616490355</v>
+        <v>-2327.707616509579</v>
       </c>
       <c r="AS11" t="n">
-        <v>2327.707616495056</v>
+        <v>2327.707616497588</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-180.0000000000001</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-30.00000000000001</v>
+        <v>-29.99999999999998</v>
       </c>
       <c r="H12" t="n">
-        <v>-28440000.00000001</v>
+        <v>-28439999.99999998</v>
       </c>
       <c r="I12" t="n">
-        <v>-6000000000.000001</v>
+        <v>-5999999999.999995</v>
       </c>
       <c r="J12" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="K12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="L12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="N12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="O12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="P12" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="Q12" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="R12" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="S12" t="n">
-        <v>0.660349443347221</v>
+        <v>0.6603494433643113</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="U12" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="V12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="W12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="X12" t="n">
-        <v>120.039098701887</v>
+        <v>120.0390987017544</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.917176071140197</v>
+        <v>2.917176071121575</v>
       </c>
       <c r="AB12" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="AC12" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="AD12" t="n">
-        <v>119.991695166331</v>
+        <v>119.9916951661173</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.660349443347221</v>
+        <v>-0.6603494433643113</v>
       </c>
       <c r="AH12" t="n">
+        <v>-7.450580596923828e-09</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1658.358832407139</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-1658.35883241082</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4.023333503681037e-12</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>7622.445377948388</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>7622.445377940967</v>
+      </c>
+      <c r="AN12" t="n">
         <v>7.450580596923828e-09</v>
       </c>
-      <c r="AI12" t="n">
-        <v>1658.358832396134</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-1658.358832416807</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-4.012638059121664e-11</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>7622.445377965032</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>7622.445377909098</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-7.450580596923828e-09</v>
-      </c>
       <c r="AO12" t="n">
-        <v>-1658.358832396134</v>
+        <v>-1658.358832407139</v>
       </c>
       <c r="AP12" t="n">
-        <v>1658.358832416807</v>
+        <v>1658.35883241082</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.012638059121664e-11</v>
+        <v>-4.023333503681037e-12</v>
       </c>
       <c r="AR12" t="n">
-        <v>2327.707616535823</v>
+        <v>2327.707616516534</v>
       </c>
       <c r="AS12" t="n">
-        <v>2327.707616467713</v>
+        <v>2327.707616501837</v>
       </c>
     </row>
     <row r="13">
@@ -5532,112 +5532,112 @@
         <v>-6000000000.000004</v>
       </c>
       <c r="J13" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="K13" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="L13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="M13" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="N13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="O13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="P13" t="n">
-        <v>-119.9916951660405</v>
+        <v>-119.9916951661319</v>
       </c>
       <c r="Q13" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="R13" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="U13" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="V13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="W13" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="X13" t="n">
-        <v>120.0390987017087</v>
+        <v>120.0390987017699</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071112084</v>
       </c>
       <c r="AB13" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="AD13" t="n">
-        <v>119.9916951660405</v>
+        <v>119.9916951661319</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.6603494433809615</v>
+        <v>0.6603494433638429</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>2.235174179077148e-08</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1658.358832423168</v>
+        <v>-1658.358832412167</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1658.358832407449</v>
+        <v>-1658.358832409711</v>
       </c>
       <c r="AK13" t="n">
-        <v>-4.011772803527846e-11</v>
+        <v>3.889027553857218e-12</v>
       </c>
       <c r="AL13" t="n">
-        <v>7622.445377939776</v>
+        <v>7622.445377945551</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7622.445377980606</v>
+        <v>-7622.445377948679</v>
       </c>
       <c r="AN13" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-2.235174179077148e-08</v>
       </c>
       <c r="AO13" t="n">
-        <v>1658.358832423168</v>
+        <v>1658.358832412167</v>
       </c>
       <c r="AP13" t="n">
-        <v>1658.358832407449</v>
+        <v>1658.358832409711</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.011772803527846e-11</v>
+        <v>-3.889027553857218e-12</v>
       </c>
       <c r="AR13" t="n">
-        <v>2327.707616504927</v>
+        <v>2327.707616512693</v>
       </c>
       <c r="AS13" t="n">
-        <v>-2327.7076165584</v>
+        <v>-2327.707616524305</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000001</v>
+        <v>-180.0000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000002</v>
+        <v>-30.00000000000004</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000002</v>
+        <v>-28440000.00000004</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000004</v>
+        <v>-6000000000.000008</v>
       </c>
       <c r="J14" t="n">
-        <v>119.9916951661322</v>
+        <v>119.9916951660409</v>
       </c>
       <c r="K14" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="L14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-0.6603494433671542</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="O14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="P14" t="n">
-        <v>120.001307539296</v>
+        <v>120.0013075391888</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="R14" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2383793660995245</v>
+        <v>0.2383793661006169</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="U14" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="V14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="W14" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="X14" t="n">
-        <v>-119.9916951661322</v>
+        <v>-119.9916951660409</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6603494433687225</v>
+        <v>0.6603494433671542</v>
       </c>
       <c r="AB14" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="AC14" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="AD14" t="n">
-        <v>-120.001307539296</v>
+        <v>-120.0013075391888</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-0.2383793661006169</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>4.470348358154297e-08</v>
       </c>
       <c r="AI14" t="n">
-        <v>309.8868051251302</v>
+        <v>309.8868051258833</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-309.8868051271218</v>
+        <v>-309.8868051280224</v>
       </c>
       <c r="AK14" t="n">
-        <v>-2.410522176876903e-11</v>
+        <v>7.834545089346882e-12</v>
       </c>
       <c r="AL14" t="n">
-        <v>1594.71973438634</v>
+        <v>1594.719734387909</v>
       </c>
       <c r="AM14" t="n">
-        <v>1594.719734381884</v>
+        <v>1594.719734383805</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-4.470348358154297e-08</v>
       </c>
       <c r="AO14" t="n">
-        <v>-309.8868051251302</v>
+        <v>-309.8868051258833</v>
       </c>
       <c r="AP14" t="n">
-        <v>309.8868051271218</v>
+        <v>309.8868051280224</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.410522176876903e-11</v>
+        <v>-7.834545089346882e-12</v>
       </c>
       <c r="AR14" t="n">
-        <v>264.6010963763609</v>
+        <v>264.6010963802401</v>
       </c>
       <c r="AS14" t="n">
-        <v>264.6010963688896</v>
+        <v>264.6010963715089</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-180</v>
+        <v>-179.9999999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>-30</v>
+        <v>-29.99999999999996</v>
       </c>
       <c r="H15" t="n">
-        <v>-28440000</v>
+        <v>-28439999.99999996</v>
       </c>
       <c r="I15" t="n">
-        <v>-6000000000</v>
+        <v>-5999999999.999991</v>
       </c>
       <c r="J15" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="K15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="L15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="O15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="P15" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075392201</v>
       </c>
       <c r="Q15" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="R15" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-0.2383793661002568</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="U15" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="V15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="W15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="X15" t="n">
-        <v>-119.9916951658417</v>
+        <v>-119.9916951660554</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-0.6603494433610113</v>
       </c>
       <c r="AB15" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="AC15" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="AD15" t="n">
-        <v>-120.0013075389503</v>
+        <v>-120.0013075392201</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2383793661013374</v>
+        <v>0.2383793661002568</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-2.980232238769531e-08</v>
       </c>
       <c r="AI15" t="n">
-        <v>-309.8868051250465</v>
+        <v>-309.8868051242753</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-309.8868051299721</v>
+        <v>-309.8868051258978</v>
       </c>
       <c r="AK15" t="n">
-        <v>-2.409488232592988e-11</v>
+        <v>7.819979700184162e-12</v>
       </c>
       <c r="AL15" t="n">
-        <v>1594.719734390186</v>
+        <v>1594.719734380909</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1594.719734376107</v>
+        <v>-1594.719734374157</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.980232238769531e-08</v>
       </c>
       <c r="AO15" t="n">
-        <v>309.8868051250465</v>
+        <v>309.8868051242753</v>
       </c>
       <c r="AP15" t="n">
-        <v>309.8868051299721</v>
+        <v>309.8868051258978</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.409488232592988e-11</v>
+        <v>-7.819979700184162e-12</v>
       </c>
       <c r="AR15" t="n">
-        <v>264.6010963896686</v>
+        <v>264.6010963744775</v>
       </c>
       <c r="AS15" t="n">
-        <v>-264.6010963741574</v>
+        <v>-264.6010963714798</v>
       </c>
     </row>
     <row r="16">
@@ -5949,112 +5949,112 @@
         <v>-6000000000</v>
       </c>
       <c r="J16" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="K16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="L16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="M16" t="n">
-        <v>0.660349443347221</v>
+        <v>0.6603494433643113</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="O16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="P16" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="Q16" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="R16" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="U16" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="V16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="W16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="X16" t="n">
-        <v>119.991695166331</v>
+        <v>119.9916951661173</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.660349443347221</v>
+        <v>-0.6603494433643113</v>
       </c>
       <c r="AB16" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="AC16" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="AD16" t="n">
-        <v>120.0013075395739</v>
+        <v>120.0013075393042</v>
       </c>
       <c r="AE16" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2383793661078827</v>
+        <v>0.2383793660978497</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-309.8868051309946</v>
+        <v>-309.8868051217396</v>
       </c>
       <c r="AJ16" t="n">
-        <v>309.8868051201698</v>
+        <v>309.8868051242207</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.411927784824087e-11</v>
+        <v>7.783451216547496e-12</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1594.719734367751</v>
+        <v>-1594.719734376951</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1594.719734389742</v>
+        <v>-1594.719734367216</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>309.8868051309946</v>
+        <v>309.8868051217396</v>
       </c>
       <c r="AP16" t="n">
-        <v>-309.8868051201698</v>
+        <v>-309.8868051242207</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.411927784824087e-11</v>
+        <v>-7.783451216547496e-12</v>
       </c>
       <c r="AR16" t="n">
-        <v>-264.6010963532681</v>
+        <v>-264.6010963683948</v>
       </c>
       <c r="AS16" t="n">
-        <v>-264.601096396189</v>
+        <v>-264.6010963631998</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000002</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000004</v>
+        <v>-30.00000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000004</v>
+        <v>-28440000.00000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000008</v>
+        <v>-6000000000.000004</v>
       </c>
       <c r="J17" t="n">
-        <v>-119.9916951660405</v>
+        <v>-119.9916951661319</v>
       </c>
       <c r="K17" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="L17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="O17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="P17" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="R17" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="S17" t="n">
-        <v>0.238379366093001</v>
+        <v>0.2383793661030328</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="U17" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="V17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="X17" t="n">
-        <v>119.9916951660405</v>
+        <v>119.9916951661319</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6603494433809615</v>
+        <v>0.6603494433638429</v>
       </c>
       <c r="AB17" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="AC17" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="AD17" t="n">
-        <v>120.0013075392282</v>
+        <v>120.0013075393354</v>
       </c>
       <c r="AE17" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.238379366093001</v>
+        <v>-0.2383793661030328</v>
       </c>
       <c r="AH17" t="n">
         <v>2.980232238769531e-08</v>
       </c>
       <c r="AI17" t="n">
-        <v>309.8868051191603</v>
+        <v>309.8868051283935</v>
       </c>
       <c r="AJ17" t="n">
-        <v>309.886805123052</v>
+        <v>309.8868051221543</v>
       </c>
       <c r="AK17" t="n">
-        <v>-2.409387806605927e-11</v>
+        <v>7.860845011439737e-12</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1594.719734371638</v>
+        <v>-1594.719734370112</v>
       </c>
       <c r="AM17" t="n">
-        <v>1594.719734368206</v>
+        <v>1594.719734390674</v>
       </c>
       <c r="AN17" t="n">
         <v>-2.980232238769531e-08</v>
       </c>
       <c r="AO17" t="n">
-        <v>-309.8868051191603</v>
+        <v>-309.8868051283935</v>
       </c>
       <c r="AP17" t="n">
-        <v>-309.886805123052</v>
+        <v>-309.8868051221543</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.409387806605927e-11</v>
+        <v>-7.860845011439737e-12</v>
       </c>
       <c r="AR17" t="n">
-        <v>-264.6010963666739</v>
+        <v>-264.6010963628069</v>
       </c>
       <c r="AS17" t="n">
-        <v>264.6010963467415</v>
+        <v>264.6010963796871</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861586</v>
+        <v>-239.7689901861587</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326983</v>
+        <v>-29.97112377326984</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.3370598</v>
+        <v>-28412625.33705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653966</v>
+        <v>-5994224754.653967</v>
       </c>
       <c r="J18" t="n">
-        <v>119.8844950930915</v>
+        <v>119.8844950930664</v>
       </c>
       <c r="K18" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="L18" t="n">
+        <v>-180.0000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-13.2498369309509</v>
+      </c>
+      <c r="N18" t="n">
+        <v>13.2498369309421</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-6.298268134835391e-13</v>
+      </c>
+      <c r="P18" t="n">
+        <v>119.8844950930735</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-119.8844950930415</v>
+      </c>
+      <c r="R18" t="n">
         <v>-179.9999999999999</v>
       </c>
-      <c r="M18" t="n">
-        <v>-13.24983693095458</v>
-      </c>
-      <c r="N18" t="n">
-        <v>13.24983693094634</v>
-      </c>
-      <c r="O18" t="n">
-        <v>8.506228303696583e-12</v>
-      </c>
-      <c r="P18" t="n">
-        <v>119.8844950930244</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-119.8844950930202</v>
-      </c>
-      <c r="R18" t="n">
-        <v>-180.0000000000003</v>
-      </c>
       <c r="S18" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="T18" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="U18" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="V18" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="W18" t="n">
-        <v>-119.8844950930915</v>
+        <v>-119.8844950930664</v>
       </c>
       <c r="X18" t="n">
+        <v>-180.0000000000001</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.2498369309421</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13.2498369309509</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-6.298268134835391e-13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-119.8844950930415</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-119.8844950930735</v>
+      </c>
+      <c r="AD18" t="n">
         <v>-179.9999999999999</v>
       </c>
-      <c r="Y18" t="n">
-        <v>13.24983693094634</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>13.24983693095458</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>8.506228303696583e-12</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-119.8844950930202</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-119.8844950930244</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-180.0000000000003</v>
-      </c>
       <c r="AE18" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="AF18" t="n">
-        <v>-13.24983693093416</v>
+        <v>-13.24983693093785</v>
       </c>
       <c r="AG18" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="AH18" t="n">
-        <v>-27374.66294020042</v>
+        <v>-27374.66294019669</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>2.146407496184111e-10</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-8.45739123178646e-09</v>
+        <v>-5.453330231830478e-09</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.558309120104241e-11</v>
+        <v>-2.561506562415161e-12</v>
       </c>
       <c r="AL18" t="n">
-        <v>14707.31899338208</v>
+        <v>14707.31899337007</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>8.512870408594608e-10</v>
       </c>
       <c r="AN18" t="n">
-        <v>27374.66294020042</v>
+        <v>27374.66294019669</v>
       </c>
       <c r="AO18" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-2.146407496184111e-10</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.45739123178646e-09</v>
+        <v>5.453330231830478e-09</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-2.558309120104241e-11</v>
+        <v>2.561506562415161e-12</v>
       </c>
       <c r="AR18" t="n">
-        <v>-14707.31899331443</v>
+        <v>-14707.31899332644</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>8.585629984736443e-10</v>
       </c>
     </row>
     <row r="19">
@@ -6354,7 +6354,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861587</v>
+        <v>-239.7689901861586</v>
       </c>
       <c r="G19" t="n">
         <v>-29.97112377326983</v>
@@ -6363,115 +6363,115 @@
         <v>-28412625.3370598</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653967</v>
+        <v>-5994224754.653966</v>
       </c>
       <c r="J19" t="n">
-        <v>119.8844950930244</v>
+        <v>119.8844950930735</v>
       </c>
       <c r="K19" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="L19" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="N19" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="O19" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="P19" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="Q19" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="R19" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="S19" t="n">
-        <v>13.24983693092235</v>
+        <v>13.24983693093862</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="U19" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="V19" t="n">
-        <v>119.8844950930244</v>
+        <v>119.8844950930735</v>
       </c>
       <c r="W19" t="n">
-        <v>-119.8844950930202</v>
+        <v>-119.8844950930415</v>
       </c>
       <c r="X19" t="n">
-        <v>-180.0000000000003</v>
+        <v>-179.9999999999999</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.24983693093416</v>
+        <v>13.24983693093785</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.24983693093435</v>
+        <v>13.2498369309433</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>-6.261751098448146e-13</v>
       </c>
       <c r="AB19" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="AC19" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="AD19" t="n">
-        <v>-180</v>
+        <v>-179.9999999999997</v>
       </c>
       <c r="AE19" t="n">
-        <v>13.24983693092235</v>
+        <v>13.24983693093862</v>
       </c>
       <c r="AF19" t="n">
-        <v>-13.24983693095439</v>
+        <v>-13.24983693094545</v>
       </c>
       <c r="AG19" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>-6.291202605871676e-13</v>
       </c>
       <c r="AH19" t="n">
         <v>-27374.66294019669</v>
       </c>
       <c r="AI19" t="n">
-        <v>-9.276845958083868e-11</v>
+        <v>-2.128217602148652e-10</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8.317329047713429e-09</v>
+        <v>8.74933903105557e-10</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.521716169212596e-11</v>
+        <v>-1.644906433284632e-12</v>
       </c>
       <c r="AL19" t="n">
-        <v>14707.31899331497</v>
+        <v>14707.31899334475</v>
       </c>
       <c r="AM19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-8.512870408594608e-10</v>
       </c>
       <c r="AN19" t="n">
         <v>27374.66294019669</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.276845958083868e-11</v>
+        <v>2.128217602148652e-10</v>
       </c>
       <c r="AP19" t="n">
-        <v>-8.317329047713429e-09</v>
+        <v>-8.74933903105557e-10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-2.521716169212596e-11</v>
+        <v>1.644906433284632e-12</v>
       </c>
       <c r="AR19" t="n">
-        <v>-14707.31899338152</v>
+        <v>-14707.31899335176</v>
       </c>
       <c r="AS19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-8.585629984736443e-10</v>
       </c>
     </row>
     <row r="20">
@@ -6505,112 +6505,112 @@
         <v>-5994224754.653966</v>
       </c>
       <c r="J20" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="K20" t="n">
-        <v>-119.8844950929513</v>
+        <v>-119.8844950930445</v>
       </c>
       <c r="L20" t="n">
+        <v>-179.9999999999997</v>
+      </c>
+      <c r="M20" t="n">
+        <v>13.24983693093862</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-13.24983693094545</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-6.291202605871676e-13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-119.8844950930922</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>119.8844950931142</v>
+      </c>
+      <c r="R20" t="n">
         <v>-180</v>
       </c>
-      <c r="M20" t="n">
-        <v>13.24983693092235</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-13.24983693095439</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8.510261567519426e-12</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-119.8844950930671</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>119.8844950932074</v>
-      </c>
-      <c r="R20" t="n">
-        <v>-179.9999999999999</v>
-      </c>
       <c r="S20" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="U20" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="V20" t="n">
-        <v>119.8844950929513</v>
+        <v>119.8844950930445</v>
       </c>
       <c r="W20" t="n">
-        <v>-119.8844950931343</v>
+        <v>-119.8844950930851</v>
       </c>
       <c r="X20" t="n">
+        <v>-179.9999999999997</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.24983693094545</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>13.24983693093862</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-6.291202605871676e-13</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-119.8844950931142</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-119.8844950930922</v>
+      </c>
+      <c r="AD20" t="n">
         <v>-180</v>
       </c>
-      <c r="Y20" t="n">
-        <v>13.24983693095439</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>13.24983693092235</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>8.510261567519426e-12</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>-119.8844950932074</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>-119.8844950930671</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>-179.9999999999999</v>
-      </c>
       <c r="AE20" t="n">
-        <v>13.24983693094242</v>
+        <v>13.24983693094665</v>
       </c>
       <c r="AF20" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="AG20" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="AH20" t="n">
-        <v>-27374.66294019669</v>
+        <v>-27374.66294020042</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>2.110027708113194e-10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.831995177781209e-08</v>
+        <v>4.825778887607157e-09</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.55582222052908e-11</v>
+        <v>-2.561506562415161e-12</v>
       </c>
       <c r="AL20" t="n">
-        <v>14707.31899327498</v>
+        <v>14707.31899332895</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
       <c r="AN20" t="n">
-        <v>27374.66294019669</v>
+        <v>27374.66294020042</v>
       </c>
       <c r="AO20" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-2.110027708113194e-10</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1.831995177781209e-08</v>
+        <v>-4.825778887607157e-09</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-2.55582222052908e-11</v>
+        <v>2.561506562415161e-12</v>
       </c>
       <c r="AR20" t="n">
-        <v>-14707.31899342155</v>
+        <v>-14707.31899336755</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861587</v>
+        <v>-239.7689901861586</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326984</v>
+        <v>-29.97112377326983</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.33705981</v>
+        <v>-28412625.3370598</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653967</v>
+        <v>-5994224754.653966</v>
       </c>
       <c r="J21" t="n">
-        <v>-119.8844950930671</v>
+        <v>-119.8844950930922</v>
       </c>
       <c r="K21" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="L21" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.24983693096641</v>
+        <v>-13.24983693095013</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="O21" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>-6.335095483592647e-13</v>
       </c>
       <c r="P21" t="n">
-        <v>119.8844950930915</v>
+        <v>119.8844950930664</v>
       </c>
       <c r="Q21" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="R21" t="n">
-        <v>-179.9999999999999</v>
+        <v>-180.0000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-13.24983693095458</v>
+        <v>-13.2498369309509</v>
       </c>
       <c r="T21" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="U21" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>-6.298268134835391e-13</v>
       </c>
       <c r="V21" t="n">
-        <v>119.8844950930671</v>
+        <v>119.8844950930922</v>
       </c>
       <c r="W21" t="n">
-        <v>119.8844950932074</v>
+        <v>119.8844950931142</v>
       </c>
       <c r="X21" t="n">
-        <v>179.9999999999999</v>
+        <v>180</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.24983693096641</v>
+        <v>13.24983693095013</v>
       </c>
       <c r="Z21" t="n">
-        <v>-13.24983693094242</v>
+        <v>-13.24983693094665</v>
       </c>
       <c r="AA21" t="n">
-        <v>-8.510392338635117e-12</v>
+        <v>6.335095483592647e-13</v>
       </c>
       <c r="AB21" t="n">
-        <v>-119.8844950930915</v>
+        <v>-119.8844950930664</v>
       </c>
       <c r="AC21" t="n">
-        <v>119.8844950931384</v>
+        <v>119.8844950931172</v>
       </c>
       <c r="AD21" t="n">
-        <v>179.9999999999999</v>
+        <v>180.0000000000001</v>
       </c>
       <c r="AE21" t="n">
-        <v>13.24983693095458</v>
+        <v>13.2498369309509</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.24983693094634</v>
+        <v>13.2498369309421</v>
       </c>
       <c r="AG21" t="n">
-        <v>-8.506228303696583e-12</v>
+        <v>6.298268134835391e-13</v>
       </c>
       <c r="AH21" t="n">
         <v>-27374.66294019669</v>
       </c>
       <c r="AI21" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>2.110027708113194e-10</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-1.627086021471769e-09</v>
+        <v>1.886292011477053e-09</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.524203068787756e-11</v>
+        <v>-1.63424829224823e-12</v>
       </c>
       <c r="AL21" t="n">
-        <v>-14707.31899334175</v>
+        <v>-14707.3189933558</v>
       </c>
       <c r="AM21" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
       <c r="AN21" t="n">
         <v>27374.66294019669</v>
       </c>
       <c r="AO21" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-2.110027708113194e-10</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.627086021471769e-09</v>
+        <v>-1.886292011477053e-09</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-2.524203068787756e-11</v>
+        <v>1.63424829224823e-12</v>
       </c>
       <c r="AR21" t="n">
-        <v>14707.31899335478</v>
+        <v>14707.31899334072</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>8.440110832452774e-10</v>
       </c>
     </row>
     <row r="22">
@@ -6780,115 +6780,115 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086895</v>
+        <v>-6001954935.086894</v>
       </c>
       <c r="J22" t="n">
-        <v>120.039098701767</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="K22" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="L22" t="n">
+        <v>-360.0000000000002</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.917176071110052</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-2.917176071118671</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.822148453449026e-12</v>
+      </c>
+      <c r="P22" t="n">
+        <v>120.0390987017214</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-120.0390987016426</v>
+      </c>
+      <c r="R22" t="n">
         <v>-359.9999999999998</v>
       </c>
-      <c r="M22" t="n">
-        <v>2.917176071107192</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-2.917176071114491</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.209591840121953e-11</v>
-      </c>
-      <c r="P22" t="n">
-        <v>120.0390987015889</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-120.0390987015913</v>
-      </c>
-      <c r="R22" t="n">
-        <v>-360.0000000000005</v>
-      </c>
       <c r="S22" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="U22" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="V22" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="W22" t="n">
-        <v>-120.039098701767</v>
+        <v>-120.0390987017059</v>
       </c>
       <c r="X22" t="n">
+        <v>-360.0000000000002</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-2.917176071118671</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-2.917176071110052</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-1.822148453449026e-12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-120.0390987016426</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-120.0390987017214</v>
+      </c>
+      <c r="AD22" t="n">
         <v>-359.9999999999998</v>
       </c>
-      <c r="Y22" t="n">
-        <v>-2.917176071114491</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>-2.917176071107192</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.209591840121953e-11</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-120.0390987015913</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>-120.0390987015889</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>-360.0000000000005</v>
-      </c>
       <c r="AE22" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071123615</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="AH22" t="n">
-        <v>9266.392311882228</v>
+        <v>9266.392311878502</v>
       </c>
       <c r="AI22" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>9.640643838793039e-11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-7.940798241179436e-09</v>
+        <v>-5.697074811905622e-09</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.044675622732029e-11</v>
+        <v>-5.53335155473178e-13</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3238.065438907926</v>
+        <v>-3238.065438916907</v>
       </c>
       <c r="AM22" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>4.001776687800884e-10</v>
       </c>
       <c r="AN22" t="n">
-        <v>-9266.392311882228</v>
+        <v>-9266.392311878502</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>-9.640643838793039e-11</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.940798241179436e-09</v>
+        <v>5.697074811905622e-09</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-3.044675622732029e-11</v>
+        <v>5.53335155473178e-13</v>
       </c>
       <c r="AR22" t="n">
-        <v>3238.065438971422</v>
+        <v>3238.065438962483</v>
       </c>
       <c r="AS22" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>3.783497959375381e-10</v>
       </c>
     </row>
     <row r="23">
@@ -6922,112 +6922,112 @@
         <v>-6001954935.086895</v>
       </c>
       <c r="J23" t="n">
-        <v>120.0390987015889</v>
+        <v>120.0390987017214</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="L23" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="O23" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="P23" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="Q23" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="R23" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="T23" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="U23" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="V23" t="n">
-        <v>120.0390987015889</v>
+        <v>120.0390987017214</v>
       </c>
       <c r="W23" t="n">
-        <v>-120.0390987015913</v>
+        <v>-120.0390987016426</v>
       </c>
       <c r="X23" t="n">
-        <v>-360.0000000000005</v>
+        <v>-359.9999999999998</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071123615</v>
       </c>
       <c r="Z23" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071118412</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>-1.838581571782945e-12</v>
       </c>
       <c r="AB23" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="AC23" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="AD23" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="AE23" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="AH23" t="n">
         <v>9266.392311885953</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.473381416872144e-10</v>
+        <v>-1.01863406598568e-10</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.896666597342119e-09</v>
+        <v>1.280568540096283e-09</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.933653320269514e-11</v>
+        <v>-4.352962434950314e-12</v>
       </c>
       <c r="AL23" t="n">
-        <v>-3238.065438979261</v>
+        <v>-3238.065438944817</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>-4.220055416226387e-10</v>
       </c>
       <c r="AN23" t="n">
         <v>-9266.392311885953</v>
       </c>
       <c r="AO23" t="n">
-        <v>-1.473381416872144e-10</v>
+        <v>1.01863406598568e-10</v>
       </c>
       <c r="AP23" t="n">
-        <v>-9.896666597342119e-09</v>
+        <v>-1.280568540096283e-09</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-2.933653320269514e-11</v>
+        <v>4.352962434950314e-12</v>
       </c>
       <c r="AR23" t="n">
-        <v>3238.065438900087</v>
+        <v>3238.065438934573</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>-3.856257535517216e-10</v>
       </c>
     </row>
     <row r="24">
@@ -7058,115 +7058,115 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086894</v>
+        <v>-6001954935.086895</v>
       </c>
       <c r="J24" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.0390987014159</v>
+        <v>-120.0390987016563</v>
       </c>
       <c r="L24" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="N24" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071115255</v>
       </c>
       <c r="O24" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="P24" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="Q24" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="R24" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="S24" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="T24" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="U24" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="V24" t="n">
-        <v>120.0390987014159</v>
+        <v>120.0390987016563</v>
       </c>
       <c r="W24" t="n">
-        <v>-120.039098701887</v>
+        <v>-120.0390987017544</v>
       </c>
       <c r="X24" t="n">
-        <v>-360.0000000000001</v>
+        <v>-359.9999999999994</v>
       </c>
       <c r="Y24" t="n">
-        <v>-2.917176071104874</v>
+        <v>-2.917176071115255</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071121575</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>-1.804880584799103e-12</v>
       </c>
       <c r="AB24" t="n">
-        <v>-120.0390987020598</v>
+        <v>-120.0390987018195</v>
       </c>
       <c r="AC24" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="AD24" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="AE24" t="n">
-        <v>-2.917176071119162</v>
+        <v>-2.917176071114994</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="AH24" t="n">
-        <v>9266.392311878502</v>
+        <v>9266.392311882228</v>
       </c>
       <c r="AI24" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>1.036823960021138e-10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.939906724146567e-08</v>
+        <v>4.009052645415068e-09</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.04991587540826e-11</v>
+        <v>-5.568878691519785e-13</v>
       </c>
       <c r="AL24" t="n">
-        <v>-3238.065439017271</v>
+        <v>-3238.065438955702</v>
       </c>
       <c r="AM24" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>4.292814992368221e-10</v>
       </c>
       <c r="AN24" t="n">
-        <v>-9266.392311878502</v>
+        <v>-9266.392311882228</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>-1.036823960021138e-10</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1.939906724146567e-08</v>
+        <v>-4.009052645415068e-09</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-3.04991587540826e-11</v>
+        <v>5.568878691519785e-13</v>
       </c>
       <c r="AR24" t="n">
-        <v>3238.065438862105</v>
+        <v>3238.065438923659</v>
       </c>
       <c r="AS24" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>4.074536263942719e-10</v>
       </c>
     </row>
     <row r="25">
@@ -7197,115 +7197,115 @@
         <v>-28449266.39231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086894</v>
+        <v>-6001954935.086895</v>
       </c>
       <c r="J25" t="n">
-        <v>-120.0390987017087</v>
+        <v>-120.0390987017699</v>
       </c>
       <c r="K25" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="L25" t="n">
-        <v>-359.9999999999997</v>
+        <v>-360</v>
       </c>
       <c r="M25" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071112084</v>
       </c>
       <c r="N25" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="O25" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>-1.825339387183125e-12</v>
       </c>
       <c r="P25" t="n">
-        <v>120.039098701767</v>
+        <v>120.0390987017059</v>
       </c>
       <c r="Q25" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="R25" t="n">
-        <v>-359.9999999999998</v>
+        <v>-360.0000000000002</v>
       </c>
       <c r="S25" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071110052</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="U25" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>-1.822148453449026e-12</v>
       </c>
       <c r="V25" t="n">
-        <v>120.0390987017087</v>
+        <v>120.0390987017699</v>
       </c>
       <c r="W25" t="n">
-        <v>120.0390987020598</v>
+        <v>120.0390987018195</v>
       </c>
       <c r="X25" t="n">
-        <v>359.9999999999997</v>
+        <v>360</v>
       </c>
       <c r="Y25" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071112084</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071114994</v>
       </c>
       <c r="AA25" t="n">
-        <v>-2.210527673673511e-11</v>
+        <v>1.825339387183125e-12</v>
       </c>
       <c r="AB25" t="n">
-        <v>-120.039098701767</v>
+        <v>-120.0390987017059</v>
       </c>
       <c r="AC25" t="n">
-        <v>120.0390987018845</v>
+        <v>120.0390987018331</v>
       </c>
       <c r="AD25" t="n">
-        <v>359.9999999999998</v>
+        <v>360.0000000000002</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071110052</v>
       </c>
       <c r="AF25" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071118671</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.209591840121953e-11</v>
+        <v>1.822148453449026e-12</v>
       </c>
       <c r="AH25" t="n">
-        <v>9266.392311878502</v>
+        <v>9266.392311882228</v>
       </c>
       <c r="AI25" t="n">
-        <v>-1.491571310907602e-10</v>
+        <v>1.073203748092055e-10</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-1.949956640601158e-09</v>
+        <v>1.506123226135969e-09</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.923972175494782e-11</v>
+        <v>-4.338751580235112e-12</v>
       </c>
       <c r="AL25" t="n">
-        <v>3238.065438947485</v>
+        <v>3238.065438933641</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.111804395914078e-10</v>
+        <v>4.292814992368221e-10</v>
       </c>
       <c r="AN25" t="n">
-        <v>-9266.392311878502</v>
+        <v>-9266.392311882228</v>
       </c>
       <c r="AO25" t="n">
-        <v>1.491571310907602e-10</v>
+        <v>-1.073203748092055e-10</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.949956640601158e-09</v>
+        <v>-1.506123226135969e-09</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-2.923972175494782e-11</v>
+        <v>4.338751580235112e-12</v>
       </c>
       <c r="AR25" t="n">
-        <v>-3238.065438931885</v>
+        <v>-3238.06543894572</v>
       </c>
       <c r="AS25" t="n">
-        <v>-5.966285243630409e-10</v>
+        <v>4.220055416226387e-10</v>
       </c>
     </row>
     <row r="26">
@@ -7333,118 +7333,118 @@
         <v>-29.99792379152159</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436247</v>
+        <v>-28438031.75436246</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304318</v>
+        <v>-5999584758.304317</v>
       </c>
       <c r="J26" t="n">
-        <v>119.9916951661322</v>
+        <v>119.9916951660409</v>
       </c>
       <c r="K26" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="L26" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-0.6603494433671542</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="O26" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="P26" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="Q26" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="R26" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="U26" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="V26" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="W26" t="n">
-        <v>-119.9916951661322</v>
+        <v>-119.9916951660409</v>
       </c>
       <c r="X26" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6603494433687225</v>
+        <v>0.6603494433671542</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="AB26" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="AC26" t="n">
-        <v>-119.9916951658417</v>
+        <v>-119.9916951660554</v>
       </c>
       <c r="AD26" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-0.6603494433610113</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1968.245637528598</v>
+        <v>-1968.245637536049</v>
       </c>
       <c r="AI26" t="n">
-        <v>-9.094947017729282e-11</v>
+        <v>-1.153239281848073e-09</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-3.78480535800918e-09</v>
+        <v>-2.65572452917695e-09</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.237432461527078e-11</v>
+        <v>-1.999733711954832e-12</v>
       </c>
       <c r="AL26" t="n">
-        <v>732.9878821492639</v>
+        <v>732.9878821447492</v>
       </c>
       <c r="AM26" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
       <c r="AN26" t="n">
-        <v>1968.245637528598</v>
+        <v>1968.245637536049</v>
       </c>
       <c r="AO26" t="n">
-        <v>9.094947017729282e-11</v>
+        <v>1.153239281848073e-09</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.78480535800918e-09</v>
+        <v>2.65572452917695e-09</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-2.237432461527078e-11</v>
+        <v>1.999733711954832e-12</v>
       </c>
       <c r="AR26" t="n">
-        <v>-732.987882118985</v>
+        <v>-732.9878821235034</v>
       </c>
       <c r="AS26" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321727</v>
+        <v>-239.9833903321726</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152159</v>
+        <v>-29.99792379152158</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436247</v>
+        <v>-28438031.75436246</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304318</v>
+        <v>-5999584758.304316</v>
       </c>
       <c r="J27" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="L27" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="O27" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="P27" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="Q27" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="R27" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="S27" t="n">
-        <v>0.660349443347221</v>
+        <v>0.6603494433643113</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="U27" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="V27" t="n">
-        <v>119.9916951658417</v>
+        <v>119.9916951660554</v>
       </c>
       <c r="W27" t="n">
-        <v>-119.9916951658776</v>
+        <v>-119.9916951659443</v>
       </c>
       <c r="X27" t="n">
-        <v>-540.0000000000006</v>
+        <v>-539.9999999999995</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.6603494433594336</v>
+        <v>0.6603494433610113</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.6603494433538359</v>
+        <v>0.6603494433624342</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>-3.202814053526971e-12</v>
       </c>
       <c r="AB27" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="AC27" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="AD27" t="n">
-        <v>-540.0000000000001</v>
+        <v>-539.9999999999993</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.660349443347221</v>
+        <v>0.6603494433643113</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.660349443374319</v>
+        <v>-0.660349443365725</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>-3.218484248254603e-12</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1968.245637528598</v>
+        <v>-1968.245637543499</v>
       </c>
       <c r="AI27" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>1.142325345426798e-09</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8.479389634885592e-09</v>
+        <v>1.346052158623934e-09</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.60691468412233e-11</v>
+        <v>-7.044365091246618e-12</v>
       </c>
       <c r="AL27" t="n">
-        <v>732.987882100203</v>
+        <v>732.9878821287421</v>
       </c>
       <c r="AM27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>4.583853296935558e-09</v>
       </c>
       <c r="AN27" t="n">
-        <v>1968.245637528598</v>
+        <v>1968.245637543499</v>
       </c>
       <c r="AO27" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-1.142325345426798e-09</v>
       </c>
       <c r="AP27" t="n">
-        <v>-8.479389634885592e-09</v>
+        <v>-1.346052158623934e-09</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-2.60691468412233e-11</v>
+        <v>7.044365091246618e-12</v>
       </c>
       <c r="AR27" t="n">
-        <v>-732.9878821680668</v>
+        <v>-732.9878821395105</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>4.562025424093008e-09</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321726</v>
+        <v>-239.9833903321727</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152158</v>
+        <v>-29.99792379152159</v>
       </c>
       <c r="H28" t="n">
         <v>-28438031.75436246</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304316</v>
+        <v>-5999584758.304317</v>
       </c>
       <c r="J28" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="K28" t="n">
-        <v>-119.9916951655889</v>
+        <v>-119.991695165981</v>
       </c>
       <c r="L28" t="n">
+        <v>-539.9999999999993</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.6603494433643113</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.660349443365725</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-3.218484248254603e-12</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-119.9916951661319</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>119.9916951661917</v>
+      </c>
+      <c r="R28" t="n">
         <v>-540.0000000000001</v>
       </c>
-      <c r="M28" t="n">
-        <v>0.660349443347221</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-0.660349443374319</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.620102839067906e-11</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-119.9916951660405</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>119.9916951665838</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-539.9999999999998</v>
-      </c>
       <c r="S28" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="U28" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="V28" t="n">
-        <v>119.9916951655889</v>
+        <v>119.991695165981</v>
       </c>
       <c r="W28" t="n">
-        <v>-119.991695166331</v>
+        <v>-119.9916951661173</v>
       </c>
       <c r="X28" t="n">
+        <v>-539.9999999999993</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.660349443365725</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.6603494433643113</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-3.218484248254603e-12</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-119.9916951661917</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-119.9916951661319</v>
+      </c>
+      <c r="AD28" t="n">
         <v>-540.0000000000001</v>
       </c>
-      <c r="Y28" t="n">
-        <v>0.660349443374319</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0.660349443347221</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.620102839067906e-11</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>-119.9916951665838</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>-119.9916951660405</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>-539.9999999999998</v>
-      </c>
       <c r="AE28" t="n">
-        <v>0.6603494433638434</v>
+        <v>0.6603494433666658</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1968.245637543499</v>
+        <v>-1968.245637536049</v>
       </c>
       <c r="AI28" t="n">
-        <v>-8.913048077374697e-11</v>
+        <v>-1.144144334830344e-09</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.400917426508386e-08</v>
+        <v>-1.091393642127514e-10</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.236144602818513e-11</v>
+        <v>-2.008393451546908e-12</v>
       </c>
       <c r="AL28" t="n">
-        <v>732.9878820781033</v>
+        <v>732.9878821345628</v>
       </c>
       <c r="AM28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.591129254549742e-09</v>
       </c>
       <c r="AN28" t="n">
-        <v>1968.245637543499</v>
+        <v>1968.245637536049</v>
       </c>
       <c r="AO28" t="n">
-        <v>8.913048077374697e-11</v>
+        <v>1.144144334830344e-09</v>
       </c>
       <c r="AP28" t="n">
-        <v>-1.400917426508386e-08</v>
+        <v>1.091393642127514e-10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-2.236144602818513e-11</v>
+        <v>2.008393451546908e-12</v>
       </c>
       <c r="AR28" t="n">
-        <v>-732.9878821901764</v>
+        <v>-732.9878821336897</v>
       </c>
       <c r="AS28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-4.562025424093008e-09</v>
       </c>
     </row>
     <row r="29">
@@ -7753,115 +7753,115 @@
         <v>-28438031.75436247</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304317</v>
+        <v>-5999584758.304318</v>
       </c>
       <c r="J29" t="n">
-        <v>-119.9916951660405</v>
+        <v>-119.9916951661319</v>
       </c>
       <c r="K29" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="L29" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-0.6603494433638429</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="O29" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>-3.191754473673499e-12</v>
       </c>
       <c r="P29" t="n">
-        <v>119.9916951661322</v>
+        <v>119.9916951660409</v>
       </c>
       <c r="Q29" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="R29" t="n">
-        <v>-539.9999999999998</v>
+        <v>-540.0000000000005</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-0.6603494433671542</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="U29" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>-3.202095367613299e-12</v>
       </c>
       <c r="V29" t="n">
-        <v>119.9916951660405</v>
+        <v>119.9916951661319</v>
       </c>
       <c r="W29" t="n">
-        <v>119.9916951665838</v>
+        <v>119.9916951661917</v>
       </c>
       <c r="X29" t="n">
-        <v>539.9999999999998</v>
+        <v>540.0000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6603494433809615</v>
+        <v>0.6603494433638429</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-0.6603494433666658</v>
       </c>
       <c r="AA29" t="n">
-        <v>-3.620069469507619e-11</v>
+        <v>3.191754473673499e-12</v>
       </c>
       <c r="AB29" t="n">
-        <v>-119.9916951661322</v>
+        <v>-119.9916951660409</v>
       </c>
       <c r="AC29" t="n">
-        <v>119.9916951662951</v>
+        <v>119.9916951662284</v>
       </c>
       <c r="AD29" t="n">
-        <v>539.9999999999998</v>
+        <v>540.0000000000005</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.6603494433687225</v>
+        <v>0.6603494433671542</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6603494433643176</v>
+        <v>0.6603494433614974</v>
       </c>
       <c r="AG29" t="n">
-        <v>-3.618836610953347e-11</v>
+        <v>3.202095367613299e-12</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1968.245637532324</v>
+        <v>-1968.245637528598</v>
       </c>
       <c r="AI29" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-1.153239281848073e-09</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-1.980993147299159e-10</v>
+        <v>2.117303665727377e-09</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.612554617087426e-11</v>
+        <v>-7.068345908578522e-12</v>
       </c>
       <c r="AL29" t="n">
-        <v>-732.9878821333361</v>
+        <v>-732.9878821425955</v>
       </c>
       <c r="AM29" t="n">
-        <v>-4.001776687800884e-10</v>
+        <v>-4.612957127392292e-09</v>
       </c>
       <c r="AN29" t="n">
-        <v>1968.245637532324</v>
+        <v>1968.245637528598</v>
       </c>
       <c r="AO29" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>1.153239281848073e-09</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.980993147299159e-10</v>
+        <v>-2.117303665727377e-09</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-2.612554617087426e-11</v>
+        <v>7.068345908578522e-12</v>
       </c>
       <c r="AR29" t="n">
-        <v>732.9878821349207</v>
+        <v>732.9878821256571</v>
       </c>
       <c r="AS29" t="n">
-        <v>-3.92901711165905e-10</v>
+        <v>-4.605681169778109e-09</v>
       </c>
     </row>
     <row r="30">
@@ -7886,121 +7886,121 @@
         <v>-240.0026150785242</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481552</v>
+        <v>-30.00032688481553</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680511</v>
+        <v>-28440309.88680512</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963103</v>
+        <v>-6000065376.963104</v>
       </c>
       <c r="J30" t="n">
-        <v>120.001307539296</v>
+        <v>120.0013075391888</v>
       </c>
       <c r="K30" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="L30" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2383793660995245</v>
+        <v>0.2383793661006169</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="O30" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="P30" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075392201</v>
       </c>
       <c r="Q30" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="R30" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-0.2383793661002568</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="U30" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="V30" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="W30" t="n">
-        <v>-120.001307539296</v>
+        <v>-120.0013075391888</v>
       </c>
       <c r="X30" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-0.2383793661006169</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="AB30" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="AC30" t="n">
-        <v>-120.0013075389503</v>
+        <v>-120.0013075392201</v>
       </c>
       <c r="AD30" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2383793661013374</v>
+        <v>0.2383793661002568</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="AH30" t="n">
         <v>309.8868051171303</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.205989974550903e-09</v>
+        <v>-1.702574081718922e-09</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-6.750866532456712e-10</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="AK30" t="n">
-        <v>8.726019906646343e-12</v>
+        <v>-3.771205570046732e-12</v>
       </c>
       <c r="AL30" t="n">
-        <v>-264.6010963687289</v>
+        <v>-264.6010963714798</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.823959898203611e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
       <c r="AN30" t="n">
         <v>-309.8868051171303</v>
       </c>
       <c r="AO30" t="n">
-        <v>-1.205989974550903e-09</v>
+        <v>1.702574081718922e-09</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.750866532456712e-10</v>
+        <v>-1.455191522836685e-11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-8.726019906646343e-12</v>
+        <v>3.771205570046732e-12</v>
       </c>
       <c r="AR30" t="n">
-        <v>264.6010963741877</v>
+        <v>264.6010963714798</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-6.803020369261503e-09</v>
       </c>
     </row>
     <row r="31">
@@ -8022,7 +8022,7 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785243</v>
+        <v>-240.0026150785242</v>
       </c>
       <c r="G31" t="n">
         <v>-30.00032688481553</v>
@@ -8031,115 +8031,115 @@
         <v>-28440309.88680512</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963106</v>
+        <v>-6000065376.963105</v>
       </c>
       <c r="J31" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075392201</v>
       </c>
       <c r="K31" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="L31" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-0.2383793661002568</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="O31" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="P31" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="Q31" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="R31" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="U31" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="V31" t="n">
-        <v>120.0013075389503</v>
+        <v>120.0013075392201</v>
       </c>
       <c r="W31" t="n">
-        <v>-120.0013075390368</v>
+        <v>-120.0013075391147</v>
       </c>
       <c r="X31" t="n">
-        <v>-720.0000000000006</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-0.2383793661002568</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-0.2383793661013742</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>-5.950374488726812e-12</v>
       </c>
       <c r="AB31" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="AC31" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="AD31" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="AH31" t="n">
-        <v>309.8868051245809</v>
+        <v>309.8868051208556</v>
       </c>
       <c r="AI31" t="n">
-        <v>-1.218722900375724e-09</v>
+        <v>1.709850039333105e-09</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.557804800242593e-09</v>
+        <v>7.712515071034431e-10</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.397171267569774e-11</v>
+        <v>-5.13833420257015e-12</v>
       </c>
       <c r="AL31" t="n">
-        <v>-264.601096389707</v>
+        <v>-264.6010963745648</v>
       </c>
       <c r="AM31" t="n">
-        <v>-4.874891601502895e-09</v>
+        <v>6.83940015733242e-09</v>
       </c>
       <c r="AN31" t="n">
-        <v>-309.8868051245809</v>
+        <v>-309.8868051208556</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.218722900375724e-09</v>
+        <v>-1.709850039333105e-09</v>
       </c>
       <c r="AP31" t="n">
-        <v>-4.557804800242593e-09</v>
+        <v>-7.712515071034431e-10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-1.397171267569774e-11</v>
+        <v>5.13833420257015e-12</v>
       </c>
       <c r="AR31" t="n">
-        <v>264.6010963532444</v>
+        <v>264.6010963683948</v>
       </c>
       <c r="AS31" t="n">
-        <v>-4.867615643888712e-09</v>
+        <v>6.83940015733242e-09</v>
       </c>
     </row>
     <row r="32">
@@ -8173,112 +8173,112 @@
         <v>-6000065376.963105</v>
       </c>
       <c r="J32" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="K32" t="n">
-        <v>-120.0013075386678</v>
+        <v>-120.0013075391787</v>
       </c>
       <c r="L32" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2383793660949187</v>
+        <v>0.2383793660995157</v>
       </c>
       <c r="O32" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="P32" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="R32" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="S32" t="n">
-        <v>0.238379366093001</v>
+        <v>0.2383793661030328</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="U32" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="V32" t="n">
-        <v>120.0013075386678</v>
+        <v>120.0013075391787</v>
       </c>
       <c r="W32" t="n">
-        <v>-120.0013075395739</v>
+        <v>-120.0013075393042</v>
       </c>
       <c r="X32" t="n">
-        <v>-720.0000000000001</v>
+        <v>-719.9999999999993</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.2383793660949187</v>
+        <v>-0.2383793660995157</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-0.2383793660978497</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>-5.953210351365886e-12</v>
       </c>
       <c r="AB32" t="n">
-        <v>-120.0013075398565</v>
+        <v>-120.0013075393455</v>
       </c>
       <c r="AC32" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="AD32" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.2383793660989685</v>
+        <v>-0.238379366097723</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.238379366093001</v>
+        <v>0.2383793661030328</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="AH32" t="n">
-        <v>309.8868051208556</v>
+        <v>309.8868051245809</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.207808963954449e-09</v>
+        <v>-1.704393071122468e-09</v>
       </c>
       <c r="AJ32" t="n">
-        <v>6.185530310176546e-09</v>
+        <v>-2.066371962428093e-09</v>
       </c>
       <c r="AK32" t="n">
-        <v>8.644529536638856e-12</v>
+        <v>-3.82671672127799e-12</v>
       </c>
       <c r="AL32" t="n">
-        <v>-264.6010963962013</v>
+        <v>-264.6010963632143</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.838511813431978e-09</v>
+        <v>-6.81757228448987e-09</v>
       </c>
       <c r="AN32" t="n">
-        <v>-309.8868051208556</v>
+        <v>-309.8868051245809</v>
       </c>
       <c r="AO32" t="n">
-        <v>-1.207808963954449e-09</v>
+        <v>1.704393071122468e-09</v>
       </c>
       <c r="AP32" t="n">
-        <v>-6.185530310176546e-09</v>
+        <v>2.066371962428093e-09</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-8.644529536638856e-12</v>
+        <v>3.82671672127799e-12</v>
       </c>
       <c r="AR32" t="n">
-        <v>264.6010963467751</v>
+        <v>264.6010963797453</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-6.824848242104053e-09</v>
       </c>
     </row>
     <row r="33">
@@ -8309,115 +8309,115 @@
         <v>-28440309.88680512</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963105</v>
+        <v>-6000065376.963104</v>
       </c>
       <c r="J33" t="n">
-        <v>-120.0013075392282</v>
+        <v>-120.0013075393354</v>
       </c>
       <c r="K33" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="L33" t="n">
-        <v>-720</v>
+        <v>-720.0000000000002</v>
       </c>
       <c r="M33" t="n">
-        <v>0.238379366093001</v>
+        <v>0.2383793661030328</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="O33" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>-5.95367299120638e-12</v>
       </c>
       <c r="P33" t="n">
-        <v>120.001307539296</v>
+        <v>120.0013075391888</v>
       </c>
       <c r="Q33" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="R33" t="n">
-        <v>-719.9999999999999</v>
+        <v>-720.0000000000007</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2383793660995245</v>
+        <v>0.2383793661006169</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="U33" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>-5.954773371978419e-12</v>
       </c>
       <c r="V33" t="n">
-        <v>120.0013075392282</v>
+        <v>120.0013075393354</v>
       </c>
       <c r="W33" t="n">
-        <v>120.0013075398565</v>
+        <v>120.0013075393455</v>
       </c>
       <c r="X33" t="n">
-        <v>720</v>
+        <v>720.0000000000002</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.238379366093001</v>
+        <v>-0.2383793661030328</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2383793660989685</v>
+        <v>0.238379366097723</v>
       </c>
       <c r="AA33" t="n">
-        <v>-4.466611131288079e-11</v>
+        <v>5.95367299120638e-12</v>
       </c>
       <c r="AB33" t="n">
-        <v>-120.001307539296</v>
+        <v>-120.0013075391888</v>
       </c>
       <c r="AC33" t="n">
-        <v>120.0013075394874</v>
+        <v>120.0013075394095</v>
       </c>
       <c r="AD33" t="n">
-        <v>719.9999999999999</v>
+        <v>720.0000000000007</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-0.2383793661006169</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-0.2383793661031409</v>
       </c>
       <c r="AG33" t="n">
-        <v>-4.465776835261449e-11</v>
+        <v>5.954773371978419e-12</v>
       </c>
       <c r="AH33" t="n">
         <v>309.8868051171303</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.229636836796999e-09</v>
+        <v>-1.702574081718922e-09</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.223313006448734e-09</v>
+        <v>2.197339199483395e-09</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.392519433096595e-11</v>
+        <v>-5.157096971686315e-12</v>
       </c>
       <c r="AL33" t="n">
-        <v>264.6010963665491</v>
+        <v>264.6010963626322</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.911271389573812e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
       <c r="AN33" t="n">
         <v>-309.8868051171303</v>
       </c>
       <c r="AO33" t="n">
-        <v>-1.229636836796999e-09</v>
+        <v>1.702574081718922e-09</v>
       </c>
       <c r="AP33" t="n">
-        <v>-1.223313006448734e-09</v>
+        <v>-2.197339199483395e-09</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-1.392519433096595e-11</v>
+        <v>5.157096971686315e-12</v>
       </c>
       <c r="AR33" t="n">
-        <v>-264.6010963763936</v>
+        <v>-264.6010963802692</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.918547347187996e-09</v>
+        <v>-6.810296326875687e-09</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_temperature.xlsx
+++ b/outputs/validation_frame_temperature.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>119.8844950930915</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="F6" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="G6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="H6" t="n">
-        <v>-13.24983693095458</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="I6" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="J6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="K6" t="n">
-        <v>247.2743098816821</v>
+        <v>0.002472743098815779</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="F7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="G7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="H7" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="I7" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="J7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>247.2743098815926</v>
+        <v>0.002472743098816677</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="F8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="G8" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="I8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="J8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="K8" t="n">
-        <v>247.2743098816123</v>
+        <v>0.002472743098817284</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="F9" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="G9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="J9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="K9" t="n">
-        <v>247.2743098817037</v>
+        <v>0.00247274309881617</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>120.039098701767</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="F10" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="G10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="K10" t="n">
-        <v>398.0185553894356</v>
+        <v>0.003980185553892722</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="F11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="G11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>398.0185553892941</v>
+        <v>0.003980185553894126</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="F12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="G12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>398.0185553893306</v>
+        <v>0.003980185553895161</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="F13" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="G13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>398.0185553894707</v>
+        <v>0.003980185553893303</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>119.9916951661322</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="F14" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="G14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>566.0353467918085</v>
+        <v>0.005660353467916279</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="F15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="G15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="K15" t="n">
-        <v>566.0353467916591</v>
+        <v>0.005660353467917999</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="F16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="G16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="H16" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="K16" t="n">
-        <v>566.0353467917012</v>
+        <v>0.005660353467918954</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="F17" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="G17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>566.0353467918502</v>
+        <v>0.00566035346791696</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>120.001307539296</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="F18" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="G18" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2383793660995245</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>739.7301045802632</v>
+        <v>0.007397301045800966</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>120.0013075389503</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="F19" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="G19" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="K19" t="n">
-        <v>739.7301045801347</v>
+        <v>0.007397301045802761</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="F20" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="G20" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="J20" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="K20" t="n">
-        <v>739.7301045801756</v>
+        <v>0.007397301045803481</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="F21" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="G21" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="H21" t="n">
-        <v>0.238379366093001</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>739.7301045803122</v>
+        <v>0.007397301045801653</v>
       </c>
     </row>
   </sheetData>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>739.7301045803122</v>
+        <v>0.007397301045803481</v>
       </c>
       <c r="D2" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="E2" t="n">
-        <v>120.0013075398565</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="F2" t="n">
-        <v>-720</v>
+        <v>-0.00719999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1267,16 +1267,16 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="D3" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="E3" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="F3" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0390987020598</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="D4" t="n">
-        <v>-120.0390987017087</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="E4" t="n">
-        <v>120.0390987020598</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="F4" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.003599999999999991</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0013075389503</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="E5" t="n">
-        <v>-120.0013075390368</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="F5" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007200000000000015</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="C2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>69104.76771110963</v>
+        <v>0.6910476771102511</v>
       </c>
       <c r="F2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>-1.227948388079732e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="C3" t="n">
-        <v>19766.62946072038</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="D3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="E3" t="n">
-        <v>-69104.76771105242</v>
+        <v>-0.6910476771113704</v>
       </c>
       <c r="F3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>-1.232406124819545e-16</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>19766.62946073354</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="C4" t="n">
-        <v>19766.62946071211</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="D4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="E4" t="n">
-        <v>-69104.76771101885</v>
+        <v>-0.6910476771112495</v>
       </c>
       <c r="F4" t="n">
-        <v>69104.76771110686</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>-1.231034558950431e-16</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>19766.62946072584</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="C5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="E5" t="n">
-        <v>69104.76771114318</v>
+        <v>0.6910476771103716</v>
       </c>
       <c r="F5" t="n">
-        <v>69104.76771107491</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>-1.233893320291097e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G2" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000009</v>
       </c>
       <c r="H2" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I2" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="L2" t="n">
-        <v>19766.62946072896</v>
+        <v>0.1976662946072387</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>-1.227948388079732e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="O2" t="n">
-        <v>-69104.76771110963</v>
+        <v>-0.6910476771102511</v>
       </c>
       <c r="P2" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="Q2" t="n">
-        <v>19766.62946073442</v>
+        <v>0.1976662946071376</v>
       </c>
       <c r="R2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="S2" t="n">
-        <v>2.421003440282873e-11</v>
+        <v>1.227948388079732e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-49495.00905328659</v>
+        <v>-0.4949500905327627</v>
       </c>
       <c r="U2" t="n">
-        <v>-49495.00905329685</v>
+        <v>-0.4949500905325742</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-30.00000000000005</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H3" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I3" t="n">
-        <v>-6000000000.00001</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>19766.62946072038</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="L3" t="n">
-        <v>19766.62946072127</v>
+        <v>0.1976662946071929</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>-1.232406124819545e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="O3" t="n">
-        <v>69104.76771105242</v>
+        <v>0.6910476771113704</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="Q3" t="n">
-        <v>-19766.62946072038</v>
+        <v>-0.1976662946074107</v>
       </c>
       <c r="R3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="S3" t="n">
-        <v>2.423009033885211e-11</v>
+        <v>1.232406124819545e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-49495.00905327238</v>
+        <v>-0.4949500905326924</v>
       </c>
       <c r="U3" t="n">
-        <v>49495.00905326986</v>
+        <v>0.4949500905330936</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H4" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I4" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="K4" t="n">
-        <v>19766.62946071211</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="L4" t="n">
-        <v>-19766.62946073354</v>
+        <v>-0.1976662946073556</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>-1.231034558950431e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>69104.76771110686</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="O4" t="n">
-        <v>69104.76771101885</v>
+        <v>0.6910476771112495</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="Q4" t="n">
-        <v>-19766.62946071211</v>
+        <v>-0.1976662946073792</v>
       </c>
       <c r="R4" t="n">
-        <v>19766.62946073354</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="S4" t="n">
-        <v>2.422151369217067e-11</v>
+        <v>1.231034558950431e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>49495.00905329436</v>
+        <v>0.4949500905329763</v>
       </c>
       <c r="U4" t="n">
-        <v>49495.00905325378</v>
+        <v>0.4949500905330254</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G5" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H5" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I5" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="K5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="L5" t="n">
-        <v>-19766.62946072584</v>
+        <v>-0.1976662946073095</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>-1.233893320291097e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>69104.76771107491</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="O5" t="n">
-        <v>-69104.76771114318</v>
+        <v>-0.6910476771103716</v>
       </c>
       <c r="P5" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="Q5" t="n">
-        <v>19766.62946074268</v>
+        <v>0.1976662946071689</v>
       </c>
       <c r="R5" t="n">
-        <v>19766.62946072584</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="S5" t="n">
-        <v>2.422188588688456e-11</v>
+        <v>1.233893320291097e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>49495.00905328012</v>
+        <v>0.494950090532905</v>
       </c>
       <c r="U5" t="n">
-        <v>-49495.0090533129</v>
+        <v>-0.494950090532642</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G6" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H6" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I6" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000015</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>7608.033479463036</v>
+        <v>0.07608033479482673</v>
       </c>
       <c r="L6" t="n">
-        <v>-7608.033479468945</v>
+        <v>-0.07608033479472942</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.867834873910378e-11</v>
+        <v>-2.119131582129195e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>34787.69005993183</v>
+        <v>0.3478769005994383</v>
       </c>
       <c r="O6" t="n">
-        <v>34787.69005991481</v>
+        <v>0.3478769005997626</v>
       </c>
       <c r="P6" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7608.033479463036</v>
+        <v>-0.07608033479482673</v>
       </c>
       <c r="R6" t="n">
-        <v>7608.033479468945</v>
+        <v>0.07608033479472942</v>
       </c>
       <c r="S6" t="n">
-        <v>3.867834873910378e-11</v>
+        <v>2.119131582129195e-16</v>
       </c>
       <c r="T6" t="n">
-        <v>10860.51081688182</v>
+        <v>0.1086051081689382</v>
       </c>
       <c r="U6" t="n">
-        <v>10860.51081686339</v>
+        <v>0.1086051081691977</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001799999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0002999999999999993</v>
       </c>
       <c r="H7" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.3999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>-6000000000.000008</v>
+        <v>-59999.99999999986</v>
       </c>
       <c r="J7" t="n">
-        <v>4.097819328308105e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="K7" t="n">
-        <v>-7608.033479476842</v>
+        <v>-0.07608033479457235</v>
       </c>
       <c r="L7" t="n">
-        <v>-7608.033479476904</v>
+        <v>-0.07608033479480569</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.867545858883965e-11</v>
+        <v>-2.115723902159476e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>34787.69005995742</v>
+        <v>0.3478769005996691</v>
       </c>
       <c r="O7" t="n">
-        <v>-34787.69005995538</v>
+        <v>-0.3478769005989404</v>
       </c>
       <c r="P7" t="n">
-        <v>-4.097819328308105e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="Q7" t="n">
-        <v>7608.033479476842</v>
+        <v>0.07608033479457235</v>
       </c>
       <c r="R7" t="n">
-        <v>7608.033479476904</v>
+        <v>0.07608033479480569</v>
       </c>
       <c r="S7" t="n">
-        <v>3.867545858883965e-11</v>
+        <v>2.115723902159476e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>10860.51081690402</v>
+        <v>0.1086051081691652</v>
       </c>
       <c r="U7" t="n">
-        <v>-10860.51081690566</v>
+        <v>-0.1086051081684936</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999996</v>
       </c>
       <c r="I8" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999991</v>
       </c>
       <c r="J8" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="K8" t="n">
-        <v>-7608.033479484184</v>
+        <v>-0.07608033479458301</v>
       </c>
       <c r="L8" t="n">
-        <v>7608.03347946298</v>
+        <v>0.07608033479459361</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.868580190546846e-11</v>
+        <v>-2.113669821224497e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>-34787.6900599128</v>
+        <v>-0.3478769005990348</v>
       </c>
       <c r="O8" t="n">
-        <v>-34787.69005997882</v>
+        <v>-0.3478769005989906</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="Q8" t="n">
-        <v>7608.033479484184</v>
+        <v>0.07608033479458301</v>
       </c>
       <c r="R8" t="n">
-        <v>-7608.03347946298</v>
+        <v>-0.07608033479459361</v>
       </c>
       <c r="S8" t="n">
-        <v>3.868580190546846e-11</v>
+        <v>2.113669821224497e-16</v>
       </c>
       <c r="T8" t="n">
-        <v>-10860.51081686508</v>
+        <v>-0.1086051081685271</v>
       </c>
       <c r="U8" t="n">
-        <v>-10860.51081692625</v>
+        <v>-0.1086051081685075</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G9" t="n">
-        <v>-29.99999999999997</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H9" t="n">
-        <v>-28439999.99999997</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999993</v>
+        <v>-60000.00000000016</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K9" t="n">
-        <v>7608.03347945568</v>
+        <v>0.07608033479481566</v>
       </c>
       <c r="L9" t="n">
-        <v>7608.033479470957</v>
+        <v>0.07608033479466958</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.869313251766919e-11</v>
+        <v>-2.114968923479162e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>-34787.69005993844</v>
+        <v>-0.3478769005992646</v>
       </c>
       <c r="O9" t="n">
-        <v>34787.69005989138</v>
+        <v>0.3478769005997115</v>
       </c>
       <c r="P9" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7608.03347945568</v>
+        <v>-0.07608033479481566</v>
       </c>
       <c r="R9" t="n">
-        <v>-7608.033479470957</v>
+        <v>-0.07608033479466958</v>
       </c>
       <c r="S9" t="n">
-        <v>3.869313251766919e-11</v>
+        <v>2.114968923479162e-16</v>
       </c>
       <c r="T9" t="n">
-        <v>-10860.51081688729</v>
+        <v>-0.1086051081687528</v>
       </c>
       <c r="U9" t="n">
-        <v>10860.51081684273</v>
+        <v>0.1086051081691825</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000003</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000</v>
+        <v>-60000.00000000005</v>
       </c>
       <c r="J10" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>-1658.358832414433</v>
+        <v>-0.01658358832394202</v>
       </c>
       <c r="L10" t="n">
-        <v>1658.358832411864</v>
+        <v>0.01658358832407774</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.010927424673966e-11</v>
+        <v>-2.077521622880486e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>-7622.445377949901</v>
+        <v>-0.07622445377939645</v>
       </c>
       <c r="O10" t="n">
-        <v>-7622.445377955475</v>
+        <v>-0.07622445377900067</v>
       </c>
       <c r="P10" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1658.358832414433</v>
+        <v>0.01658358832394202</v>
       </c>
       <c r="R10" t="n">
-        <v>-1658.358832411864</v>
+        <v>-0.01658358832407774</v>
       </c>
       <c r="S10" t="n">
-        <v>4.010927424673966e-11</v>
+        <v>2.077521622880486e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>-2327.707616521262</v>
+        <v>-0.02327707616506976</v>
       </c>
       <c r="U10" t="n">
-        <v>-2327.70761653113</v>
+        <v>-0.02327707616465158</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-30.00000000000001</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H11" t="n">
-        <v>-28440000.00000001</v>
+        <v>-284.3999999999995</v>
       </c>
       <c r="I11" t="n">
-        <v>-6000000000.000001</v>
+        <v>-59999.9999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>1658.358832404872</v>
+        <v>0.01658358832425133</v>
       </c>
       <c r="L11" t="n">
-        <v>1658.358832402486</v>
+        <v>0.01658358832403251</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.012493149746856e-11</v>
+        <v>-2.0804665930623e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>-7622.445377924581</v>
+        <v>-0.07622445377931243</v>
       </c>
       <c r="O11" t="n">
-        <v>7622.445377934186</v>
+        <v>0.07622445377989695</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1658.358832404872</v>
+        <v>-0.01658358832425133</v>
       </c>
       <c r="R11" t="n">
-        <v>-1658.358832402486</v>
+        <v>-0.01658358832403251</v>
       </c>
       <c r="S11" t="n">
-        <v>4.012493149746856e-11</v>
+        <v>2.0804665930623e-16</v>
       </c>
       <c r="T11" t="n">
-        <v>-2327.707616490355</v>
+        <v>-0.02327707616488241</v>
       </c>
       <c r="U11" t="n">
-        <v>2327.707616495056</v>
+        <v>0.02327707616561103</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001799999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-30.00000000000001</v>
+        <v>-0.0002999999999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>-28440000.00000001</v>
+        <v>-284.3999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>-6000000000.000001</v>
+        <v>-59999.99999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="K12" t="n">
-        <v>1658.358832396134</v>
+        <v>0.01658358832419271</v>
       </c>
       <c r="L12" t="n">
-        <v>-1658.358832416807</v>
+        <v>-0.01658358832416097</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.012638059121664e-11</v>
+        <v>-2.076096844797136e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>7622.445377965032</v>
+        <v>0.07622445377958545</v>
       </c>
       <c r="O12" t="n">
-        <v>7622.445377909098</v>
+        <v>0.07622445377971176</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1658.358832396134</v>
+        <v>-0.01658358832419271</v>
       </c>
       <c r="R12" t="n">
-        <v>1658.358832416807</v>
+        <v>0.01658358832416097</v>
       </c>
       <c r="S12" t="n">
-        <v>4.012638059121664e-11</v>
+        <v>2.076096844797136e-16</v>
       </c>
       <c r="T12" t="n">
-        <v>2327.707616535823</v>
+        <v>0.02327707616538048</v>
       </c>
       <c r="U12" t="n">
-        <v>2327.707616467713</v>
+        <v>0.02327707616544428</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000004</v>
       </c>
       <c r="G13" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H13" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000014</v>
       </c>
       <c r="J13" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K13" t="n">
-        <v>-1658.358832423168</v>
+        <v>-0.01658358832400036</v>
       </c>
       <c r="L13" t="n">
-        <v>-1658.358832407449</v>
+        <v>-0.01658358832411552</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.011772803527846e-11</v>
+        <v>-2.078127505562269e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>7622.445377939776</v>
+        <v>0.07622445377950053</v>
       </c>
       <c r="O13" t="n">
-        <v>-7622.445377980606</v>
+        <v>-0.07622445377918496</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q13" t="n">
-        <v>1658.358832423168</v>
+        <v>0.01658358832400036</v>
       </c>
       <c r="R13" t="n">
-        <v>1658.358832407449</v>
+        <v>0.01658358832411552</v>
       </c>
       <c r="S13" t="n">
-        <v>4.011772803527846e-11</v>
+        <v>2.078127505562269e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>2327.707616504927</v>
+        <v>0.02327707616519245</v>
       </c>
       <c r="U13" t="n">
-        <v>-2327.7076165584</v>
+        <v>-0.02327707616481722</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000005</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.0000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="K14" t="n">
-        <v>309.8868051251302</v>
+        <v>0.003098868051357451</v>
       </c>
       <c r="L14" t="n">
-        <v>-309.8868051271218</v>
+        <v>-0.00309886805127513</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.410522176876903e-11</v>
+        <v>-6.724768271676742e-17</v>
       </c>
       <c r="N14" t="n">
-        <v>1594.71973438634</v>
+        <v>0.01594719734385297</v>
       </c>
       <c r="O14" t="n">
-        <v>1594.719734381884</v>
+        <v>0.01594719734403593</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="Q14" t="n">
-        <v>-309.8868051251302</v>
+        <v>-0.003098868051357451</v>
       </c>
       <c r="R14" t="n">
-        <v>309.8868051271218</v>
+        <v>0.00309886805127513</v>
       </c>
       <c r="S14" t="n">
-        <v>2.410522176876903e-11</v>
+        <v>6.724768271676742e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>264.6010963763609</v>
+        <v>0.002646010963797804</v>
       </c>
       <c r="U14" t="n">
-        <v>264.6010963688896</v>
+        <v>0.002646010964108547</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G15" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-28440000</v>
+        <v>-284.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-6000000000</v>
+        <v>-60000</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="K15" t="n">
-        <v>-309.8868051250465</v>
+        <v>-0.00309886805114401</v>
       </c>
       <c r="L15" t="n">
-        <v>-309.8868051299721</v>
+        <v>-0.003098868051247916</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.409488232592988e-11</v>
+        <v>-6.745272321585572e-17</v>
       </c>
       <c r="N15" t="n">
-        <v>1594.719734390186</v>
+        <v>0.0159471973437427</v>
       </c>
       <c r="O15" t="n">
-        <v>-1594.719734376107</v>
+        <v>-0.01594719734354322</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="Q15" t="n">
-        <v>309.8868051250465</v>
+        <v>0.00309886805114401</v>
       </c>
       <c r="R15" t="n">
-        <v>309.8868051299721</v>
+        <v>0.003098868051247916</v>
       </c>
       <c r="S15" t="n">
-        <v>2.409488232592988e-11</v>
+        <v>6.745272321585572e-17</v>
       </c>
       <c r="T15" t="n">
-        <v>264.6010963896686</v>
+        <v>0.002646010963744572</v>
       </c>
       <c r="U15" t="n">
-        <v>-264.6010963741574</v>
+        <v>-0.002646010963320955</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G16" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999998</v>
       </c>
       <c r="J16" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-309.8868051309946</v>
+        <v>-0.003098868051177428</v>
       </c>
       <c r="L16" t="n">
-        <v>309.8868051201698</v>
+        <v>0.003098868051253503</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.411927784824087e-11</v>
+        <v>-6.803347718465976e-17</v>
       </c>
       <c r="N16" t="n">
-        <v>-1594.719734367751</v>
+        <v>-0.01594719734383659</v>
       </c>
       <c r="O16" t="n">
-        <v>-1594.719734389742</v>
+        <v>-0.01594719734361782</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>309.8868051309946</v>
+        <v>0.003098868051177428</v>
       </c>
       <c r="R16" t="n">
-        <v>-309.8868051201698</v>
+        <v>-0.003098868051253503</v>
       </c>
       <c r="S16" t="n">
-        <v>2.411927784824087e-11</v>
+        <v>6.803347718465976e-17</v>
       </c>
       <c r="T16" t="n">
-        <v>-264.6010963532681</v>
+        <v>-0.002646010963684871</v>
       </c>
       <c r="U16" t="n">
-        <v>-264.601096396189</v>
+        <v>-0.002646010963446743</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.00000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K17" t="n">
-        <v>309.8868051191603</v>
+        <v>0.003098868051323977</v>
       </c>
       <c r="L17" t="n">
-        <v>309.886805123052</v>
+        <v>0.003098868051226509</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.409387806605927e-11</v>
+        <v>-6.727537542781763e-17</v>
       </c>
       <c r="N17" t="n">
-        <v>-1594.719734371638</v>
+        <v>-0.01594719734372643</v>
       </c>
       <c r="O17" t="n">
-        <v>1594.719734368206</v>
+        <v>0.01594719734396133</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="Q17" t="n">
-        <v>-309.8868051191603</v>
+        <v>-0.003098868051323977</v>
       </c>
       <c r="R17" t="n">
-        <v>-309.886805123052</v>
+        <v>-0.003098868051226509</v>
       </c>
       <c r="S17" t="n">
-        <v>2.409387806605927e-11</v>
+        <v>6.727537542781763e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>-264.6010963666739</v>
+        <v>-0.002646010963632412</v>
       </c>
       <c r="U17" t="n">
-        <v>264.6010963467415</v>
+        <v>0.002646010963982204</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J18" t="n">
-        <v>-27374.66294020042</v>
+        <v>-0.2737466294018986</v>
       </c>
       <c r="K18" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-1.153244166829381e-14</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.45739123178646e-09</v>
+        <v>1.676783711879182e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>2.558309120104241e-11</v>
+        <v>1.928795664851712e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>14707.31899338208</v>
+        <v>0.1470731899328119</v>
       </c>
       <c r="O18" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-4.624078897563777e-14</v>
       </c>
       <c r="P18" t="n">
-        <v>27374.66294020042</v>
+        <v>0.2737466294018986</v>
       </c>
       <c r="Q18" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>1.153244166829381e-14</v>
       </c>
       <c r="R18" t="n">
-        <v>8.45739123178646e-09</v>
+        <v>-1.676783711879182e-13</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.558309120104241e-11</v>
+        <v>-1.928795664851712e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>-14707.31899331443</v>
+        <v>-0.1470731899341532</v>
       </c>
       <c r="U18" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>-4.601874437071274e-14</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861589</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326986</v>
       </c>
       <c r="H19" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705982</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653971</v>
       </c>
       <c r="J19" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018418</v>
       </c>
       <c r="K19" t="n">
-        <v>-9.276845958083868e-11</v>
+        <v>1.16157083951407e-14</v>
       </c>
       <c r="L19" t="n">
-        <v>8.317329047713429e-09</v>
+        <v>1.147831829584334e-13</v>
       </c>
       <c r="M19" t="n">
-        <v>2.521716169212596e-11</v>
+        <v>7.600257229123386e-17</v>
       </c>
       <c r="N19" t="n">
-        <v>14707.31899331497</v>
+        <v>0.1470731899330236</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>4.651834473179406e-14</v>
       </c>
       <c r="P19" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018418</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.276845958083868e-11</v>
+        <v>-1.16157083951407e-14</v>
       </c>
       <c r="R19" t="n">
-        <v>-8.317329047713429e-09</v>
+        <v>-1.147831829584334e-13</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.521716169212596e-11</v>
+        <v>-7.600257229123386e-17</v>
       </c>
       <c r="T19" t="n">
-        <v>-14707.31899338152</v>
+        <v>-0.1470731899339416</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>4.64628335805628e-14</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H20" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I20" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J20" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294020123</v>
       </c>
       <c r="K20" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>-1.160183060733289e-14</v>
       </c>
       <c r="L20" t="n">
-        <v>1.831995177781209e-08</v>
+        <v>-1.380145997487148e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>2.55582222052908e-11</v>
+        <v>1.92825356376547e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>14707.31899327498</v>
+        <v>0.1470731899340347</v>
       </c>
       <c r="O20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
       <c r="P20" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294020123</v>
       </c>
       <c r="Q20" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>1.160183060733289e-14</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.831995177781209e-08</v>
+        <v>1.380145997487148e-13</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.55582222052908e-11</v>
+        <v>-1.92825356376547e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>-14707.31899342155</v>
+        <v>-0.1470731899329306</v>
       </c>
       <c r="U20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-4.629630012686903e-14</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326984</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.33705981</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J21" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294019555</v>
       </c>
       <c r="K21" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-1.162958618294851e-14</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.627086021471769e-09</v>
+        <v>3.953781746446339e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>2.524203068787756e-11</v>
+        <v>7.605678239985814e-17</v>
       </c>
       <c r="N21" t="n">
-        <v>-14707.31899334175</v>
+        <v>-0.1470731899336408</v>
       </c>
       <c r="O21" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-4.668487818548783e-14</v>
       </c>
       <c r="P21" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294019555</v>
       </c>
       <c r="Q21" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>1.162958618294851e-14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.627086021471769e-09</v>
+        <v>-3.953781746446339e-14</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.524203068787756e-11</v>
+        <v>-7.605678239985814e-17</v>
       </c>
       <c r="T21" t="n">
-        <v>14707.31899335478</v>
+        <v>0.1470731899333244</v>
       </c>
       <c r="U21" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H22" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J22" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="L22" t="n">
-        <v>-7.940798241179436e-09</v>
+        <v>1.999719834167024e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>3.044675622732029e-11</v>
+        <v>1.989104410696219e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>-3238.065438907926</v>
+        <v>-0.03238065439019683</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>-1.563749130184533e-13</v>
       </c>
       <c r="P22" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="R22" t="n">
-        <v>7.940798241179436e-09</v>
+        <v>-1.999719834167024e-13</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.044675622732029e-11</v>
+        <v>-1.989104410696219e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>3238.065438971422</v>
+        <v>0.03238065438859682</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>-1.562638907159908e-13</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G23" t="n">
-        <v>-30.00977467543448</v>
+        <v>-0.0003000977467543447</v>
       </c>
       <c r="H23" t="n">
-        <v>-28449266.39231189</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I23" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086893</v>
       </c>
       <c r="J23" t="n">
-        <v>9266.392311885953</v>
+        <v>0.09266392311866412</v>
       </c>
       <c r="K23" t="n">
-        <v>1.473381416872144e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="L23" t="n">
-        <v>9.896666597342119e-09</v>
+        <v>1.138637795161657e-13</v>
       </c>
       <c r="M23" t="n">
-        <v>2.933653320269514e-11</v>
+        <v>1.280984866791623e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>-3238.065438979261</v>
+        <v>-0.03238065438985234</v>
       </c>
       <c r="O23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>1.564859353209158e-13</v>
       </c>
       <c r="P23" t="n">
-        <v>-9266.392311885953</v>
+        <v>-0.09266392311866412</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.473381416872144e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="R23" t="n">
-        <v>-9.896666597342119e-09</v>
+        <v>-1.138637795161657e-13</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.933653320269514e-11</v>
+        <v>-1.280984866791623e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>3238.065438900087</v>
+        <v>0.03238065438894119</v>
       </c>
       <c r="U23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>1.56319401867222e-13</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543449</v>
       </c>
       <c r="H24" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086897</v>
       </c>
       <c r="J24" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311883465</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>-3.903821710338207e-14</v>
       </c>
       <c r="L24" t="n">
-        <v>1.939906724146567e-08</v>
+        <v>-1.501750113153122e-13</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04991587540826e-11</v>
+        <v>1.986393905265005e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>-3238.065439017271</v>
+        <v>-0.032380654388796</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>-1.562083795647595e-13</v>
       </c>
       <c r="P24" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311883465</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>3.903821710338207e-14</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.939906724146567e-08</v>
+        <v>1.501750113153122e-13</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.04991587540826e-11</v>
+        <v>-1.986393905265005e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>3238.065438862105</v>
+        <v>0.03238065438999761</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>-1.560418461110658e-13</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G25" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H25" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J25" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.491571310907602e-10</v>
+        <v>-3.907985046680551e-14</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.949956640601158e-09</v>
+        <v>3.622623034882366e-14</v>
       </c>
       <c r="M25" t="n">
-        <v>2.923972175494782e-11</v>
+        <v>1.278680937175092e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>3238.065438947485</v>
+        <v>0.03238065438925182</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.111804395914078e-10</v>
+        <v>-1.564304241696846e-13</v>
       </c>
       <c r="P25" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.491571310907602e-10</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.949956640601158e-09</v>
+        <v>-3.622623034882366e-14</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.923972175494782e-11</v>
+        <v>-1.278680937175092e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>-3238.065438931885</v>
+        <v>-0.03238065438954182</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.966285243630409e-10</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321729</v>
       </c>
       <c r="G26" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.0002999792379152161</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436249</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304321</v>
       </c>
       <c r="J26" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637522159</v>
       </c>
       <c r="K26" t="n">
-        <v>-9.094947017729282e-11</v>
+        <v>-3.372302437298913e-14</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.78480535800918e-09</v>
+        <v>1.817729994302297e-13</v>
       </c>
       <c r="M26" t="n">
-        <v>2.237432461527078e-11</v>
+        <v>4.984280674823205e-17</v>
       </c>
       <c r="N26" t="n">
-        <v>732.9878821492639</v>
+        <v>0.007329878820614492</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-1.35003119794419e-13</v>
       </c>
       <c r="P26" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637522159</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.094947017729282e-11</v>
+        <v>3.372302437298913e-14</v>
       </c>
       <c r="R26" t="n">
-        <v>3.78480535800918e-09</v>
+        <v>-1.817729994302297e-13</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.237432461527078e-11</v>
+        <v>-4.984280674823205e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>-732.987882118985</v>
+        <v>-0.007329878822068229</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.348365863407253e-13</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J27" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K27" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>3.37924133120282e-14</v>
       </c>
       <c r="L27" t="n">
-        <v>8.479389634885592e-09</v>
+        <v>5.07484679279635e-14</v>
       </c>
       <c r="M27" t="n">
-        <v>2.60691468412233e-11</v>
+        <v>1.548037414401959e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>732.987882100203</v>
+        <v>0.00732987882113827</v>
       </c>
       <c r="O27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>1.352806755505753e-13</v>
       </c>
       <c r="P27" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q27" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-3.37924133120282e-14</v>
       </c>
       <c r="R27" t="n">
-        <v>-8.479389634885592e-09</v>
+        <v>-5.07484679279635e-14</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.60691468412233e-11</v>
+        <v>-1.548037414401959e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>-732.9878821680668</v>
+        <v>-0.007329878821544254</v>
       </c>
       <c r="U27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>1.35003119794419e-13</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321726</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152158</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H28" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304316</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J28" t="n">
-        <v>-1968.245637543499</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.913048077374697e-11</v>
+        <v>-3.380629109983602e-14</v>
       </c>
       <c r="L28" t="n">
-        <v>1.400917426508386e-08</v>
+        <v>-1.213413050593637e-13</v>
       </c>
       <c r="M28" t="n">
-        <v>2.236144602818513e-11</v>
+        <v>4.998680234926528e-17</v>
       </c>
       <c r="N28" t="n">
-        <v>732.9878820781033</v>
+        <v>0.00732987882182677</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.353361867018066e-13</v>
       </c>
       <c r="P28" t="n">
-        <v>1968.245637543499</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q28" t="n">
-        <v>8.913048077374697e-11</v>
+        <v>3.380629109983602e-14</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.400917426508386e-08</v>
+        <v>1.213413050593637e-13</v>
       </c>
       <c r="S28" t="n">
-        <v>-2.236144602818513e-11</v>
+        <v>-4.998680234926528e-17</v>
       </c>
       <c r="T28" t="n">
-        <v>-732.9878821901764</v>
+        <v>-0.007329878820855593</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.351141420968816e-13</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G29" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H29" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J29" t="n">
-        <v>-1968.245637532324</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-3.393119119010635e-14</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.980993147299159e-10</v>
+        <v>3.120854269456075e-14</v>
       </c>
       <c r="M29" t="n">
-        <v>2.612554617087426e-11</v>
+        <v>1.546631339709517e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>-732.9878821333361</v>
+        <v>-0.007329878821466364</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.001776687800884e-10</v>
+        <v>-1.357802759116566e-13</v>
       </c>
       <c r="P29" t="n">
-        <v>1968.245637532324</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>3.393119119010635e-14</v>
       </c>
       <c r="R29" t="n">
-        <v>1.980993147299159e-10</v>
+        <v>-3.120854269456075e-14</v>
       </c>
       <c r="S29" t="n">
-        <v>-2.612554617087426e-11</v>
+        <v>-1.546631339709517e-16</v>
       </c>
       <c r="T29" t="n">
-        <v>732.9878821349207</v>
+        <v>0.007329878821216248</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.92901711165905e-10</v>
+        <v>-1.356692536091941e-13</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785245</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481552</v>
+        <v>-0.0003000032688481556</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680511</v>
+        <v>-284.4030988680515</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963103</v>
+        <v>-60000.65376963112</v>
       </c>
       <c r="J30" t="n">
-        <v>309.8868051171303</v>
+        <v>0.00309886805143833</v>
       </c>
       <c r="K30" t="n">
-        <v>1.205989974550903e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="L30" t="n">
-        <v>-6.750866532456712e-10</v>
+        <v>9.846290449644357e-14</v>
       </c>
       <c r="M30" t="n">
-        <v>8.726019906646343e-12</v>
+        <v>-3.246761990120459e-17</v>
       </c>
       <c r="N30" t="n">
-        <v>-264.6010963687289</v>
+        <v>-0.002646010964108621</v>
       </c>
       <c r="O30" t="n">
-        <v>4.823959898203611e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
       <c r="P30" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.00309886805143833</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.205989974550903e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="R30" t="n">
-        <v>6.750866532456712e-10</v>
+        <v>-9.846290449644357e-14</v>
       </c>
       <c r="S30" t="n">
-        <v>-8.726019906646343e-12</v>
+        <v>3.246761990120459e-17</v>
       </c>
       <c r="T30" t="n">
-        <v>264.6010963741877</v>
+        <v>0.002646010963320918</v>
       </c>
       <c r="U30" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-2.015054789694659e-14</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785243</v>
+        <v>-0.002400026150785244</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481555</v>
       </c>
       <c r="H31" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680514</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963106</v>
+        <v>-60000.65376963108</v>
       </c>
       <c r="J31" t="n">
-        <v>309.8868051245809</v>
+        <v>0.003098868051324644</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.218722900375724e-09</v>
+        <v>5.023759186428833e-15</v>
       </c>
       <c r="L31" t="n">
-        <v>4.557804800242593e-09</v>
+        <v>7.490102288398859e-15</v>
       </c>
       <c r="M31" t="n">
-        <v>1.397171267569774e-11</v>
+        <v>8.102124250371559e-17</v>
       </c>
       <c r="N31" t="n">
-        <v>-264.601096389707</v>
+        <v>-0.002646010963744791</v>
       </c>
       <c r="O31" t="n">
-        <v>-4.874891601502895e-09</v>
+        <v>2.009503674571533e-14</v>
       </c>
       <c r="P31" t="n">
-        <v>-309.8868051245809</v>
+        <v>-0.003098868051324644</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.218722900375724e-09</v>
+        <v>-5.023759186428833e-15</v>
       </c>
       <c r="R31" t="n">
-        <v>-4.557804800242593e-09</v>
+        <v>-7.490102288398859e-15</v>
       </c>
       <c r="S31" t="n">
-        <v>-1.397171267569774e-11</v>
+        <v>-8.102124250371559e-17</v>
       </c>
       <c r="T31" t="n">
-        <v>264.6010963532444</v>
+        <v>0.00264601096368487</v>
       </c>
       <c r="U31" t="n">
-        <v>-4.867615643888712e-09</v>
+        <v>2.003952559448408e-14</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481553</v>
       </c>
       <c r="H32" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680512</v>
       </c>
       <c r="I32" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963106</v>
       </c>
       <c r="J32" t="n">
-        <v>309.8868051208556</v>
+        <v>0.003098868051154113</v>
       </c>
       <c r="K32" t="n">
-        <v>1.207808963954449e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="L32" t="n">
-        <v>6.185530310176546e-09</v>
+        <v>-6.722400414105323e-14</v>
       </c>
       <c r="M32" t="n">
-        <v>8.644529536638856e-12</v>
+        <v>-3.310458867753982e-17</v>
       </c>
       <c r="N32" t="n">
-        <v>-264.6010963962013</v>
+        <v>-0.002646010963446374</v>
       </c>
       <c r="O32" t="n">
-        <v>4.838511813431978e-09</v>
+        <v>-2.031708135064036e-14</v>
       </c>
       <c r="P32" t="n">
-        <v>-309.8868051208556</v>
+        <v>-0.003098868051154113</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.207808963954449e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.185530310176546e-09</v>
+        <v>6.722400414105323e-14</v>
       </c>
       <c r="S32" t="n">
-        <v>-8.644529536638856e-12</v>
+        <v>3.310458867753982e-17</v>
       </c>
       <c r="T32" t="n">
-        <v>264.6010963467751</v>
+        <v>0.00264601096398372</v>
       </c>
       <c r="U32" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-2.037259250187162e-14</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481554</v>
       </c>
       <c r="H33" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680513</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963107</v>
       </c>
       <c r="J33" t="n">
-        <v>309.8868051171303</v>
+        <v>0.0030988680512678</v>
       </c>
       <c r="K33" t="n">
-        <v>1.229636836796999e-09</v>
+        <v>-5.120903701083535e-15</v>
       </c>
       <c r="L33" t="n">
-        <v>1.223313006448734e-09</v>
+        <v>2.023619986857295e-14</v>
       </c>
       <c r="M33" t="n">
-        <v>1.392519433096595e-11</v>
+        <v>8.009628252531389e-17</v>
       </c>
       <c r="N33" t="n">
-        <v>264.6010963665491</v>
+        <v>0.002646010963633847</v>
       </c>
       <c r="O33" t="n">
-        <v>4.911271389573812e-09</v>
+        <v>-2.059463710679665e-14</v>
       </c>
       <c r="P33" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.0030988680512678</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.229636836796999e-09</v>
+        <v>5.120903701083535e-15</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.223313006448734e-09</v>
+        <v>-2.023619986857295e-14</v>
       </c>
       <c r="S33" t="n">
-        <v>-1.392519433096595e-11</v>
+        <v>-8.009628252531389e-17</v>
       </c>
       <c r="T33" t="n">
-        <v>-264.6010963763936</v>
+        <v>-0.002646010963795291</v>
       </c>
       <c r="U33" t="n">
-        <v>4.918547347187996e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G2" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000009</v>
       </c>
       <c r="H2" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I2" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>119.8844950930915</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="Q2" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="R2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.24983693095458</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="T2" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="U2" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AC2" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="AD2" t="n">
-        <v>-119.8844950930915</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="AE2" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.24983693095458</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AH2" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AI2" t="n">
-        <v>-19766.62946073442</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19766.62946072896</v>
+        <v>0.1976662946072387</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2.421003440282873e-11</v>
+        <v>-1.227948388079732e-16</v>
       </c>
       <c r="AL2" t="n">
-        <v>-69104.76771108717</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="AM2" t="n">
-        <v>-69104.76771110963</v>
+        <v>-0.6910476771102511</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AO2" t="n">
-        <v>19766.62946073442</v>
+        <v>0.1976662946071376</v>
       </c>
       <c r="AP2" t="n">
-        <v>-19766.62946072896</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.421003440282873e-11</v>
+        <v>1.227948388079732e-16</v>
       </c>
       <c r="AR2" t="n">
-        <v>-49495.00905328659</v>
+        <v>-0.4949500905327627</v>
       </c>
       <c r="AS2" t="n">
-        <v>-49495.00905329685</v>
+        <v>-0.4949500905325742</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-30.00000000000005</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H3" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I3" t="n">
-        <v>-6000000000.00001</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="Q3" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="R3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S3" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="T3" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="U3" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AC3" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="AD3" t="n">
-        <v>-119.8844950930244</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="AE3" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AG3" t="n">
-        <v>-13.24983693093416</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AI3" t="n">
-        <v>19766.62946072038</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19766.62946072127</v>
+        <v>0.1976662946071929</v>
       </c>
       <c r="AK3" t="n">
-        <v>-2.423009033885211e-11</v>
+        <v>-1.232406124819545e-16</v>
       </c>
       <c r="AL3" t="n">
-        <v>-69104.76771105522</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="AM3" t="n">
-        <v>69104.76771105242</v>
+        <v>0.6910476771113704</v>
       </c>
       <c r="AN3" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AO3" t="n">
-        <v>-19766.62946072038</v>
+        <v>-0.1976662946074107</v>
       </c>
       <c r="AP3" t="n">
-        <v>-19766.62946072127</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.423009033885211e-11</v>
+        <v>1.232406124819545e-16</v>
       </c>
       <c r="AR3" t="n">
-        <v>-49495.00905327238</v>
+        <v>-0.4949500905326924</v>
       </c>
       <c r="AS3" t="n">
-        <v>49495.00905326986</v>
+        <v>0.4949500905330936</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H4" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I4" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="Q4" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="R4" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S4" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="U4" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AC4" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="AD4" t="n">
-        <v>119.8844950931343</v>
+        <v>0.001198844950931538</v>
       </c>
       <c r="AE4" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AG4" t="n">
-        <v>-13.24983693092235</v>
+        <v>-0.0001324983693096109</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AI4" t="n">
-        <v>19766.62946071211</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-19766.62946073354</v>
+        <v>-0.1976662946073556</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2.422151369217067e-11</v>
+        <v>-1.231034558950431e-16</v>
       </c>
       <c r="AL4" t="n">
-        <v>69104.76771110686</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="AM4" t="n">
-        <v>69104.76771101885</v>
+        <v>0.6910476771112495</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AO4" t="n">
-        <v>-19766.62946071211</v>
+        <v>-0.1976662946073792</v>
       </c>
       <c r="AP4" t="n">
-        <v>19766.62946073354</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.422151369217067e-11</v>
+        <v>1.231034558950431e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>49495.00905329436</v>
+        <v>0.4949500905329763</v>
       </c>
       <c r="AS4" t="n">
-        <v>49495.00905325378</v>
+        <v>0.4949500905330254</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G5" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H5" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I5" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="Q5" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="R5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S5" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="U5" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AC5" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="AD5" t="n">
-        <v>119.8844950930671</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="AE5" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="AF5" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.24983693096641</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1.862645149230957e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AI5" t="n">
-        <v>-19766.62946074268</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19766.62946072584</v>
+        <v>-0.1976662946073095</v>
       </c>
       <c r="AK5" t="n">
-        <v>-2.422188588688456e-11</v>
+        <v>-1.233893320291097e-16</v>
       </c>
       <c r="AL5" t="n">
-        <v>69104.76771107491</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="AM5" t="n">
-        <v>-69104.76771114318</v>
+        <v>-0.6910476771103716</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.862645149230957e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AO5" t="n">
-        <v>19766.62946074268</v>
+        <v>0.1976662946071689</v>
       </c>
       <c r="AP5" t="n">
-        <v>19766.62946072584</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.422188588688456e-11</v>
+        <v>1.233893320291097e-16</v>
       </c>
       <c r="AR5" t="n">
-        <v>49495.00905328012</v>
+        <v>0.494950090532905</v>
       </c>
       <c r="AS5" t="n">
-        <v>-49495.0090533129</v>
+        <v>-0.494950090532642</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G6" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H6" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I6" t="n">
-        <v>-5999999999.999995</v>
+        <v>-60000.00000000015</v>
       </c>
       <c r="J6" t="n">
-        <v>119.8844950930915</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="K6" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="L6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.24983693095458</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="N6" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="O6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="P6" t="n">
-        <v>120.039098701767</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="Q6" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="R6" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="W6" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="X6" t="n">
-        <v>-119.8844950930915</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.24983693095458</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AB6" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="AD6" t="n">
-        <v>-120.039098701767</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>7608.033479463036</v>
+        <v>0.07608033479482673</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-7608.033479468945</v>
+        <v>-0.07608033479472942</v>
       </c>
       <c r="AK6" t="n">
-        <v>-3.867834873910378e-11</v>
+        <v>-2.119131582129195e-16</v>
       </c>
       <c r="AL6" t="n">
-        <v>34787.69005993183</v>
+        <v>0.3478769005994383</v>
       </c>
       <c r="AM6" t="n">
-        <v>34787.69005991481</v>
+        <v>0.3478769005997626</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>-7608.033479463036</v>
+        <v>-0.07608033479482673</v>
       </c>
       <c r="AP6" t="n">
-        <v>7608.033479468945</v>
+        <v>0.07608033479472942</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.867834873910378e-11</v>
+        <v>2.119131582129195e-16</v>
       </c>
       <c r="AR6" t="n">
-        <v>10860.51081688182</v>
+        <v>0.1086051081689382</v>
       </c>
       <c r="AS6" t="n">
-        <v>10860.51081686339</v>
+        <v>0.1086051081691977</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001799999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0002999999999999993</v>
       </c>
       <c r="H7" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.3999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>-6000000000.000008</v>
+        <v>-59999.99999999986</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="K7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="L7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M7" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="N7" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="O7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="P7" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="R7" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="W7" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="X7" t="n">
-        <v>-119.8844950930244</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AA7" t="n">
-        <v>-13.24983693093416</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AB7" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="AC7" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="AD7" t="n">
-        <v>-120.0390987015889</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.097819328308105e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AI7" t="n">
-        <v>-7608.033479476842</v>
+        <v>-0.07608033479457235</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-7608.033479476904</v>
+        <v>-0.07608033479480569</v>
       </c>
       <c r="AK7" t="n">
-        <v>-3.867545858883965e-11</v>
+        <v>-2.115723902159476e-16</v>
       </c>
       <c r="AL7" t="n">
-        <v>34787.69005995742</v>
+        <v>0.3478769005996691</v>
       </c>
       <c r="AM7" t="n">
-        <v>-34787.69005995538</v>
+        <v>-0.3478769005989404</v>
       </c>
       <c r="AN7" t="n">
-        <v>-4.097819328308105e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AO7" t="n">
-        <v>7608.033479476842</v>
+        <v>0.07608033479457235</v>
       </c>
       <c r="AP7" t="n">
-        <v>7608.033479476904</v>
+        <v>0.07608033479480569</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.867545858883965e-11</v>
+        <v>2.115723902159476e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>10860.51081690402</v>
+        <v>0.1086051081691652</v>
       </c>
       <c r="AS7" t="n">
-        <v>-10860.51081690566</v>
+        <v>-0.1086051081684936</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999996</v>
       </c>
       <c r="I8" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999991</v>
       </c>
       <c r="J8" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="K8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="L8" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M8" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="O8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="P8" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="Q8" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="R8" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="W8" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="X8" t="n">
-        <v>119.8844950931343</v>
+        <v>0.001198844950931538</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AA8" t="n">
-        <v>-13.24983693092235</v>
+        <v>-0.0001324983693096109</v>
       </c>
       <c r="AB8" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="AC8" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="AD8" t="n">
-        <v>120.039098701887</v>
+        <v>0.001200390987019375</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.917176071140197</v>
+        <v>2.917176071098574e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AI8" t="n">
-        <v>-7608.033479484184</v>
+        <v>-0.07608033479458301</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7608.03347946298</v>
+        <v>0.07608033479459361</v>
       </c>
       <c r="AK8" t="n">
-        <v>-3.868580190546846e-11</v>
+        <v>-2.113669821224497e-16</v>
       </c>
       <c r="AL8" t="n">
-        <v>-34787.6900599128</v>
+        <v>-0.3478769005990348</v>
       </c>
       <c r="AM8" t="n">
-        <v>-34787.69005997882</v>
+        <v>-0.3478769005989906</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AO8" t="n">
-        <v>7608.033479484184</v>
+        <v>0.07608033479458301</v>
       </c>
       <c r="AP8" t="n">
-        <v>-7608.03347946298</v>
+        <v>-0.07608033479459361</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.868580190546846e-11</v>
+        <v>2.113669821224497e-16</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10860.51081686508</v>
+        <v>-0.1086051081685271</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10860.51081692625</v>
+        <v>-0.1086051081685075</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G9" t="n">
-        <v>-29.99999999999997</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H9" t="n">
-        <v>-28439999.99999997</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999993</v>
+        <v>-60000.00000000016</v>
       </c>
       <c r="J9" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="K9" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="L9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="O9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="P9" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="Q9" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="R9" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="V9" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="W9" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="X9" t="n">
-        <v>119.8844950930671</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="Z9" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.24983693096641</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="AB9" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="AD9" t="n">
-        <v>120.0390987017087</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AG9" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="AH9" t="n">
-        <v>-2.60770320892334e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI9" t="n">
-        <v>7608.03347945568</v>
+        <v>0.07608033479481566</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7608.033479470957</v>
+        <v>0.07608033479466958</v>
       </c>
       <c r="AK9" t="n">
-        <v>-3.869313251766919e-11</v>
+        <v>-2.114968923479162e-16</v>
       </c>
       <c r="AL9" t="n">
-        <v>-34787.69005993844</v>
+        <v>-0.3478769005992646</v>
       </c>
       <c r="AM9" t="n">
-        <v>34787.69005989138</v>
+        <v>0.3478769005997115</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.60770320892334e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO9" t="n">
-        <v>-7608.03347945568</v>
+        <v>-0.07608033479481566</v>
       </c>
       <c r="AP9" t="n">
-        <v>-7608.033479470957</v>
+        <v>-0.07608033479466958</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.869313251766919e-11</v>
+        <v>2.114968923479162e-16</v>
       </c>
       <c r="AR9" t="n">
-        <v>-10860.51081688729</v>
+        <v>-0.1086051081687528</v>
       </c>
       <c r="AS9" t="n">
-        <v>10860.51081684273</v>
+        <v>0.1086051081691825</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000003</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000</v>
+        <v>-60000.00000000005</v>
       </c>
       <c r="J10" t="n">
-        <v>120.039098701767</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="K10" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="L10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="P10" t="n">
-        <v>119.9916951661322</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="R10" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="V10" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="X10" t="n">
-        <v>-120.039098701767</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="AC10" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="AD10" t="n">
-        <v>-119.9916951661322</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6603494433687225</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1658.358832414433</v>
+        <v>-0.01658358832394202</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1658.358832411864</v>
+        <v>0.01658358832407774</v>
       </c>
       <c r="AK10" t="n">
-        <v>-4.010927424673966e-11</v>
+        <v>-2.077521622880486e-16</v>
       </c>
       <c r="AL10" t="n">
-        <v>-7622.445377949901</v>
+        <v>-0.07622445377939645</v>
       </c>
       <c r="AM10" t="n">
-        <v>-7622.445377955475</v>
+        <v>-0.07622445377900067</v>
       </c>
       <c r="AN10" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AO10" t="n">
-        <v>1658.358832414433</v>
+        <v>0.01658358832394202</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1658.358832411864</v>
+        <v>-0.01658358832407774</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.010927424673966e-11</v>
+        <v>2.077521622880486e-16</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2327.707616521262</v>
+        <v>-0.02327707616506976</v>
       </c>
       <c r="AS10" t="n">
-        <v>-2327.70761653113</v>
+        <v>-0.02327707616465158</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-30.00000000000001</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H11" t="n">
-        <v>-28440000.00000001</v>
+        <v>-284.3999999999995</v>
       </c>
       <c r="I11" t="n">
-        <v>-6000000000.000001</v>
+        <v>-59999.9999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="K11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="L11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="Q11" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="R11" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="V11" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="W11" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="X11" t="n">
-        <v>-120.0390987015889</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="AC11" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="AD11" t="n">
-        <v>-119.9916951658417</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AI11" t="n">
-        <v>1658.358832404872</v>
+        <v>0.01658358832425133</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1658.358832402486</v>
+        <v>0.01658358832403251</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.012493149746856e-11</v>
+        <v>-2.0804665930623e-16</v>
       </c>
       <c r="AL11" t="n">
-        <v>-7622.445377924581</v>
+        <v>-0.07622445377931243</v>
       </c>
       <c r="AM11" t="n">
-        <v>7622.445377934186</v>
+        <v>0.07622445377989695</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1658.358832404872</v>
+        <v>-0.01658358832425133</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1658.358832402486</v>
+        <v>-0.01658358832403251</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.012493149746856e-11</v>
+        <v>2.0804665930623e-16</v>
       </c>
       <c r="AR11" t="n">
-        <v>-2327.707616490355</v>
+        <v>-0.02327707616488241</v>
       </c>
       <c r="AS11" t="n">
-        <v>2327.707616495056</v>
+        <v>0.02327707616561103</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001799999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-30.00000000000001</v>
+        <v>-0.0002999999999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>-28440000.00000001</v>
+        <v>-284.3999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>-6000000000.000001</v>
+        <v>-59999.99999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="K12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="L12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="Q12" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="R12" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="S12" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="V12" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="W12" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="X12" t="n">
-        <v>120.039098701887</v>
+        <v>0.001200390987019375</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.917176071140197</v>
+        <v>2.917176071098574e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="AC12" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="AD12" t="n">
-        <v>119.991695166331</v>
+        <v>0.001199916951663713</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.660349443347221</v>
+        <v>-6.603494433789558e-06</v>
       </c>
       <c r="AH12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AI12" t="n">
-        <v>1658.358832396134</v>
+        <v>0.01658358832419271</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-1658.358832416807</v>
+        <v>-0.01658358832416097</v>
       </c>
       <c r="AK12" t="n">
-        <v>-4.012638059121664e-11</v>
+        <v>-2.076096844797136e-16</v>
       </c>
       <c r="AL12" t="n">
-        <v>7622.445377965032</v>
+        <v>0.07622445377958545</v>
       </c>
       <c r="AM12" t="n">
-        <v>7622.445377909098</v>
+        <v>0.07622445377971176</v>
       </c>
       <c r="AN12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1658.358832396134</v>
+        <v>-0.01658358832419271</v>
       </c>
       <c r="AP12" t="n">
-        <v>1658.358832416807</v>
+        <v>0.01658358832416097</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.012638059121664e-11</v>
+        <v>2.076096844797136e-16</v>
       </c>
       <c r="AR12" t="n">
-        <v>2327.707616535823</v>
+        <v>0.02327707616538048</v>
       </c>
       <c r="AS12" t="n">
-        <v>2327.707616467713</v>
+        <v>0.02327707616544428</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000004</v>
       </c>
       <c r="G13" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H13" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000014</v>
       </c>
       <c r="J13" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="K13" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="L13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="Q13" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="R13" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="V13" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="X13" t="n">
-        <v>120.0390987017087</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="AC13" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="AD13" t="n">
-        <v>119.9916951660405</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="AE13" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.6603494433809615</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1658.358832423168</v>
+        <v>-0.01658358832400036</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1658.358832407449</v>
+        <v>-0.01658358832411552</v>
       </c>
       <c r="AK13" t="n">
-        <v>-4.011772803527846e-11</v>
+        <v>-2.078127505562269e-16</v>
       </c>
       <c r="AL13" t="n">
-        <v>7622.445377939776</v>
+        <v>0.07622445377950053</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7622.445377980606</v>
+        <v>-0.07622445377918496</v>
       </c>
       <c r="AN13" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO13" t="n">
-        <v>1658.358832423168</v>
+        <v>0.01658358832400036</v>
       </c>
       <c r="AP13" t="n">
-        <v>1658.358832407449</v>
+        <v>0.01658358832411552</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.011772803527846e-11</v>
+        <v>2.078127505562269e-16</v>
       </c>
       <c r="AR13" t="n">
-        <v>2327.707616504927</v>
+        <v>0.02327707616519245</v>
       </c>
       <c r="AS13" t="n">
-        <v>-2327.7076165584</v>
+        <v>-0.02327707616481722</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000005</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.0000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>119.9916951661322</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="K14" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="L14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>120.001307539296</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="R14" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2383793660995245</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="V14" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="W14" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="X14" t="n">
-        <v>-119.9916951661322</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6603494433687225</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AC14" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="AD14" t="n">
-        <v>-120.001307539296</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="AE14" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AI14" t="n">
-        <v>309.8868051251302</v>
+        <v>0.003098868051357451</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-309.8868051271218</v>
+        <v>-0.00309886805127513</v>
       </c>
       <c r="AK14" t="n">
-        <v>-2.410522176876903e-11</v>
+        <v>-6.724768271676742e-17</v>
       </c>
       <c r="AL14" t="n">
-        <v>1594.71973438634</v>
+        <v>0.01594719734385297</v>
       </c>
       <c r="AM14" t="n">
-        <v>1594.719734381884</v>
+        <v>0.01594719734403593</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AO14" t="n">
-        <v>-309.8868051251302</v>
+        <v>-0.003098868051357451</v>
       </c>
       <c r="AP14" t="n">
-        <v>309.8868051271218</v>
+        <v>0.00309886805127513</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.410522176876903e-11</v>
+        <v>6.724768271676742e-17</v>
       </c>
       <c r="AR14" t="n">
-        <v>264.6010963763609</v>
+        <v>0.002646010963797804</v>
       </c>
       <c r="AS14" t="n">
-        <v>264.6010963688896</v>
+        <v>0.002646010964108547</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G15" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-28440000</v>
+        <v>-284.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-6000000000</v>
+        <v>-60000</v>
       </c>
       <c r="J15" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="K15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="L15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="O15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="P15" t="n">
-        <v>120.0013075389503</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="Q15" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="R15" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="V15" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="W15" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="X15" t="n">
-        <v>-119.9916951658417</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="AC15" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="AD15" t="n">
-        <v>-120.0013075389503</v>
+        <v>-0.001200013075389576</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2383793661013374</v>
+        <v>2.383793660882689e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AI15" t="n">
-        <v>-309.8868051250465</v>
+        <v>-0.00309886805114401</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-309.8868051299721</v>
+        <v>-0.003098868051247916</v>
       </c>
       <c r="AK15" t="n">
-        <v>-2.409488232592988e-11</v>
+        <v>-6.745272321585572e-17</v>
       </c>
       <c r="AL15" t="n">
-        <v>1594.719734390186</v>
+        <v>0.0159471973437427</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1594.719734376107</v>
+        <v>-0.01594719734354322</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AO15" t="n">
-        <v>309.8868051250465</v>
+        <v>0.00309886805114401</v>
       </c>
       <c r="AP15" t="n">
-        <v>309.8868051299721</v>
+        <v>0.003098868051247916</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.409488232592988e-11</v>
+        <v>6.745272321585572e-17</v>
       </c>
       <c r="AR15" t="n">
-        <v>264.6010963896686</v>
+        <v>0.002646010963744572</v>
       </c>
       <c r="AS15" t="n">
-        <v>-264.6010963741574</v>
+        <v>-0.002646010963320955</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G16" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999998</v>
       </c>
       <c r="J16" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="K16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="L16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="M16" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="Q16" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="R16" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="V16" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="W16" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="X16" t="n">
-        <v>119.991695166331</v>
+        <v>0.001199916951663713</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.660349443347221</v>
+        <v>-6.603494433789558e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="AD16" t="n">
-        <v>120.0013075395739</v>
+        <v>0.001200013075395668</v>
       </c>
       <c r="AE16" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2383793661078827</v>
+        <v>2.383793660920645e-06</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-309.8868051309946</v>
+        <v>-0.003098868051177428</v>
       </c>
       <c r="AJ16" t="n">
-        <v>309.8868051201698</v>
+        <v>0.003098868051253503</v>
       </c>
       <c r="AK16" t="n">
-        <v>-2.411927784824087e-11</v>
+        <v>-6.803347718465976e-17</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1594.719734367751</v>
+        <v>-0.01594719734383659</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1594.719734389742</v>
+        <v>-0.01594719734361782</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>309.8868051309946</v>
+        <v>0.003098868051177428</v>
       </c>
       <c r="AP16" t="n">
-        <v>-309.8868051201698</v>
+        <v>-0.003098868051253503</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.411927784824087e-11</v>
+        <v>6.803347718465976e-17</v>
       </c>
       <c r="AR16" t="n">
-        <v>-264.6010963532681</v>
+        <v>-0.002646010963684871</v>
       </c>
       <c r="AS16" t="n">
-        <v>-264.601096396189</v>
+        <v>-0.002646010963446743</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.00000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="K17" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="L17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="O17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="R17" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S17" t="n">
-        <v>0.238379366093001</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="U17" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="V17" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="W17" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="X17" t="n">
-        <v>119.9916951660405</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6603494433809615</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="AB17" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AC17" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="AD17" t="n">
-        <v>120.0013075392282</v>
+        <v>0.001200013075393904</v>
       </c>
       <c r="AE17" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.238379366093001</v>
+        <v>-2.38379366108843e-06</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AI17" t="n">
-        <v>309.8868051191603</v>
+        <v>0.003098868051323977</v>
       </c>
       <c r="AJ17" t="n">
-        <v>309.886805123052</v>
+        <v>0.003098868051226509</v>
       </c>
       <c r="AK17" t="n">
-        <v>-2.409387806605927e-11</v>
+        <v>-6.727537542781763e-17</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1594.719734371638</v>
+        <v>-0.01594719734372643</v>
       </c>
       <c r="AM17" t="n">
-        <v>1594.719734368206</v>
+        <v>0.01594719734396133</v>
       </c>
       <c r="AN17" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AO17" t="n">
-        <v>-309.8868051191603</v>
+        <v>-0.003098868051323977</v>
       </c>
       <c r="AP17" t="n">
-        <v>-309.886805123052</v>
+        <v>-0.003098868051226509</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.409387806605927e-11</v>
+        <v>6.727537542781763e-17</v>
       </c>
       <c r="AR17" t="n">
-        <v>-264.6010963666739</v>
+        <v>-0.002646010963632412</v>
       </c>
       <c r="AS17" t="n">
-        <v>264.6010963467415</v>
+        <v>0.002646010963982204</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J18" t="n">
-        <v>119.8844950930915</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="K18" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="L18" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.24983693095458</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="N18" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="O18" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="P18" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="Q18" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="R18" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S18" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="T18" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="U18" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="V18" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="W18" t="n">
-        <v>-119.8844950930915</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="X18" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.24983693095458</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="AB18" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="AC18" t="n">
-        <v>-119.8844950930244</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="AD18" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AE18" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AF18" t="n">
-        <v>-13.24983693093416</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AG18" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AH18" t="n">
-        <v>-27374.66294020042</v>
+        <v>-0.2737466294018986</v>
       </c>
       <c r="AI18" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-1.153244166829381e-14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-8.45739123178646e-09</v>
+        <v>1.676783711879182e-13</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.558309120104241e-11</v>
+        <v>1.928795664851712e-16</v>
       </c>
       <c r="AL18" t="n">
-        <v>14707.31899338208</v>
+        <v>0.1470731899328119</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-4.624078897563777e-14</v>
       </c>
       <c r="AN18" t="n">
-        <v>27374.66294020042</v>
+        <v>0.2737466294018986</v>
       </c>
       <c r="AO18" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>1.153244166829381e-14</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.45739123178646e-09</v>
+        <v>-1.676783711879182e-13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>-2.558309120104241e-11</v>
+        <v>-1.928795664851712e-16</v>
       </c>
       <c r="AR18" t="n">
-        <v>-14707.31899331443</v>
+        <v>-0.1470731899341532</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>-4.601874437071274e-14</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861589</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326986</v>
       </c>
       <c r="H19" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705982</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653971</v>
       </c>
       <c r="J19" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="K19" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="L19" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M19" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="N19" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="O19" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="P19" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="Q19" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="R19" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S19" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="U19" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="V19" t="n">
-        <v>119.8844950930244</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="W19" t="n">
-        <v>-119.8844950930202</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="X19" t="n">
-        <v>-180.0000000000003</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.24983693093416</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.24983693093435</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.513274983921015e-12</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AB19" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="AC19" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="AD19" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AE19" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="AF19" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AG19" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AH19" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018418</v>
       </c>
       <c r="AI19" t="n">
-        <v>-9.276845958083868e-11</v>
+        <v>1.16157083951407e-14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8.317329047713429e-09</v>
+        <v>1.147831829584334e-13</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.521716169212596e-11</v>
+        <v>7.600257229123386e-17</v>
       </c>
       <c r="AL19" t="n">
-        <v>14707.31899331497</v>
+        <v>0.1470731899330236</v>
       </c>
       <c r="AM19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>4.651834473179406e-14</v>
       </c>
       <c r="AN19" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018418</v>
       </c>
       <c r="AO19" t="n">
-        <v>9.276845958083868e-11</v>
+        <v>-1.16157083951407e-14</v>
       </c>
       <c r="AP19" t="n">
-        <v>-8.317329047713429e-09</v>
+        <v>-1.147831829584334e-13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-2.521716169212596e-11</v>
+        <v>-7.600257229123386e-17</v>
       </c>
       <c r="AR19" t="n">
-        <v>-14707.31899338152</v>
+        <v>-0.1470731899339416</v>
       </c>
       <c r="AS19" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>4.64628335805628e-14</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H20" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I20" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J20" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="K20" t="n">
-        <v>-119.8844950929513</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="L20" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M20" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="N20" t="n">
-        <v>-13.24983693095439</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="O20" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="P20" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="Q20" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="R20" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S20" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="U20" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="V20" t="n">
-        <v>119.8844950929513</v>
+        <v>0.001198844950931721</v>
       </c>
       <c r="W20" t="n">
-        <v>-119.8844950931343</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="X20" t="n">
-        <v>-180</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.24983693095439</v>
+        <v>0.0001324983693095816</v>
       </c>
       <c r="Z20" t="n">
-        <v>13.24983693092235</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="AA20" t="n">
-        <v>8.510261567519426e-12</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AB20" t="n">
-        <v>-119.8844950932074</v>
+        <v>-0.001198844950929866</v>
       </c>
       <c r="AC20" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="AD20" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AE20" t="n">
-        <v>13.24983693094242</v>
+        <v>0.0001324983693094913</v>
       </c>
       <c r="AF20" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="AG20" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="AH20" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294020123</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>-1.160183060733289e-14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.831995177781209e-08</v>
+        <v>-1.380145997487148e-13</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.55582222052908e-11</v>
+        <v>1.92825356376547e-16</v>
       </c>
       <c r="AL20" t="n">
-        <v>14707.31899327498</v>
+        <v>0.1470731899340347</v>
       </c>
       <c r="AM20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
       <c r="AN20" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294020123</v>
       </c>
       <c r="AO20" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>1.160183060733289e-14</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1.831995177781209e-08</v>
+        <v>1.380145997487148e-13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>-2.55582222052908e-11</v>
+        <v>-1.92825356376547e-16</v>
       </c>
       <c r="AR20" t="n">
-        <v>-14707.31899342155</v>
+        <v>-0.1470731899329306</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-4.629630012686903e-14</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326984</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.33705981</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J21" t="n">
-        <v>-119.8844950930671</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="K21" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="L21" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.24983693096641</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="O21" t="n">
-        <v>8.510392338635117e-12</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="P21" t="n">
-        <v>119.8844950930915</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="Q21" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="R21" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S21" t="n">
-        <v>-13.24983693095458</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="T21" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="U21" t="n">
-        <v>8.506228303696583e-12</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="V21" t="n">
-        <v>119.8844950930671</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="W21" t="n">
-        <v>119.8844950932074</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="X21" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001800000000000005</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.24983693096641</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="Z21" t="n">
-        <v>-13.24983693094242</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AA21" t="n">
-        <v>-8.510392338635117e-12</v>
+        <v>-4.335300855076827e-17</v>
       </c>
       <c r="AB21" t="n">
-        <v>-119.8844950930915</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="AC21" t="n">
-        <v>119.8844950931384</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="AD21" t="n">
-        <v>179.9999999999999</v>
+        <v>0.001800000000000005</v>
       </c>
       <c r="AE21" t="n">
-        <v>13.24983693095458</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.24983693094634</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AG21" t="n">
-        <v>-8.506228303696583e-12</v>
+        <v>-4.314413255415275e-17</v>
       </c>
       <c r="AH21" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294019555</v>
       </c>
       <c r="AI21" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-1.162958618294851e-14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-1.627086021471769e-09</v>
+        <v>3.953781746446339e-14</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.524203068787756e-11</v>
+        <v>7.605678239985814e-17</v>
       </c>
       <c r="AL21" t="n">
-        <v>-14707.31899334175</v>
+        <v>-0.1470731899336408</v>
       </c>
       <c r="AM21" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-4.668487818548783e-14</v>
       </c>
       <c r="AN21" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294019555</v>
       </c>
       <c r="AO21" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>1.162958618294851e-14</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.627086021471769e-09</v>
+        <v>-3.953781746446339e-14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>-2.524203068787756e-11</v>
+        <v>-7.605678239985814e-17</v>
       </c>
       <c r="AR21" t="n">
-        <v>14707.31899335478</v>
+        <v>0.1470731899333244</v>
       </c>
       <c r="AS21" t="n">
-        <v>3.92901711165905e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H22" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J22" t="n">
-        <v>120.039098701767</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="K22" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="L22" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="O22" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="P22" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="R22" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="U22" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="W22" t="n">
-        <v>-120.039098701767</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="X22" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="Z22" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="AB22" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="AC22" t="n">
-        <v>-120.0390987015889</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="AD22" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="AE22" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.917176071126454</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AH22" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="AI22" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-7.940798241179436e-09</v>
+        <v>1.999719834167024e-13</v>
       </c>
       <c r="AK22" t="n">
-        <v>3.044675622732029e-11</v>
+        <v>1.989104410696219e-16</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3238.065438907926</v>
+        <v>-0.03238065439019683</v>
       </c>
       <c r="AM22" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>-1.563749130184533e-13</v>
       </c>
       <c r="AN22" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="AO22" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.940798241179436e-09</v>
+        <v>-1.999719834167024e-13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>-3.044675622732029e-11</v>
+        <v>-1.989104410696219e-16</v>
       </c>
       <c r="AR22" t="n">
-        <v>3238.065438971422</v>
+        <v>0.03238065438859682</v>
       </c>
       <c r="AS22" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>-1.562638907159908e-13</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G23" t="n">
-        <v>-30.00977467543448</v>
+        <v>-0.0003000977467543447</v>
       </c>
       <c r="H23" t="n">
-        <v>-28449266.39231189</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I23" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086893</v>
       </c>
       <c r="J23" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="L23" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="P23" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="Q23" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="R23" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="U23" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>120.0390987015889</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="W23" t="n">
-        <v>-120.0390987015913</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="X23" t="n">
-        <v>-360.0000000000005</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.917176071126454</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="Z23" t="n">
-        <v>-2.917176071128754</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.210194962324305e-11</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AB23" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="AC23" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="AD23" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="AE23" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AH23" t="n">
-        <v>9266.392311885953</v>
+        <v>0.09266392311866412</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.473381416872144e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>9.896666597342119e-09</v>
+        <v>1.138637795161657e-13</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.933653320269514e-11</v>
+        <v>1.280984866791623e-16</v>
       </c>
       <c r="AL23" t="n">
-        <v>-3238.065438979261</v>
+        <v>-0.03238065438985234</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>1.564859353209158e-13</v>
       </c>
       <c r="AN23" t="n">
-        <v>-9266.392311885953</v>
+        <v>-0.09266392311866412</v>
       </c>
       <c r="AO23" t="n">
-        <v>-1.473381416872144e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="AP23" t="n">
-        <v>-9.896666597342119e-09</v>
+        <v>-1.138637795161657e-13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-2.933653320269514e-11</v>
+        <v>-1.280984866791623e-16</v>
       </c>
       <c r="AR23" t="n">
-        <v>3238.065438900087</v>
+        <v>0.03238065438894119</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.893525667488575e-10</v>
+        <v>1.56319401867222e-13</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543449</v>
       </c>
       <c r="H24" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086897</v>
       </c>
       <c r="J24" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.0390987014159</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="L24" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.917176071104874</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="O24" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="P24" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="Q24" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="R24" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="U24" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="V24" t="n">
-        <v>120.0390987014159</v>
+        <v>0.001200390987019827</v>
       </c>
       <c r="W24" t="n">
-        <v>-120.039098701887</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="X24" t="n">
-        <v>-360.0000000000001</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="Y24" t="n">
-        <v>-2.917176071104874</v>
+        <v>-2.917176071103165e-05</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.917176071140197</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.210257034511645e-11</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AB24" t="n">
-        <v>-120.0390987020598</v>
+        <v>-0.001200390987014932</v>
       </c>
       <c r="AC24" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="AD24" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>-2.917176071119162</v>
+        <v>-2.917176071112471e-05</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="AH24" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311883465</v>
       </c>
       <c r="AI24" t="n">
-        <v>-1.455191522836685e-10</v>
+        <v>-3.903821710338207e-14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.939906724146567e-08</v>
+        <v>-1.501750113153122e-13</v>
       </c>
       <c r="AK24" t="n">
-        <v>3.04991587540826e-11</v>
+        <v>1.986393905265005e-16</v>
       </c>
       <c r="AL24" t="n">
-        <v>-3238.065439017271</v>
+        <v>-0.032380654388796</v>
       </c>
       <c r="AM24" t="n">
-        <v>-5.820766091346741e-10</v>
+        <v>-1.562083795647595e-13</v>
       </c>
       <c r="AN24" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311883465</v>
       </c>
       <c r="AO24" t="n">
-        <v>1.455191522836685e-10</v>
+        <v>3.903821710338207e-14</v>
       </c>
       <c r="AP24" t="n">
-        <v>-1.939906724146567e-08</v>
+        <v>1.501750113153122e-13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-3.04991587540826e-11</v>
+        <v>-1.986393905265005e-16</v>
       </c>
       <c r="AR24" t="n">
-        <v>3238.065438862105</v>
+        <v>0.03238065438999761</v>
       </c>
       <c r="AS24" t="n">
-        <v>-5.748006515204906e-10</v>
+        <v>-1.560418461110658e-13</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G25" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H25" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J25" t="n">
-        <v>-120.0390987017087</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="K25" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="L25" t="n">
-        <v>-359.9999999999997</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>2.917176071093494</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.210527673673511e-11</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="P25" t="n">
-        <v>120.039098701767</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="Q25" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="R25" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>2.917176071107192</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="U25" t="n">
-        <v>2.209591840121953e-11</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>120.0390987017087</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="W25" t="n">
-        <v>120.0390987020598</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="X25" t="n">
-        <v>359.9999999999997</v>
+        <v>0.00360000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>-2.917176071093494</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.917176071119162</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AA25" t="n">
-        <v>-2.210527673673511e-11</v>
+        <v>-1.176627274838199e-16</v>
       </c>
       <c r="AB25" t="n">
-        <v>-120.039098701767</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="AC25" t="n">
-        <v>120.0390987018845</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="AD25" t="n">
-        <v>359.9999999999998</v>
+        <v>0.00360000000000001</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.917176071107192</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AF25" t="n">
-        <v>-2.917176071114491</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AG25" t="n">
-        <v>-2.209591840121953e-11</v>
+        <v>-1.176001070613948e-16</v>
       </c>
       <c r="AH25" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="AI25" t="n">
-        <v>-1.491571310907602e-10</v>
+        <v>-3.907985046680551e-14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>-1.949956640601158e-09</v>
+        <v>3.622623034882366e-14</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.923972175494782e-11</v>
+        <v>1.278680937175092e-16</v>
       </c>
       <c r="AL25" t="n">
-        <v>3238.065438947485</v>
+        <v>0.03238065438925182</v>
       </c>
       <c r="AM25" t="n">
-        <v>-6.111804395914078e-10</v>
+        <v>-1.564304241696846e-13</v>
       </c>
       <c r="AN25" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="AO25" t="n">
-        <v>1.491571310907602e-10</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.949956640601158e-09</v>
+        <v>-3.622623034882366e-14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-2.923972175494782e-11</v>
+        <v>-1.278680937175092e-16</v>
       </c>
       <c r="AR25" t="n">
-        <v>-3238.065438931885</v>
+        <v>-0.03238065438954182</v>
       </c>
       <c r="AS25" t="n">
-        <v>-5.966285243630409e-10</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321729</v>
       </c>
       <c r="G26" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.0002999792379152161</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436249</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304321</v>
       </c>
       <c r="J26" t="n">
-        <v>119.9916951661322</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="K26" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="L26" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="O26" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="P26" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="Q26" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="R26" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="U26" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="V26" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="W26" t="n">
-        <v>-119.9916951661322</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="X26" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6603494433687225</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="AB26" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="AC26" t="n">
-        <v>-119.9916951658417</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="AD26" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.6603494433594336</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637522159</v>
       </c>
       <c r="AI26" t="n">
-        <v>-9.094947017729282e-11</v>
+        <v>-3.372302437298913e-14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-3.78480535800918e-09</v>
+        <v>1.817729994302297e-13</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.237432461527078e-11</v>
+        <v>4.984280674823205e-17</v>
       </c>
       <c r="AL26" t="n">
-        <v>732.9878821492639</v>
+        <v>0.007329878820614492</v>
       </c>
       <c r="AM26" t="n">
-        <v>-3.637978807091713e-10</v>
+        <v>-1.35003119794419e-13</v>
       </c>
       <c r="AN26" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637522159</v>
       </c>
       <c r="AO26" t="n">
-        <v>9.094947017729282e-11</v>
+        <v>3.372302437298913e-14</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.78480535800918e-09</v>
+        <v>-1.817729994302297e-13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-2.237432461527078e-11</v>
+        <v>-4.984280674823205e-17</v>
       </c>
       <c r="AR26" t="n">
-        <v>-732.987882118985</v>
+        <v>-0.007329878822068229</v>
       </c>
       <c r="AS26" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.348365863407253e-13</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J27" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="L27" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="O27" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="P27" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="Q27" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="R27" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="S27" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="U27" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="V27" t="n">
-        <v>119.9916951658417</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="W27" t="n">
-        <v>-119.9916951658776</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="X27" t="n">
-        <v>-540.0000000000006</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.6603494433594336</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.6603494433538359</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.619989852775904e-11</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AB27" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="AC27" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="AD27" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI27" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>3.37924133120282e-14</v>
       </c>
       <c r="AJ27" t="n">
-        <v>8.479389634885592e-09</v>
+        <v>5.07484679279635e-14</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.60691468412233e-11</v>
+        <v>1.548037414401959e-16</v>
       </c>
       <c r="AL27" t="n">
-        <v>732.987882100203</v>
+        <v>0.00732987882113827</v>
       </c>
       <c r="AM27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>1.352806755505753e-13</v>
       </c>
       <c r="AN27" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO27" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>-3.37924133120282e-14</v>
       </c>
       <c r="AP27" t="n">
-        <v>-8.479389634885592e-09</v>
+        <v>-5.07484679279635e-14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-2.60691468412233e-11</v>
+        <v>-1.548037414401959e-16</v>
       </c>
       <c r="AR27" t="n">
-        <v>-732.9878821680668</v>
+        <v>-0.007329878821544254</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.856257535517216e-10</v>
+        <v>1.35003119794419e-13</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321726</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152158</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H28" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304316</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J28" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="K28" t="n">
-        <v>-119.9916951655889</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="L28" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="M28" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.660349443374319</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="O28" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="P28" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="Q28" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="R28" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="U28" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="V28" t="n">
-        <v>119.9916951655889</v>
+        <v>0.001199916951664696</v>
       </c>
       <c r="W28" t="n">
-        <v>-119.991695166331</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="X28" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.660349443374319</v>
+        <v>6.603494433701469e-06</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.660349443347221</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.620102839067906e-11</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AB28" t="n">
-        <v>-119.9916951665838</v>
+        <v>-0.001199916951657032</v>
       </c>
       <c r="AC28" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="AD28" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.6603494433638434</v>
+        <v>6.603494433678052e-06</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1968.245637543499</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI28" t="n">
-        <v>-8.913048077374697e-11</v>
+        <v>-3.380629109983602e-14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.400917426508386e-08</v>
+        <v>-1.213413050593637e-13</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.236144602818513e-11</v>
+        <v>4.998680234926528e-17</v>
       </c>
       <c r="AL28" t="n">
-        <v>732.9878820781033</v>
+        <v>0.00732987882182677</v>
       </c>
       <c r="AM28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.353361867018066e-13</v>
       </c>
       <c r="AN28" t="n">
-        <v>1968.245637543499</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO28" t="n">
-        <v>8.913048077374697e-11</v>
+        <v>3.380629109983602e-14</v>
       </c>
       <c r="AP28" t="n">
-        <v>-1.400917426508386e-08</v>
+        <v>1.213413050593637e-13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-2.236144602818513e-11</v>
+        <v>-4.998680234926528e-17</v>
       </c>
       <c r="AR28" t="n">
-        <v>-732.9878821901764</v>
+        <v>-0.007329878820855593</v>
       </c>
       <c r="AS28" t="n">
-        <v>-3.565219230949879e-10</v>
+        <v>-1.351141420968816e-13</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G29" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H29" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J29" t="n">
-        <v>-119.9916951660405</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="K29" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="L29" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6603494433809615</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="O29" t="n">
-        <v>3.620069469507619e-11</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="P29" t="n">
-        <v>119.9916951661322</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="Q29" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="R29" t="n">
-        <v>-539.9999999999998</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6603494433687225</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="U29" t="n">
-        <v>3.618836610953347e-11</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="V29" t="n">
-        <v>119.9916951660405</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="W29" t="n">
-        <v>119.9916951665838</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="X29" t="n">
-        <v>539.9999999999998</v>
+        <v>0.005400000000000014</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6603494433809615</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.6603494433638434</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AA29" t="n">
-        <v>-3.620069469507619e-11</v>
+        <v>-1.906780182197915e-16</v>
       </c>
       <c r="AB29" t="n">
-        <v>-119.9916951661322</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="AC29" t="n">
-        <v>119.9916951662951</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="AD29" t="n">
-        <v>539.9999999999998</v>
+        <v>0.005400000000000012</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.6603494433687225</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6603494433643176</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AG29" t="n">
-        <v>-3.618836610953347e-11</v>
+        <v>-1.905941100274659e-16</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1968.245637532324</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI29" t="n">
-        <v>-9.822542779147625e-11</v>
+        <v>-3.393119119010635e-14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-1.980993147299159e-10</v>
+        <v>3.120854269456075e-14</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.612554617087426e-11</v>
+        <v>1.546631339709517e-16</v>
       </c>
       <c r="AL29" t="n">
-        <v>-732.9878821333361</v>
+        <v>-0.007329878821466364</v>
       </c>
       <c r="AM29" t="n">
-        <v>-4.001776687800884e-10</v>
+        <v>-1.357802759116566e-13</v>
       </c>
       <c r="AN29" t="n">
-        <v>1968.245637532324</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO29" t="n">
-        <v>9.822542779147625e-11</v>
+        <v>3.393119119010635e-14</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.980993147299159e-10</v>
+        <v>-3.120854269456075e-14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>-2.612554617087426e-11</v>
+        <v>-1.546631339709517e-16</v>
       </c>
       <c r="AR29" t="n">
-        <v>732.9878821349207</v>
+        <v>0.007329878821216248</v>
       </c>
       <c r="AS29" t="n">
-        <v>-3.92901711165905e-10</v>
+        <v>-1.356692536091941e-13</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785245</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481552</v>
+        <v>-0.0003000032688481556</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680511</v>
+        <v>-284.4030988680515</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963103</v>
+        <v>-60000.65376963112</v>
       </c>
       <c r="J30" t="n">
-        <v>120.001307539296</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="K30" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="L30" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2383793660995245</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="O30" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="P30" t="n">
-        <v>120.0013075389503</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="Q30" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="R30" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="U30" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="V30" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="W30" t="n">
-        <v>-120.001307539296</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="X30" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="AB30" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="AC30" t="n">
-        <v>-120.0013075389503</v>
+        <v>-0.001200013075389576</v>
       </c>
       <c r="AD30" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2383793661013374</v>
+        <v>2.383793660882689e-06</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AH30" t="n">
-        <v>309.8868051171303</v>
+        <v>0.00309886805143833</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.205989974550903e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-6.750866532456712e-10</v>
+        <v>9.846290449644357e-14</v>
       </c>
       <c r="AK30" t="n">
-        <v>8.726019906646343e-12</v>
+        <v>-3.246761990120459e-17</v>
       </c>
       <c r="AL30" t="n">
-        <v>-264.6010963687289</v>
+        <v>-0.002646010964108621</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.823959898203611e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
       <c r="AN30" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.00309886805143833</v>
       </c>
       <c r="AO30" t="n">
-        <v>-1.205989974550903e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="AP30" t="n">
-        <v>6.750866532456712e-10</v>
+        <v>-9.846290449644357e-14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>-8.726019906646343e-12</v>
+        <v>3.246761990120459e-17</v>
       </c>
       <c r="AR30" t="n">
-        <v>264.6010963741877</v>
+        <v>0.002646010963320918</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-2.015054789694659e-14</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785243</v>
+        <v>-0.002400026150785244</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481555</v>
       </c>
       <c r="H31" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680514</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963106</v>
+        <v>-60000.65376963108</v>
       </c>
       <c r="J31" t="n">
-        <v>120.0013075389503</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="K31" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="L31" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="O31" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="P31" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="Q31" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="R31" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="U31" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="V31" t="n">
-        <v>120.0013075389503</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="W31" t="n">
-        <v>-120.0013075390368</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="X31" t="n">
-        <v>-720.0000000000006</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.2383793661013374</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.2383793661059732</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.46656679936263e-11</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AB31" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="AC31" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="AD31" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AH31" t="n">
-        <v>309.8868051245809</v>
+        <v>0.003098868051324644</v>
       </c>
       <c r="AI31" t="n">
-        <v>-1.218722900375724e-09</v>
+        <v>5.023759186428833e-15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.557804800242593e-09</v>
+        <v>7.490102288398859e-15</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.397171267569774e-11</v>
+        <v>8.102124250371559e-17</v>
       </c>
       <c r="AL31" t="n">
-        <v>-264.601096389707</v>
+        <v>-0.002646010963744791</v>
       </c>
       <c r="AM31" t="n">
-        <v>-4.874891601502895e-09</v>
+        <v>2.009503674571533e-14</v>
       </c>
       <c r="AN31" t="n">
-        <v>-309.8868051245809</v>
+        <v>-0.003098868051324644</v>
       </c>
       <c r="AO31" t="n">
-        <v>1.218722900375724e-09</v>
+        <v>-5.023759186428833e-15</v>
       </c>
       <c r="AP31" t="n">
-        <v>-4.557804800242593e-09</v>
+        <v>-7.490102288398859e-15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-1.397171267569774e-11</v>
+        <v>-8.102124250371559e-17</v>
       </c>
       <c r="AR31" t="n">
-        <v>264.6010963532444</v>
+        <v>0.00264601096368487</v>
       </c>
       <c r="AS31" t="n">
-        <v>-4.867615643888712e-09</v>
+        <v>2.003952559448408e-14</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481553</v>
       </c>
       <c r="H32" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680512</v>
       </c>
       <c r="I32" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963106</v>
       </c>
       <c r="J32" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="K32" t="n">
-        <v>-120.0013075386678</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="L32" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2383793660949187</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="O32" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="P32" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="R32" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S32" t="n">
-        <v>0.238379366093001</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="T32" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="U32" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="V32" t="n">
-        <v>120.0013075386678</v>
+        <v>0.001200013075397448</v>
       </c>
       <c r="W32" t="n">
-        <v>-120.0013075395739</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="X32" t="n">
-        <v>-720.0000000000001</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.2383793660949187</v>
+        <v>-2.383793660995621e-06</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.2383793661078827</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.46753692562772e-11</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AB32" t="n">
-        <v>-120.0013075398565</v>
+        <v>-0.001200013075387795</v>
       </c>
       <c r="AC32" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="AD32" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.2383793660989685</v>
+        <v>-2.383793660980112e-06</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.238379366093001</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="AH32" t="n">
-        <v>309.8868051208556</v>
+        <v>0.003098868051154113</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.207808963954449e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="AJ32" t="n">
-        <v>6.185530310176546e-09</v>
+        <v>-6.722400414105323e-14</v>
       </c>
       <c r="AK32" t="n">
-        <v>8.644529536638856e-12</v>
+        <v>-3.310458867753982e-17</v>
       </c>
       <c r="AL32" t="n">
-        <v>-264.6010963962013</v>
+        <v>-0.002646010963446374</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.838511813431978e-09</v>
+        <v>-2.031708135064036e-14</v>
       </c>
       <c r="AN32" t="n">
-        <v>-309.8868051208556</v>
+        <v>-0.003098868051154113</v>
       </c>
       <c r="AO32" t="n">
-        <v>-1.207808963954449e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="AP32" t="n">
-        <v>-6.185530310176546e-09</v>
+        <v>6.722400414105323e-14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>-8.644529536638856e-12</v>
+        <v>3.310458867753982e-17</v>
       </c>
       <c r="AR32" t="n">
-        <v>264.6010963467751</v>
+        <v>0.00264601096398372</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.831235855817795e-09</v>
+        <v>-2.037259250187162e-14</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481554</v>
       </c>
       <c r="H33" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680513</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963107</v>
       </c>
       <c r="J33" t="n">
-        <v>-120.0013075392282</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="K33" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="L33" t="n">
-        <v>-720</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="M33" t="n">
-        <v>0.238379366093001</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>4.466611131288079e-11</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="P33" t="n">
-        <v>120.001307539296</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="Q33" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="R33" t="n">
-        <v>-719.9999999999999</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2383793660995245</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>4.465776835261449e-11</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="V33" t="n">
-        <v>120.0013075392282</v>
+        <v>0.001200013075393904</v>
       </c>
       <c r="W33" t="n">
-        <v>120.0013075398565</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="X33" t="n">
-        <v>720</v>
+        <v>0.007200000000000015</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.238379366093001</v>
+        <v>-2.38379366108843e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.2383793660989685</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>-4.466611131288079e-11</v>
+        <v>-2.143153122890248e-16</v>
       </c>
       <c r="AB33" t="n">
-        <v>-120.001307539296</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="AC33" t="n">
-        <v>120.0013075394874</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="AD33" t="n">
-        <v>719.9999999999999</v>
+        <v>0.007200000000000015</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.2383793660995245</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.2383793661018853</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="AG33" t="n">
-        <v>-4.465776835261449e-11</v>
+        <v>-2.14221674225249e-16</v>
       </c>
       <c r="AH33" t="n">
-        <v>309.8868051171303</v>
+        <v>0.0030988680512678</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.229636836796999e-09</v>
+        <v>-5.120903701083535e-15</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.223313006448734e-09</v>
+        <v>2.023619986857295e-14</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.392519433096595e-11</v>
+        <v>8.009628252531389e-17</v>
       </c>
       <c r="AL33" t="n">
-        <v>264.6010963665491</v>
+        <v>0.002646010963633847</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.911271389573812e-09</v>
+        <v>-2.059463710679665e-14</v>
       </c>
       <c r="AN33" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.0030988680512678</v>
       </c>
       <c r="AO33" t="n">
-        <v>-1.229636836796999e-09</v>
+        <v>5.120903701083535e-15</v>
       </c>
       <c r="AP33" t="n">
-        <v>-1.223313006448734e-09</v>
+        <v>-2.023619986857295e-14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>-1.392519433096595e-11</v>
+        <v>-8.009628252531389e-17</v>
       </c>
       <c r="AR33" t="n">
-        <v>-264.6010963763936</v>
+        <v>-0.002646010963795291</v>
       </c>
       <c r="AS33" t="n">
-        <v>4.918547347187996e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/validation_frame_temperature.xlsx
+++ b/outputs/validation_frame_temperature.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>119.8844950930664</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="F6" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="G6" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="H6" t="n">
-        <v>-13.2498369309509</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="I6" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="K6" t="n">
-        <v>247.2743098816599</v>
+        <v>0.002472743098815779</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="F7" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="G7" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="H7" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="I7" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="J7" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="K7" t="n">
-        <v>247.2743098816265</v>
+        <v>0.002472743098816677</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="F8" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="G8" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="I8" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="J8" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="K8" t="n">
-        <v>247.2743098816334</v>
+        <v>0.002472743098817284</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="F9" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="G9" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="I9" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="K9" t="n">
-        <v>247.2743098816708</v>
+        <v>0.00247274309881617</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="F10" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="G10" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.917176071110052</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="K10" t="n">
-        <v>398.018555389402</v>
+        <v>0.003980185553892722</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="F11" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="G11" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="K11" t="n">
-        <v>398.0185553893489</v>
+        <v>0.003980185553894126</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="F12" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="G12" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>398.0185553893626</v>
+        <v>0.003980185553895161</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="F13" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="G13" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="K13" t="n">
-        <v>398.018555389417</v>
+        <v>0.003980185553893303</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>119.9916951660409</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="F14" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="G14" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.6603494433671542</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>566.0353467917755</v>
+        <v>0.005660353467916279</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="F15" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="G15" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="K15" t="n">
-        <v>566.0353467917176</v>
+        <v>0.005660353467917999</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="F16" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="G16" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="K16" t="n">
-        <v>566.0353467917382</v>
+        <v>0.005660353467918954</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="F17" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="G17" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="K17" t="n">
-        <v>566.0353467917868</v>
+        <v>0.00566035346791696</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>120.0013075391888</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="F18" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="G18" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2383793661006169</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>739.730104580234</v>
+        <v>0.007397301045800966</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>120.0013075392201</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="F19" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="G19" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2383793661002568</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="K19" t="n">
-        <v>739.7301045801898</v>
+        <v>0.007397301045802761</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="F20" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="G20" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="K20" t="n">
-        <v>739.7301045802139</v>
+        <v>0.007397301045803481</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="F21" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="G21" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2383793661030328</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="K21" t="n">
-        <v>739.7301045802469</v>
+        <v>0.007397301045801653</v>
       </c>
     </row>
   </sheetData>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>739.7301045802469</v>
+        <v>0.007397301045803481</v>
       </c>
       <c r="D2" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="E2" t="n">
-        <v>120.0013075393455</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="F2" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.00719999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1264,19 +1264,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="D3" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="E3" t="n">
-        <v>120.0390987018195</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="F3" t="n">
-        <v>-360</v>
+        <v>-0.003599999999999993</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0390987018331</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="D4" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="E4" t="n">
-        <v>120.0390987018331</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="F4" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.003599999999999991</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0013075391888</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="E5" t="n">
-        <v>120.0013075394095</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="F5" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>-19766.6294607259</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="C2" t="n">
-        <v>-19766.62946073191</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="D2" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="E2" t="n">
-        <v>69104.76771109938</v>
+        <v>0.6910476771102511</v>
       </c>
       <c r="F2" t="n">
-        <v>-69104.76771107486</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="G2" t="n">
-        <v>1.792584007606996e-12</v>
+        <v>-1.227948388079732e-16</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-19766.62946072676</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="C3" t="n">
-        <v>19766.6294607229</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="E3" t="n">
-        <v>-69104.76771106271</v>
+        <v>-0.6910476771113704</v>
       </c>
       <c r="F3" t="n">
-        <v>-69104.76771107831</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="G3" t="n">
-        <v>1.782190697250626e-12</v>
+        <v>-1.232406124819545e-16</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>19766.62946072804</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="C4" t="n">
-        <v>19766.62946072307</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.352761268615723e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="E4" t="n">
-        <v>-69104.76771106376</v>
+        <v>-0.6910476771112495</v>
       </c>
       <c r="F4" t="n">
-        <v>69104.76771108374</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="G4" t="n">
-        <v>1.790573049363477e-12</v>
+        <v>-1.231034558950431e-16</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>19766.62946072889</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="C5" t="n">
-        <v>-19766.62946073172</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="D5" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="E5" t="n">
-        <v>69104.76771109828</v>
+        <v>0.6910476771103716</v>
       </c>
       <c r="F5" t="n">
-        <v>69104.7677110872</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="G5" t="n">
-        <v>1.803065637637907e-12</v>
+        <v>-1.233893320291097e-16</v>
       </c>
     </row>
   </sheetData>
@@ -1606,52 +1606,52 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G2" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000009</v>
       </c>
       <c r="H2" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I2" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J2" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>-19766.62946073191</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="L2" t="n">
-        <v>19766.6294607259</v>
+        <v>0.1976662946072387</v>
       </c>
       <c r="M2" t="n">
-        <v>1.792584007606996e-12</v>
+        <v>-1.227948388079732e-16</v>
       </c>
       <c r="N2" t="n">
-        <v>-69104.76771107486</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="O2" t="n">
-        <v>-69104.76771109937</v>
+        <v>-0.6910476771102511</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="Q2" t="n">
-        <v>19766.62946073191</v>
+        <v>0.1976662946071376</v>
       </c>
       <c r="R2" t="n">
-        <v>-19766.6294607259</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.792584007606996e-12</v>
+        <v>1.227948388079732e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>-49495.00905328055</v>
+        <v>-0.4949500905327627</v>
       </c>
       <c r="U2" t="n">
-        <v>-49495.00905329204</v>
+        <v>-0.4949500905325742</v>
       </c>
     </row>
     <row r="3">
@@ -1673,52 +1673,52 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-29.99999999999999</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H3" t="n">
-        <v>-28439999.99999999</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I3" t="n">
-        <v>-5999999999.999996</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>19766.6294607229</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="L3" t="n">
-        <v>19766.62946072676</v>
+        <v>0.1976662946071929</v>
       </c>
       <c r="M3" t="n">
-        <v>1.782190697250626e-12</v>
+        <v>-1.232406124819545e-16</v>
       </c>
       <c r="N3" t="n">
-        <v>-69104.76771107831</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="O3" t="n">
-        <v>69104.76771106271</v>
+        <v>0.6910476771113704</v>
       </c>
       <c r="P3" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="Q3" t="n">
-        <v>-19766.6294607229</v>
+        <v>-0.1976662946074107</v>
       </c>
       <c r="R3" t="n">
-        <v>-19766.62946072676</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.782190697250626e-12</v>
+        <v>1.232406124819545e-16</v>
       </c>
       <c r="T3" t="n">
-        <v>-49495.00905328222</v>
+        <v>-0.4949500905326924</v>
       </c>
       <c r="U3" t="n">
-        <v>49495.0090532747</v>
+        <v>0.4949500905330936</v>
       </c>
     </row>
     <row r="4">
@@ -1740,52 +1740,52 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H4" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I4" t="n">
-        <v>-5999999999.999991</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.352761268615723e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="K4" t="n">
-        <v>19766.62946072307</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="L4" t="n">
-        <v>-19766.62946072804</v>
+        <v>-0.1976662946073556</v>
       </c>
       <c r="M4" t="n">
-        <v>1.790573049363477e-12</v>
+        <v>-1.231034558950431e-16</v>
       </c>
       <c r="N4" t="n">
-        <v>69104.76771108374</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="O4" t="n">
-        <v>69104.76771106377</v>
+        <v>0.6910476771112495</v>
       </c>
       <c r="P4" t="n">
-        <v>3.352761268615723e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="Q4" t="n">
-        <v>-19766.62946072307</v>
+        <v>-0.1976662946073792</v>
       </c>
       <c r="R4" t="n">
-        <v>19766.62946072804</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.790573049363477e-12</v>
+        <v>1.231034558950431e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>49495.00905328447</v>
+        <v>0.4949500905329763</v>
       </c>
       <c r="U4" t="n">
-        <v>49495.00905327461</v>
+        <v>0.4949500905330254</v>
       </c>
     </row>
     <row r="5">
@@ -1807,52 +1807,52 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G5" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H5" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I5" t="n">
-        <v>-6000000000</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J5" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="K5" t="n">
-        <v>-19766.62946073173</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="L5" t="n">
-        <v>-19766.62946072889</v>
+        <v>-0.1976662946073095</v>
       </c>
       <c r="M5" t="n">
-        <v>1.803065637637907e-12</v>
+        <v>-1.233893320291097e-16</v>
       </c>
       <c r="N5" t="n">
-        <v>69104.7677110872</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="O5" t="n">
-        <v>-69104.76771109828</v>
+        <v>-0.6910476771103716</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="Q5" t="n">
-        <v>19766.62946073173</v>
+        <v>0.1976662946071689</v>
       </c>
       <c r="R5" t="n">
-        <v>19766.62946072889</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.803065637637907e-12</v>
+        <v>1.233893320291097e-16</v>
       </c>
       <c r="T5" t="n">
-        <v>49495.00905328616</v>
+        <v>0.494950090532905</v>
       </c>
       <c r="U5" t="n">
-        <v>-49495.00905329208</v>
+        <v>-0.494950090532642</v>
       </c>
     </row>
     <row r="6">
@@ -1874,52 +1874,52 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G6" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H6" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I6" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000015</v>
       </c>
       <c r="J6" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>7608.03347946563</v>
+        <v>0.07608033479482673</v>
       </c>
       <c r="L6" t="n">
-        <v>-7608.033479471618</v>
+        <v>-0.07608033479472942</v>
       </c>
       <c r="M6" t="n">
-        <v>3.393530821440233e-12</v>
+        <v>-2.119131582129195e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>34787.69005993984</v>
+        <v>0.3478769005994383</v>
       </c>
       <c r="O6" t="n">
-        <v>34787.690059922</v>
+        <v>0.3478769005997626</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q6" t="n">
-        <v>-7608.03347946563</v>
+        <v>-0.07608033479482673</v>
       </c>
       <c r="R6" t="n">
-        <v>7608.033479471618</v>
+        <v>0.07608033479472942</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.393530821440233e-12</v>
+        <v>2.119131582129195e-16</v>
       </c>
       <c r="T6" t="n">
-        <v>10860.51081688989</v>
+        <v>0.1086051081689382</v>
       </c>
       <c r="U6" t="n">
-        <v>10860.51081687179</v>
+        <v>0.1086051081691977</v>
       </c>
     </row>
     <row r="7">
@@ -1941,52 +1941,52 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0002999999999999993</v>
       </c>
       <c r="H7" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.3999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>-5999999999.999995</v>
+        <v>-59999.99999999986</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="K7" t="n">
-        <v>-7608.033479474256</v>
+        <v>-0.07608033479457235</v>
       </c>
       <c r="L7" t="n">
-        <v>-7608.033479470603</v>
+        <v>-0.07608033479480569</v>
       </c>
       <c r="M7" t="n">
-        <v>3.450695314746986e-12</v>
+        <v>-2.115723902159476e-16</v>
       </c>
       <c r="N7" t="n">
-        <v>34787.69005993747</v>
+        <v>0.3478769005996691</v>
       </c>
       <c r="O7" t="n">
-        <v>-34787.69005994825</v>
+        <v>-0.3478769005989404</v>
       </c>
       <c r="P7" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="Q7" t="n">
-        <v>7608.033479474256</v>
+        <v>0.07608033479457235</v>
       </c>
       <c r="R7" t="n">
-        <v>7608.033479470603</v>
+        <v>0.07608033479480569</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.450695314746986e-12</v>
+        <v>2.115723902159476e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>10860.51081688613</v>
+        <v>0.1086051081691652</v>
       </c>
       <c r="U7" t="n">
-        <v>-10860.51081689728</v>
+        <v>-0.1086051081684936</v>
       </c>
     </row>
     <row r="8">
@@ -2008,52 +2008,52 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-29.99999999999995</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28439999.99999995</v>
+        <v>-284.3999999999996</v>
       </c>
       <c r="I8" t="n">
-        <v>-5999999999.99999</v>
+        <v>-59999.99999999991</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="K8" t="n">
-        <v>-7608.03347947371</v>
+        <v>-0.07608033479458301</v>
       </c>
       <c r="L8" t="n">
-        <v>7608.033479469254</v>
+        <v>0.07608033479459361</v>
       </c>
       <c r="M8" t="n">
-        <v>3.346394768910892e-12</v>
+        <v>-2.113669821224497e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>-34787.69005993268</v>
+        <v>-0.3478769005990348</v>
       </c>
       <c r="O8" t="n">
-        <v>-34787.69005994567</v>
+        <v>-0.3478769005989906</v>
       </c>
       <c r="P8" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="Q8" t="n">
-        <v>7608.03347947371</v>
+        <v>0.07608033479458301</v>
       </c>
       <c r="R8" t="n">
-        <v>-7608.033479469254</v>
+        <v>-0.07608033479459361</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.346394768910892e-12</v>
+        <v>2.113669821224497e-16</v>
       </c>
       <c r="T8" t="n">
-        <v>-10860.51081688284</v>
+        <v>-0.1086051081685271</v>
       </c>
       <c r="U8" t="n">
-        <v>-10860.51081689657</v>
+        <v>-0.1086051081685075</v>
       </c>
     </row>
     <row r="9">
@@ -2075,52 +2075,52 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G9" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H9" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999999</v>
+        <v>-60000.00000000016</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K9" t="n">
-        <v>7608.033479466165</v>
+        <v>0.07608033479481566</v>
       </c>
       <c r="L9" t="n">
-        <v>7608.033479468249</v>
+        <v>0.07608033479466958</v>
       </c>
       <c r="M9" t="n">
-        <v>3.392131079729449e-12</v>
+        <v>-2.114968923479162e-16</v>
       </c>
       <c r="N9" t="n">
-        <v>-34787.69005993038</v>
+        <v>-0.3478769005992646</v>
       </c>
       <c r="O9" t="n">
-        <v>34787.69005992453</v>
+        <v>0.3478769005997115</v>
       </c>
       <c r="P9" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7608.033479466165</v>
+        <v>-0.07608033479481566</v>
       </c>
       <c r="R9" t="n">
-        <v>-7608.033479468249</v>
+        <v>-0.07608033479466958</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.392131079729449e-12</v>
+        <v>2.114968923479162e-16</v>
       </c>
       <c r="T9" t="n">
-        <v>-10860.51081687913</v>
+        <v>-0.1086051081687528</v>
       </c>
       <c r="U9" t="n">
-        <v>10860.51081687245</v>
+        <v>0.1086051081691825</v>
       </c>
     </row>
     <row r="10">
@@ -2142,52 +2142,52 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000003</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.00000000005</v>
       </c>
       <c r="J10" t="n">
-        <v>4.470348358154297e-08</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>-1658.358832413913</v>
+        <v>-0.01658358832394202</v>
       </c>
       <c r="L10" t="n">
-        <v>1658.358832409609</v>
+        <v>0.01658358832407774</v>
       </c>
       <c r="M10" t="n">
-        <v>3.927541217236775e-12</v>
+        <v>-2.077521622880486e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>-7622.445377944154</v>
+        <v>-0.07622445377939645</v>
       </c>
       <c r="O10" t="n">
-        <v>-7622.445377954864</v>
+        <v>-0.07622445377900067</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.470348358154297e-08</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1658.358832413913</v>
+        <v>0.01658358832394202</v>
       </c>
       <c r="R10" t="n">
-        <v>-1658.358832409609</v>
+        <v>-0.01658358832407774</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.927541217236775e-12</v>
+        <v>2.077521622880486e-16</v>
       </c>
       <c r="T10" t="n">
-        <v>-2327.707616513508</v>
+        <v>-0.02327707616506976</v>
       </c>
       <c r="U10" t="n">
-        <v>-2327.707616528598</v>
+        <v>-0.02327707616465158</v>
       </c>
     </row>
     <row r="11">
@@ -2209,52 +2209,52 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H11" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.3999999999995</v>
       </c>
       <c r="I11" t="n">
-        <v>-5999999999.999991</v>
+        <v>-59999.9999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.725290298461914e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>1658.358832405404</v>
+        <v>0.01658358832425133</v>
       </c>
       <c r="L11" t="n">
-        <v>1658.358832408467</v>
+        <v>0.01658358832403251</v>
       </c>
       <c r="M11" t="n">
-        <v>3.882815524963767e-12</v>
+        <v>-2.0804665930623e-16</v>
       </c>
       <c r="N11" t="n">
-        <v>-7622.445377941214</v>
+        <v>-0.07622445377931243</v>
       </c>
       <c r="O11" t="n">
-        <v>7622.445377934841</v>
+        <v>0.07622445377989695</v>
       </c>
       <c r="P11" t="n">
-        <v>3.725290298461914e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1658.358832405404</v>
+        <v>-0.01658358832425133</v>
       </c>
       <c r="R11" t="n">
-        <v>-1658.358832408467</v>
+        <v>-0.01658358832403251</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.882815524963767e-12</v>
+        <v>2.0804665930623e-16</v>
       </c>
       <c r="T11" t="n">
-        <v>-2327.707616509579</v>
+        <v>-0.02327707616488241</v>
       </c>
       <c r="U11" t="n">
-        <v>2327.707616497588</v>
+        <v>0.02327707616561103</v>
       </c>
     </row>
     <row r="12">
@@ -2276,52 +2276,52 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0002999999999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.3999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>-5999999999.999995</v>
+        <v>-59999.99999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="K12" t="n">
-        <v>1658.358832407139</v>
+        <v>0.01658358832419271</v>
       </c>
       <c r="L12" t="n">
-        <v>-1658.35883241082</v>
+        <v>-0.01658358832416097</v>
       </c>
       <c r="M12" t="n">
-        <v>4.023333503681037e-12</v>
+        <v>-2.076096844797136e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>7622.445377948388</v>
+        <v>0.07622445377958545</v>
       </c>
       <c r="O12" t="n">
-        <v>7622.445377940967</v>
+        <v>0.07622445377971176</v>
       </c>
       <c r="P12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1658.358832407139</v>
+        <v>-0.01658358832419271</v>
       </c>
       <c r="R12" t="n">
-        <v>1658.35883241082</v>
+        <v>0.01658358832416097</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.023333503681037e-12</v>
+        <v>2.076096844797136e-16</v>
       </c>
       <c r="T12" t="n">
-        <v>2327.707616516534</v>
+        <v>0.02327707616538048</v>
       </c>
       <c r="U12" t="n">
-        <v>2327.707616501837</v>
+        <v>0.02327707616544428</v>
       </c>
     </row>
     <row r="13">
@@ -2343,52 +2343,52 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000004</v>
       </c>
       <c r="G13" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H13" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000014</v>
       </c>
       <c r="J13" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="K13" t="n">
-        <v>-1658.358832412167</v>
+        <v>-0.01658358832400036</v>
       </c>
       <c r="L13" t="n">
-        <v>-1658.358832409711</v>
+        <v>-0.01658358832411552</v>
       </c>
       <c r="M13" t="n">
-        <v>3.889027553857218e-12</v>
+        <v>-2.078127505562269e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>7622.445377945551</v>
+        <v>0.07622445377950053</v>
       </c>
       <c r="O13" t="n">
-        <v>-7622.445377948679</v>
+        <v>-0.07622445377918496</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="Q13" t="n">
-        <v>1658.358832412167</v>
+        <v>0.01658358832400036</v>
       </c>
       <c r="R13" t="n">
-        <v>1658.358832409711</v>
+        <v>0.01658358832411552</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.889027553857218e-12</v>
+        <v>2.078127505562269e-16</v>
       </c>
       <c r="T13" t="n">
-        <v>2327.707616512693</v>
+        <v>0.02327707616519245</v>
       </c>
       <c r="U13" t="n">
-        <v>-2327.707616524305</v>
+        <v>-0.02327707616481722</v>
       </c>
     </row>
     <row r="14">
@@ -2410,52 +2410,52 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000005</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.0000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.470348358154297e-08</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="K14" t="n">
-        <v>309.8868051258833</v>
+        <v>0.003098868051357451</v>
       </c>
       <c r="L14" t="n">
-        <v>-309.8868051280224</v>
+        <v>-0.00309886805127513</v>
       </c>
       <c r="M14" t="n">
-        <v>7.834545089346882e-12</v>
+        <v>-6.724768271676742e-17</v>
       </c>
       <c r="N14" t="n">
-        <v>1594.719734387909</v>
+        <v>0.01594719734385297</v>
       </c>
       <c r="O14" t="n">
-        <v>1594.719734383805</v>
+        <v>0.01594719734403593</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.470348358154297e-08</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="Q14" t="n">
-        <v>-309.8868051258833</v>
+        <v>-0.003098868051357451</v>
       </c>
       <c r="R14" t="n">
-        <v>309.8868051280224</v>
+        <v>0.00309886805127513</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.834545089346882e-12</v>
+        <v>6.724768271676742e-17</v>
       </c>
       <c r="T14" t="n">
-        <v>264.6010963802401</v>
+        <v>0.002646010963797804</v>
       </c>
       <c r="U14" t="n">
-        <v>264.6010963715089</v>
+        <v>0.002646010964108547</v>
       </c>
     </row>
     <row r="15">
@@ -2477,52 +2477,52 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.0018</v>
       </c>
       <c r="G15" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-5999999999.999991</v>
+        <v>-60000</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="K15" t="n">
-        <v>-309.8868051242753</v>
+        <v>-0.00309886805114401</v>
       </c>
       <c r="L15" t="n">
-        <v>-309.8868051258978</v>
+        <v>-0.003098868051247916</v>
       </c>
       <c r="M15" t="n">
-        <v>7.819979700184162e-12</v>
+        <v>-6.745272321585572e-17</v>
       </c>
       <c r="N15" t="n">
-        <v>1594.719734380909</v>
+        <v>0.0159471973437427</v>
       </c>
       <c r="O15" t="n">
-        <v>-1594.719734374157</v>
+        <v>-0.01594719734354322</v>
       </c>
       <c r="P15" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="Q15" t="n">
-        <v>309.8868051242753</v>
+        <v>0.00309886805114401</v>
       </c>
       <c r="R15" t="n">
-        <v>309.8868051258978</v>
+        <v>0.003098868051247916</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.819979700184162e-12</v>
+        <v>6.745272321585572e-17</v>
       </c>
       <c r="T15" t="n">
-        <v>264.6010963744775</v>
+        <v>0.002646010963744572</v>
       </c>
       <c r="U15" t="n">
-        <v>-264.6010963714798</v>
+        <v>-0.002646010963320955</v>
       </c>
     </row>
     <row r="16">
@@ -2544,52 +2544,52 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G16" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999998</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-309.8868051217396</v>
+        <v>-0.003098868051177428</v>
       </c>
       <c r="L16" t="n">
-        <v>309.8868051242207</v>
+        <v>0.003098868051253503</v>
       </c>
       <c r="M16" t="n">
-        <v>7.783451216547496e-12</v>
+        <v>-6.803347718465976e-17</v>
       </c>
       <c r="N16" t="n">
-        <v>-1594.719734376951</v>
+        <v>-0.01594719734383659</v>
       </c>
       <c r="O16" t="n">
-        <v>-1594.719734367216</v>
+        <v>-0.01594719734361782</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>309.8868051217396</v>
+        <v>0.003098868051177428</v>
       </c>
       <c r="R16" t="n">
-        <v>-309.8868051242207</v>
+        <v>-0.003098868051253503</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.783451216547496e-12</v>
+        <v>6.803347718465976e-17</v>
       </c>
       <c r="T16" t="n">
-        <v>-264.6010963683948</v>
+        <v>-0.002646010963684871</v>
       </c>
       <c r="U16" t="n">
-        <v>-264.6010963631998</v>
+        <v>-0.002646010963446743</v>
       </c>
     </row>
     <row r="17">
@@ -2611,52 +2611,52 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="K17" t="n">
-        <v>309.8868051283935</v>
+        <v>0.003098868051323977</v>
       </c>
       <c r="L17" t="n">
-        <v>309.8868051221543</v>
+        <v>0.003098868051226509</v>
       </c>
       <c r="M17" t="n">
-        <v>7.860845011439737e-12</v>
+        <v>-6.727537542781763e-17</v>
       </c>
       <c r="N17" t="n">
-        <v>-1594.719734370112</v>
+        <v>-0.01594719734372643</v>
       </c>
       <c r="O17" t="n">
-        <v>1594.719734390674</v>
+        <v>0.01594719734396133</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="Q17" t="n">
-        <v>-309.8868051283935</v>
+        <v>-0.003098868051323977</v>
       </c>
       <c r="R17" t="n">
-        <v>-309.8868051221543</v>
+        <v>-0.003098868051226509</v>
       </c>
       <c r="S17" t="n">
-        <v>-7.860845011439737e-12</v>
+        <v>6.727537542781763e-17</v>
       </c>
       <c r="T17" t="n">
-        <v>-264.6010963628069</v>
+        <v>-0.002646010963632412</v>
       </c>
       <c r="U17" t="n">
-        <v>264.6010963796871</v>
+        <v>0.002646010963982204</v>
       </c>
     </row>
     <row r="18">
@@ -2678,52 +2678,52 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326984</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.33705981</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J18" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018986</v>
       </c>
       <c r="K18" t="n">
-        <v>2.146407496184111e-10</v>
+        <v>-1.153244166829381e-14</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.453330231830478e-09</v>
+        <v>1.676783711879182e-13</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.561506562415161e-12</v>
+        <v>1.928795664851712e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>14707.31899337007</v>
+        <v>0.1470731899328119</v>
       </c>
       <c r="O18" t="n">
-        <v>8.512870408594608e-10</v>
+        <v>-4.624078897563777e-14</v>
       </c>
       <c r="P18" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018986</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.146407496184111e-10</v>
+        <v>1.153244166829381e-14</v>
       </c>
       <c r="R18" t="n">
-        <v>5.453330231830478e-09</v>
+        <v>-1.676783711879182e-13</v>
       </c>
       <c r="S18" t="n">
-        <v>2.561506562415161e-12</v>
+        <v>-1.928795664851712e-16</v>
       </c>
       <c r="T18" t="n">
-        <v>-14707.31899332644</v>
+        <v>-0.1470731899341532</v>
       </c>
       <c r="U18" t="n">
-        <v>8.585629984736443e-10</v>
+        <v>-4.601874437071274e-14</v>
       </c>
     </row>
     <row r="19">
@@ -2745,52 +2745,52 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861589</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326986</v>
       </c>
       <c r="H19" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705982</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653971</v>
       </c>
       <c r="J19" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018418</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.128217602148652e-10</v>
+        <v>1.16157083951407e-14</v>
       </c>
       <c r="L19" t="n">
-        <v>8.74933903105557e-10</v>
+        <v>1.147831829584334e-13</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.644906433284632e-12</v>
+        <v>7.600257229123386e-17</v>
       </c>
       <c r="N19" t="n">
-        <v>14707.31899334475</v>
+        <v>0.1470731899330236</v>
       </c>
       <c r="O19" t="n">
-        <v>-8.512870408594608e-10</v>
+        <v>4.651834473179406e-14</v>
       </c>
       <c r="P19" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018418</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.128217602148652e-10</v>
+        <v>-1.16157083951407e-14</v>
       </c>
       <c r="R19" t="n">
-        <v>-8.74933903105557e-10</v>
+        <v>-1.147831829584334e-13</v>
       </c>
       <c r="S19" t="n">
-        <v>1.644906433284632e-12</v>
+        <v>-7.600257229123386e-17</v>
       </c>
       <c r="T19" t="n">
-        <v>-14707.31899335176</v>
+        <v>-0.1470731899339416</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.585629984736443e-10</v>
+        <v>4.64628335805628e-14</v>
       </c>
     </row>
     <row r="20">
@@ -2812,52 +2812,52 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H20" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I20" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J20" t="n">
-        <v>-27374.66294020042</v>
+        <v>-0.2737466294020123</v>
       </c>
       <c r="K20" t="n">
-        <v>2.110027708113194e-10</v>
+        <v>-1.160183060733289e-14</v>
       </c>
       <c r="L20" t="n">
-        <v>4.825778887607157e-09</v>
+        <v>-1.380145997487148e-13</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.561506562415161e-12</v>
+        <v>1.92825356376547e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>14707.31899332895</v>
+        <v>0.1470731899340347</v>
       </c>
       <c r="O20" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
       <c r="P20" t="n">
-        <v>27374.66294020042</v>
+        <v>0.2737466294020123</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.110027708113194e-10</v>
+        <v>1.160183060733289e-14</v>
       </c>
       <c r="R20" t="n">
-        <v>-4.825778887607157e-09</v>
+        <v>1.380145997487148e-13</v>
       </c>
       <c r="S20" t="n">
-        <v>2.561506562415161e-12</v>
+        <v>-1.92825356376547e-16</v>
       </c>
       <c r="T20" t="n">
-        <v>-14707.31899336755</v>
+        <v>-0.1470731899329306</v>
       </c>
       <c r="U20" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.629630012686903e-14</v>
       </c>
     </row>
     <row r="21">
@@ -2879,52 +2879,52 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J21" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294019555</v>
       </c>
       <c r="K21" t="n">
-        <v>2.110027708113194e-10</v>
+        <v>-1.162958618294851e-14</v>
       </c>
       <c r="L21" t="n">
-        <v>1.886292011477053e-09</v>
+        <v>3.953781746446339e-14</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.63424829224823e-12</v>
+        <v>7.605678239985814e-17</v>
       </c>
       <c r="N21" t="n">
-        <v>-14707.3189933558</v>
+        <v>-0.1470731899336408</v>
       </c>
       <c r="O21" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.668487818548783e-14</v>
       </c>
       <c r="P21" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294019555</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.110027708113194e-10</v>
+        <v>1.162958618294851e-14</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.886292011477053e-09</v>
+        <v>-3.953781746446339e-14</v>
       </c>
       <c r="S21" t="n">
-        <v>1.63424829224823e-12</v>
+        <v>-7.605678239985814e-17</v>
       </c>
       <c r="T21" t="n">
-        <v>14707.31899334072</v>
+        <v>0.1470731899333244</v>
       </c>
       <c r="U21" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
     </row>
     <row r="22">
@@ -2946,52 +2946,52 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H22" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J22" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="K22" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.697074811905622e-09</v>
+        <v>1.999719834167024e-13</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.53335155473178e-13</v>
+        <v>1.989104410696219e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>-3238.065438916907</v>
+        <v>-0.03238065439019683</v>
       </c>
       <c r="O22" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-1.563749130184533e-13</v>
       </c>
       <c r="P22" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="Q22" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="R22" t="n">
-        <v>5.697074811905622e-09</v>
+        <v>-1.999719834167024e-13</v>
       </c>
       <c r="S22" t="n">
-        <v>5.53335155473178e-13</v>
+        <v>-1.989104410696219e-16</v>
       </c>
       <c r="T22" t="n">
-        <v>3238.065438962483</v>
+        <v>0.03238065438859682</v>
       </c>
       <c r="U22" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-1.562638907159908e-13</v>
       </c>
     </row>
     <row r="23">
@@ -3013,52 +3013,52 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G23" t="n">
-        <v>-30.00977467543448</v>
+        <v>-0.0003000977467543447</v>
       </c>
       <c r="H23" t="n">
-        <v>-28449266.39231189</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I23" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086893</v>
       </c>
       <c r="J23" t="n">
-        <v>9266.392311885953</v>
+        <v>0.09266392311866412</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.01863406598568e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="L23" t="n">
-        <v>1.280568540096283e-09</v>
+        <v>1.138637795161657e-13</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.352962434950314e-12</v>
+        <v>1.280984866791623e-16</v>
       </c>
       <c r="N23" t="n">
-        <v>-3238.065438944817</v>
+        <v>-0.03238065438985234</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.220055416226387e-10</v>
+        <v>1.564859353209158e-13</v>
       </c>
       <c r="P23" t="n">
-        <v>-9266.392311885953</v>
+        <v>-0.09266392311866412</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01863406598568e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.280568540096283e-09</v>
+        <v>-1.138637795161657e-13</v>
       </c>
       <c r="S23" t="n">
-        <v>4.352962434950314e-12</v>
+        <v>-1.280984866791623e-16</v>
       </c>
       <c r="T23" t="n">
-        <v>3238.065438934573</v>
+        <v>0.03238065438894119</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.856257535517216e-10</v>
+        <v>1.56319401867222e-13</v>
       </c>
     </row>
     <row r="24">
@@ -3080,52 +3080,52 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543449</v>
       </c>
       <c r="H24" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086897</v>
       </c>
       <c r="J24" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311883465</v>
       </c>
       <c r="K24" t="n">
-        <v>1.036823960021138e-10</v>
+        <v>-3.903821710338207e-14</v>
       </c>
       <c r="L24" t="n">
-        <v>4.009052645415068e-09</v>
+        <v>-1.501750113153122e-13</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.568878691519785e-13</v>
+        <v>1.986393905265005e-16</v>
       </c>
       <c r="N24" t="n">
-        <v>-3238.065438955702</v>
+        <v>-0.032380654388796</v>
       </c>
       <c r="O24" t="n">
-        <v>4.292814992368221e-10</v>
+        <v>-1.562083795647595e-13</v>
       </c>
       <c r="P24" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311883465</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.036823960021138e-10</v>
+        <v>3.903821710338207e-14</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.009052645415068e-09</v>
+        <v>1.501750113153122e-13</v>
       </c>
       <c r="S24" t="n">
-        <v>5.568878691519785e-13</v>
+        <v>-1.986393905265005e-16</v>
       </c>
       <c r="T24" t="n">
-        <v>3238.065438923659</v>
+        <v>0.03238065438999761</v>
       </c>
       <c r="U24" t="n">
-        <v>4.074536263942719e-10</v>
+        <v>-1.560418461110658e-13</v>
       </c>
     </row>
     <row r="25">
@@ -3147,52 +3147,52 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G25" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H25" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J25" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="K25" t="n">
-        <v>1.073203748092055e-10</v>
+        <v>-3.907985046680551e-14</v>
       </c>
       <c r="L25" t="n">
-        <v>1.506123226135969e-09</v>
+        <v>3.622623034882366e-14</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.338751580235112e-12</v>
+        <v>1.278680937175092e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>3238.065438933641</v>
+        <v>0.03238065438925182</v>
       </c>
       <c r="O25" t="n">
-        <v>4.292814992368221e-10</v>
+        <v>-1.564304241696846e-13</v>
       </c>
       <c r="P25" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.073203748092055e-10</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.506123226135969e-09</v>
+        <v>-3.622623034882366e-14</v>
       </c>
       <c r="S25" t="n">
-        <v>4.338751580235112e-12</v>
+        <v>-1.278680937175092e-16</v>
       </c>
       <c r="T25" t="n">
-        <v>-3238.06543894572</v>
+        <v>-0.03238065438954182</v>
       </c>
       <c r="U25" t="n">
-        <v>4.220055416226387e-10</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="26">
@@ -3214,52 +3214,52 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321729</v>
       </c>
       <c r="G26" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.0002999792379152161</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436249</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304321</v>
       </c>
       <c r="J26" t="n">
-        <v>-1968.245637536049</v>
+        <v>-0.01968245637522159</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.153239281848073e-09</v>
+        <v>-3.372302437298913e-14</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.65572452917695e-09</v>
+        <v>1.817729994302297e-13</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.999733711954832e-12</v>
+        <v>4.984280674823205e-17</v>
       </c>
       <c r="N26" t="n">
-        <v>732.9878821447492</v>
+        <v>0.007329878820614492</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.35003119794419e-13</v>
       </c>
       <c r="P26" t="n">
-        <v>1968.245637536049</v>
+        <v>0.01968245637522159</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.153239281848073e-09</v>
+        <v>3.372302437298913e-14</v>
       </c>
       <c r="R26" t="n">
-        <v>2.65572452917695e-09</v>
+        <v>-1.817729994302297e-13</v>
       </c>
       <c r="S26" t="n">
-        <v>1.999733711954832e-12</v>
+        <v>-4.984280674823205e-17</v>
       </c>
       <c r="T26" t="n">
-        <v>-732.9878821235034</v>
+        <v>-0.007329878822068229</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.348365863407253e-13</v>
       </c>
     </row>
     <row r="27">
@@ -3281,52 +3281,52 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321726</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152158</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304316</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J27" t="n">
-        <v>-1968.245637543499</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K27" t="n">
-        <v>1.142325345426798e-09</v>
+        <v>3.37924133120282e-14</v>
       </c>
       <c r="L27" t="n">
-        <v>1.346052158623934e-09</v>
+        <v>5.07484679279635e-14</v>
       </c>
       <c r="M27" t="n">
-        <v>-7.044365091246618e-12</v>
+        <v>1.548037414401959e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>732.9878821287421</v>
+        <v>0.00732987882113827</v>
       </c>
       <c r="O27" t="n">
-        <v>4.583853296935558e-09</v>
+        <v>1.352806755505753e-13</v>
       </c>
       <c r="P27" t="n">
-        <v>1968.245637543499</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.142325345426798e-09</v>
+        <v>-3.37924133120282e-14</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.346052158623934e-09</v>
+        <v>-5.07484679279635e-14</v>
       </c>
       <c r="S27" t="n">
-        <v>7.044365091246618e-12</v>
+        <v>-1.548037414401959e-16</v>
       </c>
       <c r="T27" t="n">
-        <v>-732.9878821395105</v>
+        <v>-0.007329878821544254</v>
       </c>
       <c r="U27" t="n">
-        <v>4.562025424093008e-09</v>
+        <v>1.35003119794419e-13</v>
       </c>
     </row>
     <row r="28">
@@ -3348,52 +3348,52 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H28" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J28" t="n">
-        <v>-1968.245637536049</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.144144334830344e-09</v>
+        <v>-3.380629109983602e-14</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.091393642127514e-10</v>
+        <v>-1.213413050593637e-13</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.008393451546908e-12</v>
+        <v>4.998680234926528e-17</v>
       </c>
       <c r="N28" t="n">
-        <v>732.9878821345628</v>
+        <v>0.00732987882182677</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.591129254549742e-09</v>
+        <v>-1.353361867018066e-13</v>
       </c>
       <c r="P28" t="n">
-        <v>1968.245637536049</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.144144334830344e-09</v>
+        <v>3.380629109983602e-14</v>
       </c>
       <c r="R28" t="n">
-        <v>1.091393642127514e-10</v>
+        <v>1.213413050593637e-13</v>
       </c>
       <c r="S28" t="n">
-        <v>2.008393451546908e-12</v>
+        <v>-4.998680234926528e-17</v>
       </c>
       <c r="T28" t="n">
-        <v>-732.9878821336897</v>
+        <v>-0.007329878820855593</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.562025424093008e-09</v>
+        <v>-1.351141420968816e-13</v>
       </c>
     </row>
     <row r="29">
@@ -3415,52 +3415,52 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G29" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H29" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J29" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.153239281848073e-09</v>
+        <v>-3.393119119010635e-14</v>
       </c>
       <c r="L29" t="n">
-        <v>2.117303665727377e-09</v>
+        <v>3.120854269456075e-14</v>
       </c>
       <c r="M29" t="n">
-        <v>-7.068345908578522e-12</v>
+        <v>1.546631339709517e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>-732.9878821425955</v>
+        <v>-0.007329878821466364</v>
       </c>
       <c r="O29" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.357802759116566e-13</v>
       </c>
       <c r="P29" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.153239281848073e-09</v>
+        <v>3.393119119010635e-14</v>
       </c>
       <c r="R29" t="n">
-        <v>-2.117303665727377e-09</v>
+        <v>-3.120854269456075e-14</v>
       </c>
       <c r="S29" t="n">
-        <v>7.068345908578522e-12</v>
+        <v>-1.546631339709517e-16</v>
       </c>
       <c r="T29" t="n">
-        <v>732.9878821256571</v>
+        <v>0.007329878821216248</v>
       </c>
       <c r="U29" t="n">
-        <v>-4.605681169778109e-09</v>
+        <v>-1.356692536091941e-13</v>
       </c>
     </row>
     <row r="30">
@@ -3482,52 +3482,52 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785245</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481556</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680515</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963104</v>
+        <v>-60000.65376963112</v>
       </c>
       <c r="J30" t="n">
-        <v>309.8868051171303</v>
+        <v>0.00309886805143833</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.702574081718922e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="L30" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>9.846290449644357e-14</v>
       </c>
       <c r="M30" t="n">
-        <v>-3.771205570046732e-12</v>
+        <v>-3.246761990120459e-17</v>
       </c>
       <c r="N30" t="n">
-        <v>-264.6010963714798</v>
+        <v>-0.002646010964108621</v>
       </c>
       <c r="O30" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
       <c r="P30" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.00309886805143833</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.702574081718922e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>-9.846290449644357e-14</v>
       </c>
       <c r="S30" t="n">
-        <v>3.771205570046732e-12</v>
+        <v>3.246761990120459e-17</v>
       </c>
       <c r="T30" t="n">
-        <v>264.6010963714798</v>
+        <v>0.002646010963320918</v>
       </c>
       <c r="U30" t="n">
-        <v>-6.803020369261503e-09</v>
+        <v>-2.015054789694659e-14</v>
       </c>
     </row>
     <row r="31">
@@ -3549,52 +3549,52 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785244</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481555</v>
       </c>
       <c r="H31" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680514</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963108</v>
       </c>
       <c r="J31" t="n">
-        <v>309.8868051208556</v>
+        <v>0.003098868051324644</v>
       </c>
       <c r="K31" t="n">
-        <v>1.709850039333105e-09</v>
+        <v>5.023759186428833e-15</v>
       </c>
       <c r="L31" t="n">
-        <v>7.712515071034431e-10</v>
+        <v>7.490102288398859e-15</v>
       </c>
       <c r="M31" t="n">
-        <v>-5.13833420257015e-12</v>
+        <v>8.102124250371559e-17</v>
       </c>
       <c r="N31" t="n">
-        <v>-264.6010963745648</v>
+        <v>-0.002646010963744791</v>
       </c>
       <c r="O31" t="n">
-        <v>6.83940015733242e-09</v>
+        <v>2.009503674571533e-14</v>
       </c>
       <c r="P31" t="n">
-        <v>-309.8868051208556</v>
+        <v>-0.003098868051324644</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.709850039333105e-09</v>
+        <v>-5.023759186428833e-15</v>
       </c>
       <c r="R31" t="n">
-        <v>-7.712515071034431e-10</v>
+        <v>-7.490102288398859e-15</v>
       </c>
       <c r="S31" t="n">
-        <v>5.13833420257015e-12</v>
+        <v>-8.102124250371559e-17</v>
       </c>
       <c r="T31" t="n">
-        <v>264.6010963683948</v>
+        <v>0.00264601096368487</v>
       </c>
       <c r="U31" t="n">
-        <v>6.83940015733242e-09</v>
+        <v>2.003952559448408e-14</v>
       </c>
     </row>
     <row r="32">
@@ -3616,52 +3616,52 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481553</v>
       </c>
       <c r="H32" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680512</v>
       </c>
       <c r="I32" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963106</v>
       </c>
       <c r="J32" t="n">
-        <v>309.8868051245809</v>
+        <v>0.003098868051154113</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.704393071122468e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.066371962428093e-09</v>
+        <v>-6.722400414105323e-14</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.82671672127799e-12</v>
+        <v>-3.310458867753982e-17</v>
       </c>
       <c r="N32" t="n">
-        <v>-264.6010963632143</v>
+        <v>-0.002646010963446374</v>
       </c>
       <c r="O32" t="n">
-        <v>-6.81757228448987e-09</v>
+        <v>-2.031708135064036e-14</v>
       </c>
       <c r="P32" t="n">
-        <v>-309.8868051245809</v>
+        <v>-0.003098868051154113</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.704393071122468e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="R32" t="n">
-        <v>2.066371962428093e-09</v>
+        <v>6.722400414105323e-14</v>
       </c>
       <c r="S32" t="n">
-        <v>3.82671672127799e-12</v>
+        <v>3.310458867753982e-17</v>
       </c>
       <c r="T32" t="n">
-        <v>264.6010963797453</v>
+        <v>0.00264601096398372</v>
       </c>
       <c r="U32" t="n">
-        <v>-6.824848242104053e-09</v>
+        <v>-2.037259250187162e-14</v>
       </c>
     </row>
     <row r="33">
@@ -3683,52 +3683,52 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481554</v>
       </c>
       <c r="H33" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680513</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963104</v>
+        <v>-60000.65376963107</v>
       </c>
       <c r="J33" t="n">
-        <v>309.8868051171303</v>
+        <v>0.0030988680512678</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.702574081718922e-09</v>
+        <v>-5.120903701083535e-15</v>
       </c>
       <c r="L33" t="n">
-        <v>2.197339199483395e-09</v>
+        <v>2.023619986857295e-14</v>
       </c>
       <c r="M33" t="n">
-        <v>-5.157096971686315e-12</v>
+        <v>8.009628252531389e-17</v>
       </c>
       <c r="N33" t="n">
-        <v>264.6010963626322</v>
+        <v>0.002646010963633847</v>
       </c>
       <c r="O33" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.059463710679665e-14</v>
       </c>
       <c r="P33" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.0030988680512678</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.702574081718922e-09</v>
+        <v>5.120903701083535e-15</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.197339199483395e-09</v>
+        <v>-2.023619986857295e-14</v>
       </c>
       <c r="S33" t="n">
-        <v>5.157096971686315e-12</v>
+        <v>-8.009628252531389e-17</v>
       </c>
       <c r="T33" t="n">
-        <v>-264.6010963802692</v>
+        <v>-0.002646010963795291</v>
       </c>
       <c r="U33" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3991,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G2" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000009</v>
       </c>
       <c r="H2" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I2" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -4021,22 +4021,22 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>119.8844950930664</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="Q2" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="R2" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S2" t="n">
-        <v>-13.2498369309509</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="T2" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -4057,58 +4057,58 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AC2" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="AD2" t="n">
-        <v>-119.8844950930664</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="AE2" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="AF2" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.2498369309509</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AI2" t="n">
-        <v>-19766.62946073191</v>
+        <v>-0.1976662946071376</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19766.6294607259</v>
+        <v>0.1976662946072387</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.792584007606996e-12</v>
+        <v>-1.227948388079732e-16</v>
       </c>
       <c r="AL2" t="n">
-        <v>-69104.76771107486</v>
+        <v>-0.6910476771106692</v>
       </c>
       <c r="AM2" t="n">
-        <v>-69104.76771109937</v>
+        <v>-0.6910476771102511</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AO2" t="n">
-        <v>19766.62946073191</v>
+        <v>0.1976662946071376</v>
       </c>
       <c r="AP2" t="n">
-        <v>-19766.6294607259</v>
+        <v>-0.1976662946072387</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.792584007606996e-12</v>
+        <v>1.227948388079732e-16</v>
       </c>
       <c r="AR2" t="n">
-        <v>-49495.00905328055</v>
+        <v>-0.4949500905327627</v>
       </c>
       <c r="AS2" t="n">
-        <v>-49495.00905329204</v>
+        <v>-0.4949500905325742</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4130,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>-29.99999999999999</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H3" t="n">
-        <v>-28439999.99999999</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I3" t="n">
-        <v>-5999999999.999996</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -4160,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="Q3" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="R3" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S3" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="T3" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -4196,58 +4196,58 @@
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AC3" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="AD3" t="n">
-        <v>-119.8844950930735</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AG3" t="n">
-        <v>-13.24983693093785</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AH3" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AI3" t="n">
-        <v>19766.6294607229</v>
+        <v>0.1976662946074107</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19766.62946072676</v>
+        <v>0.1976662946071929</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.782190697250626e-12</v>
+        <v>-1.232406124819545e-16</v>
       </c>
       <c r="AL3" t="n">
-        <v>-69104.76771107831</v>
+        <v>-0.6910476771104651</v>
       </c>
       <c r="AM3" t="n">
-        <v>69104.76771106271</v>
+        <v>0.6910476771113704</v>
       </c>
       <c r="AN3" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AO3" t="n">
-        <v>-19766.6294607229</v>
+        <v>-0.1976662946074107</v>
       </c>
       <c r="AP3" t="n">
-        <v>-19766.62946072676</v>
+        <v>-0.1976662946071929</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.782190697250626e-12</v>
+        <v>1.232406124819545e-16</v>
       </c>
       <c r="AR3" t="n">
-        <v>-49495.00905328222</v>
+        <v>-0.4949500905326924</v>
       </c>
       <c r="AS3" t="n">
-        <v>49495.0090532747</v>
+        <v>0.4949500905330936</v>
       </c>
     </row>
     <row r="4">
@@ -4269,16 +4269,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="G4" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0002999999999999992</v>
       </c>
       <c r="H4" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.3999999999992</v>
       </c>
       <c r="I4" t="n">
-        <v>-5999999999.999991</v>
+        <v>-59999.99999999983</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="Q4" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="R4" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S4" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="T4" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -4335,58 +4335,58 @@
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AC4" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="AD4" t="n">
-        <v>119.8844950930851</v>
+        <v>0.001198844950931538</v>
       </c>
       <c r="AE4" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AF4" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AG4" t="n">
-        <v>-13.24983693093862</v>
+        <v>-0.0001324983693096109</v>
       </c>
       <c r="AH4" t="n">
-        <v>-3.352761268615723e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AI4" t="n">
-        <v>19766.62946072307</v>
+        <v>0.1976662946073792</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-19766.62946072804</v>
+        <v>-0.1976662946073556</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.790573049363477e-12</v>
+        <v>-1.231034558950431e-16</v>
       </c>
       <c r="AL4" t="n">
-        <v>69104.76771108374</v>
+        <v>0.6910476771111571</v>
       </c>
       <c r="AM4" t="n">
-        <v>69104.76771106377</v>
+        <v>0.6910476771112495</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.352761268615723e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AO4" t="n">
-        <v>-19766.62946072307</v>
+        <v>-0.1976662946073792</v>
       </c>
       <c r="AP4" t="n">
-        <v>19766.62946072804</v>
+        <v>0.1976662946073556</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1.790573049363477e-12</v>
+        <v>1.231034558950431e-16</v>
       </c>
       <c r="AR4" t="n">
-        <v>49495.00905328447</v>
+        <v>0.4949500905329763</v>
       </c>
       <c r="AS4" t="n">
-        <v>49495.00905327461</v>
+        <v>0.4949500905330254</v>
       </c>
     </row>
     <row r="5">
@@ -4408,16 +4408,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G5" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H5" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I5" t="n">
-        <v>-6000000000</v>
+        <v>-60000.00000000017</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="Q5" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="R5" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S5" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="T5" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="U5" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -4474,58 +4474,58 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AC5" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="AD5" t="n">
-        <v>119.8844950930922</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="AF5" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.24983693095013</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.117587089538574e-08</v>
+        <v>7.958078640513122e-13</v>
       </c>
       <c r="AI5" t="n">
-        <v>-19766.62946073173</v>
+        <v>-0.1976662946071689</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19766.62946072889</v>
+        <v>-0.1976662946073095</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.803065637637907e-12</v>
+        <v>-1.233893320291097e-16</v>
       </c>
       <c r="AL5" t="n">
-        <v>69104.7677110872</v>
+        <v>0.6910476771109521</v>
       </c>
       <c r="AM5" t="n">
-        <v>-69104.76771109828</v>
+        <v>-0.6910476771103716</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1.117587089538574e-08</v>
+        <v>-7.958078640513122e-13</v>
       </c>
       <c r="AO5" t="n">
-        <v>19766.62946073173</v>
+        <v>0.1976662946071689</v>
       </c>
       <c r="AP5" t="n">
-        <v>19766.62946072889</v>
+        <v>0.1976662946073095</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-1.803065637637907e-12</v>
+        <v>1.233893320291097e-16</v>
       </c>
       <c r="AR5" t="n">
-        <v>49495.00905328616</v>
+        <v>0.494950090532905</v>
       </c>
       <c r="AS5" t="n">
-        <v>-49495.00905329208</v>
+        <v>-0.494950090532642</v>
       </c>
     </row>
     <row r="6">
@@ -4547,124 +4547,124 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G6" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H6" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I6" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000015</v>
       </c>
       <c r="J6" t="n">
-        <v>119.8844950930664</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="K6" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="L6" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.2498369309509</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="N6" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="O6" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="P6" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="Q6" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="R6" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>2.917176071110052</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="V6" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="W6" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="X6" t="n">
-        <v>-119.8844950930664</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="Y6" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AA6" t="n">
-        <v>13.2498369309509</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AB6" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="AD6" t="n">
-        <v>-120.0390987017059</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AG6" t="n">
-        <v>-2.917176071110052</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>7608.03347946563</v>
+        <v>0.07608033479482673</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-7608.033479471618</v>
+        <v>-0.07608033479472942</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.393530821440233e-12</v>
+        <v>-2.119131582129195e-16</v>
       </c>
       <c r="AL6" t="n">
-        <v>34787.69005993984</v>
+        <v>0.3478769005994383</v>
       </c>
       <c r="AM6" t="n">
-        <v>34787.690059922</v>
+        <v>0.3478769005997626</v>
       </c>
       <c r="AN6" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>-7608.03347946563</v>
+        <v>-0.07608033479482673</v>
       </c>
       <c r="AP6" t="n">
-        <v>7608.033479471618</v>
+        <v>0.07608033479472942</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.393530821440233e-12</v>
+        <v>2.119131582129195e-16</v>
       </c>
       <c r="AR6" t="n">
-        <v>10860.51081688989</v>
+        <v>0.1086051081689382</v>
       </c>
       <c r="AS6" t="n">
-        <v>10860.51081687179</v>
+        <v>0.1086051081691977</v>
       </c>
     </row>
     <row r="7">
@@ -4686,124 +4686,124 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999996</v>
       </c>
       <c r="G7" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0002999999999999993</v>
       </c>
       <c r="H7" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.3999999999994</v>
       </c>
       <c r="I7" t="n">
-        <v>-5999999999.999995</v>
+        <v>-59999.99999999986</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="K7" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="L7" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M7" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="N7" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="P7" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="R7" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="W7" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="X7" t="n">
-        <v>-119.8844950930735</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="Y7" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AA7" t="n">
-        <v>-13.24983693093785</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AB7" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="AC7" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="AD7" t="n">
-        <v>-120.0390987017214</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="AE7" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.917176071123615</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>-1.490116119384766e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AI7" t="n">
-        <v>-7608.033479474256</v>
+        <v>-0.07608033479457235</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-7608.033479470603</v>
+        <v>-0.07608033479480569</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.450695314746986e-12</v>
+        <v>-2.115723902159476e-16</v>
       </c>
       <c r="AL7" t="n">
-        <v>34787.69005993747</v>
+        <v>0.3478769005996691</v>
       </c>
       <c r="AM7" t="n">
-        <v>-34787.69005994825</v>
+        <v>-0.3478769005989404</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.490116119384766e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AO7" t="n">
-        <v>7608.033479474256</v>
+        <v>0.07608033479457235</v>
       </c>
       <c r="AP7" t="n">
-        <v>7608.033479470603</v>
+        <v>0.07608033479480569</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.450695314746986e-12</v>
+        <v>2.115723902159476e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>10860.51081688613</v>
+        <v>0.1086051081691652</v>
       </c>
       <c r="AS7" t="n">
-        <v>-10860.51081689728</v>
+        <v>-0.1086051081684936</v>
       </c>
     </row>
     <row r="8">
@@ -4825,124 +4825,124 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G8" t="n">
-        <v>-29.99999999999995</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H8" t="n">
-        <v>-28439999.99999995</v>
+        <v>-284.3999999999996</v>
       </c>
       <c r="I8" t="n">
-        <v>-5999999999.99999</v>
+        <v>-59999.99999999991</v>
       </c>
       <c r="J8" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="K8" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="L8" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M8" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="N8" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="P8" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="Q8" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="R8" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="V8" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="W8" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="X8" t="n">
-        <v>119.8844950930851</v>
+        <v>0.001198844950931538</v>
       </c>
       <c r="Y8" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="Z8" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AA8" t="n">
-        <v>-13.24983693093862</v>
+        <v>-0.0001324983693096109</v>
       </c>
       <c r="AB8" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="AC8" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="AD8" t="n">
-        <v>120.0390987017544</v>
+        <v>0.001200390987019375</v>
       </c>
       <c r="AE8" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.917176071121575</v>
+        <v>2.917176071098574e-05</v>
       </c>
       <c r="AH8" t="n">
-        <v>-4.842877388000488e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AI8" t="n">
-        <v>-7608.03347947371</v>
+        <v>-0.07608033479458301</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7608.033479469254</v>
+        <v>0.07608033479459361</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.346394768910892e-12</v>
+        <v>-2.113669821224497e-16</v>
       </c>
       <c r="AL8" t="n">
-        <v>-34787.69005993268</v>
+        <v>-0.3478769005990348</v>
       </c>
       <c r="AM8" t="n">
-        <v>-34787.69005994567</v>
+        <v>-0.3478769005989906</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.842877388000488e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AO8" t="n">
-        <v>7608.03347947371</v>
+        <v>0.07608033479458301</v>
       </c>
       <c r="AP8" t="n">
-        <v>-7608.033479469254</v>
+        <v>-0.07608033479459361</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.346394768910892e-12</v>
+        <v>2.113669821224497e-16</v>
       </c>
       <c r="AR8" t="n">
-        <v>-10860.51081688284</v>
+        <v>-0.1086051081685271</v>
       </c>
       <c r="AS8" t="n">
-        <v>-10860.51081689657</v>
+        <v>-0.1086051081685075</v>
       </c>
     </row>
     <row r="9">
@@ -4964,124 +4964,124 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="G9" t="n">
-        <v>-30</v>
+        <v>-0.0003000000000000008</v>
       </c>
       <c r="H9" t="n">
-        <v>-28440000</v>
+        <v>-284.4000000000008</v>
       </c>
       <c r="I9" t="n">
-        <v>-5999999999.999999</v>
+        <v>-60000.00000000016</v>
       </c>
       <c r="J9" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="K9" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="L9" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="N9" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="P9" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="Q9" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="R9" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="V9" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="W9" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="X9" t="n">
-        <v>119.8844950930922</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="Y9" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="Z9" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AA9" t="n">
-        <v>13.24983693095013</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="AB9" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="AD9" t="n">
-        <v>120.0390987017699</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="AE9" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AG9" t="n">
-        <v>-2.917176071112084</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="AH9" t="n">
-        <v>-3.725290298461914e-09</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI9" t="n">
-        <v>7608.033479466165</v>
+        <v>0.07608033479481566</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7608.033479468249</v>
+        <v>0.07608033479466958</v>
       </c>
       <c r="AK9" t="n">
-        <v>3.392131079729449e-12</v>
+        <v>-2.114968923479162e-16</v>
       </c>
       <c r="AL9" t="n">
-        <v>-34787.69005993038</v>
+        <v>-0.3478769005992646</v>
       </c>
       <c r="AM9" t="n">
-        <v>34787.69005992453</v>
+        <v>0.3478769005997115</v>
       </c>
       <c r="AN9" t="n">
-        <v>3.725290298461914e-09</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO9" t="n">
-        <v>-7608.033479466165</v>
+        <v>-0.07608033479481566</v>
       </c>
       <c r="AP9" t="n">
-        <v>-7608.033479468249</v>
+        <v>-0.07608033479466958</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.392131079729449e-12</v>
+        <v>2.114968923479162e-16</v>
       </c>
       <c r="AR9" t="n">
-        <v>-10860.51081687913</v>
+        <v>-0.1086051081687528</v>
       </c>
       <c r="AS9" t="n">
-        <v>10860.51081687245</v>
+        <v>0.1086051081691825</v>
       </c>
     </row>
     <row r="10">
@@ -5103,124 +5103,124 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000002</v>
       </c>
       <c r="G10" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000003</v>
       </c>
       <c r="H10" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000003</v>
       </c>
       <c r="I10" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.00000000005</v>
       </c>
       <c r="J10" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="K10" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="L10" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>2.917176071110052</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="P10" t="n">
-        <v>119.9916951660409</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="Q10" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="R10" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6603494433671542</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="U10" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="V10" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="X10" t="n">
-        <v>-120.0390987017059</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="Z10" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>-2.917176071110052</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="AC10" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="AD10" t="n">
-        <v>-119.9916951660409</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="AE10" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.6603494433671542</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.470348358154297e-08</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1658.358832413913</v>
+        <v>-0.01658358832394202</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1658.358832409609</v>
+        <v>0.01658358832407774</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.927541217236775e-12</v>
+        <v>-2.077521622880486e-16</v>
       </c>
       <c r="AL10" t="n">
-        <v>-7622.445377944154</v>
+        <v>-0.07622445377939645</v>
       </c>
       <c r="AM10" t="n">
-        <v>-7622.445377954864</v>
+        <v>-0.07622445377900067</v>
       </c>
       <c r="AN10" t="n">
-        <v>-4.470348358154297e-08</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AO10" t="n">
-        <v>1658.358832413913</v>
+        <v>0.01658358832394202</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1658.358832409609</v>
+        <v>-0.01658358832407774</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.927541217236775e-12</v>
+        <v>2.077521622880486e-16</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2327.707616513508</v>
+        <v>-0.02327707616506976</v>
       </c>
       <c r="AS10" t="n">
-        <v>-2327.707616528598</v>
+        <v>-0.02327707616465158</v>
       </c>
     </row>
     <row r="11">
@@ -5242,124 +5242,124 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.001799999999999997</v>
       </c>
       <c r="G11" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0002999999999999995</v>
       </c>
       <c r="H11" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.3999999999995</v>
       </c>
       <c r="I11" t="n">
-        <v>-5999999999.999991</v>
+        <v>-59999.9999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="K11" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="L11" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="P11" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="Q11" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="R11" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="V11" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="W11" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="X11" t="n">
-        <v>-120.0390987017214</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="Z11" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.917176071123615</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="AC11" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="AD11" t="n">
-        <v>-119.9916951660554</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="AE11" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.6603494433610113</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>-3.725290298461914e-08</v>
+        <v>-4.547473508864641e-13</v>
       </c>
       <c r="AI11" t="n">
-        <v>1658.358832405404</v>
+        <v>0.01658358832425133</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1658.358832408467</v>
+        <v>0.01658358832403251</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.882815524963767e-12</v>
+        <v>-2.0804665930623e-16</v>
       </c>
       <c r="AL11" t="n">
-        <v>-7622.445377941214</v>
+        <v>-0.07622445377931243</v>
       </c>
       <c r="AM11" t="n">
-        <v>7622.445377934841</v>
+        <v>0.07622445377989695</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.725290298461914e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1658.358832405404</v>
+        <v>-0.01658358832425133</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1658.358832408467</v>
+        <v>-0.01658358832403251</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.882815524963767e-12</v>
+        <v>2.0804665930623e-16</v>
       </c>
       <c r="AR11" t="n">
-        <v>-2327.707616509579</v>
+        <v>-0.02327707616488241</v>
       </c>
       <c r="AS11" t="n">
-        <v>2327.707616497588</v>
+        <v>0.02327707616561103</v>
       </c>
     </row>
     <row r="12">
@@ -5381,124 +5381,124 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999998</v>
       </c>
       <c r="G12" t="n">
-        <v>-29.99999999999998</v>
+        <v>-0.0002999999999999997</v>
       </c>
       <c r="H12" t="n">
-        <v>-28439999.99999998</v>
+        <v>-284.3999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>-5999999999.999995</v>
+        <v>-59999.99999999993</v>
       </c>
       <c r="J12" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="K12" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="L12" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="P12" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="Q12" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="R12" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="V12" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="W12" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="X12" t="n">
-        <v>120.0390987017544</v>
+        <v>0.001200390987019375</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.917176071121575</v>
+        <v>2.917176071098574e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="AC12" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="AD12" t="n">
-        <v>119.9916951661173</v>
+        <v>0.001199916951663713</v>
       </c>
       <c r="AE12" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.6603494433643113</v>
+        <v>-6.603494433789558e-06</v>
       </c>
       <c r="AH12" t="n">
-        <v>-7.450580596923828e-09</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AI12" t="n">
-        <v>1658.358832407139</v>
+        <v>0.01658358832419271</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-1658.35883241082</v>
+        <v>-0.01658358832416097</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.023333503681037e-12</v>
+        <v>-2.076096844797136e-16</v>
       </c>
       <c r="AL12" t="n">
-        <v>7622.445377948388</v>
+        <v>0.07622445377958545</v>
       </c>
       <c r="AM12" t="n">
-        <v>7622.445377940967</v>
+        <v>0.07622445377971176</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.450580596923828e-09</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1658.358832407139</v>
+        <v>-0.01658358832419271</v>
       </c>
       <c r="AP12" t="n">
-        <v>1658.35883241082</v>
+        <v>0.01658358832416097</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-4.023333503681037e-12</v>
+        <v>2.076096844797136e-16</v>
       </c>
       <c r="AR12" t="n">
-        <v>2327.707616516534</v>
+        <v>0.02327707616538048</v>
       </c>
       <c r="AS12" t="n">
-        <v>2327.707616501837</v>
+        <v>0.02327707616544428</v>
       </c>
     </row>
     <row r="13">
@@ -5520,124 +5520,124 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000004</v>
       </c>
       <c r="G13" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000007</v>
       </c>
       <c r="H13" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000007</v>
       </c>
       <c r="I13" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000014</v>
       </c>
       <c r="J13" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="K13" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="L13" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="N13" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="P13" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="Q13" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="R13" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="V13" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="X13" t="n">
-        <v>120.0390987017699</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="Y13" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>-2.917176071112084</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="AC13" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="AD13" t="n">
-        <v>119.9916951661319</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="AE13" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.6603494433638429</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.235174179077148e-08</v>
+        <v>6.821210263296962e-13</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1658.358832412167</v>
+        <v>-0.01658358832400036</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-1658.358832409711</v>
+        <v>-0.01658358832411552</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.889027553857218e-12</v>
+        <v>-2.078127505562269e-16</v>
       </c>
       <c r="AL13" t="n">
-        <v>7622.445377945551</v>
+        <v>0.07622445377950053</v>
       </c>
       <c r="AM13" t="n">
-        <v>-7622.445377948679</v>
+        <v>-0.07622445377918496</v>
       </c>
       <c r="AN13" t="n">
-        <v>-2.235174179077148e-08</v>
+        <v>-6.821210263296962e-13</v>
       </c>
       <c r="AO13" t="n">
-        <v>1658.358832412167</v>
+        <v>0.01658358832400036</v>
       </c>
       <c r="AP13" t="n">
-        <v>1658.358832409711</v>
+        <v>0.01658358832411552</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-3.889027553857218e-12</v>
+        <v>2.078127505562269e-16</v>
       </c>
       <c r="AR13" t="n">
-        <v>2327.707616512693</v>
+        <v>0.02327707616519245</v>
       </c>
       <c r="AS13" t="n">
-        <v>-2327.707616524305</v>
+        <v>-0.02327707616481722</v>
       </c>
     </row>
     <row r="14">
@@ -5659,124 +5659,124 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>-180.0000000000002</v>
+        <v>-0.001800000000000003</v>
       </c>
       <c r="G14" t="n">
-        <v>-30.00000000000004</v>
+        <v>-0.0003000000000000005</v>
       </c>
       <c r="H14" t="n">
-        <v>-28440000.00000004</v>
+        <v>-284.4000000000005</v>
       </c>
       <c r="I14" t="n">
-        <v>-6000000000.000008</v>
+        <v>-60000.0000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>119.9916951660409</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="K14" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="L14" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6603494433671542</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="P14" t="n">
-        <v>120.0013075391888</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="Q14" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="R14" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2383793661006169</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="V14" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="W14" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="X14" t="n">
-        <v>-119.9916951660409</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="Y14" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.6603494433671542</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AB14" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AC14" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="AD14" t="n">
-        <v>-120.0013075391888</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="AE14" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.2383793661006169</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.470348358154297e-08</v>
+        <v>3.410605131648481e-13</v>
       </c>
       <c r="AI14" t="n">
-        <v>309.8868051258833</v>
+        <v>0.003098868051357451</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-309.8868051280224</v>
+        <v>-0.00309886805127513</v>
       </c>
       <c r="AK14" t="n">
-        <v>7.834545089346882e-12</v>
+        <v>-6.724768271676742e-17</v>
       </c>
       <c r="AL14" t="n">
-        <v>1594.719734387909</v>
+        <v>0.01594719734385297</v>
       </c>
       <c r="AM14" t="n">
-        <v>1594.719734383805</v>
+        <v>0.01594719734403593</v>
       </c>
       <c r="AN14" t="n">
-        <v>-4.470348358154297e-08</v>
+        <v>-3.410605131648481e-13</v>
       </c>
       <c r="AO14" t="n">
-        <v>-309.8868051258833</v>
+        <v>-0.003098868051357451</v>
       </c>
       <c r="AP14" t="n">
-        <v>309.8868051280224</v>
+        <v>0.00309886805127513</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-7.834545089346882e-12</v>
+        <v>6.724768271676742e-17</v>
       </c>
       <c r="AR14" t="n">
-        <v>264.6010963802401</v>
+        <v>0.002646010963797804</v>
       </c>
       <c r="AS14" t="n">
-        <v>264.6010963715089</v>
+        <v>0.002646010964108547</v>
       </c>
     </row>
     <row r="15">
@@ -5798,124 +5798,124 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>-179.9999999999998</v>
+        <v>-0.0018</v>
       </c>
       <c r="G15" t="n">
-        <v>-29.99999999999996</v>
+        <v>-0.0003000000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-28439999.99999996</v>
+        <v>-284.4</v>
       </c>
       <c r="I15" t="n">
-        <v>-5999999999.999991</v>
+        <v>-60000</v>
       </c>
       <c r="J15" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="K15" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="L15" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="P15" t="n">
-        <v>120.0013075392201</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="Q15" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="R15" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2383793661002568</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="U15" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="V15" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="W15" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="X15" t="n">
-        <v>-119.9916951660554</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0.6603494433610113</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AB15" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="AC15" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="AD15" t="n">
-        <v>-120.0013075392201</v>
+        <v>-0.001200013075389576</v>
       </c>
       <c r="AE15" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.2383793661002568</v>
+        <v>2.383793660882689e-06</v>
       </c>
       <c r="AH15" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AI15" t="n">
-        <v>-309.8868051242753</v>
+        <v>-0.00309886805114401</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-309.8868051258978</v>
+        <v>-0.003098868051247916</v>
       </c>
       <c r="AK15" t="n">
-        <v>7.819979700184162e-12</v>
+        <v>-6.745272321585572e-17</v>
       </c>
       <c r="AL15" t="n">
-        <v>1594.719734380909</v>
+        <v>0.0159471973437427</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1594.719734374157</v>
+        <v>-0.01594719734354322</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AO15" t="n">
-        <v>309.8868051242753</v>
+        <v>0.00309886805114401</v>
       </c>
       <c r="AP15" t="n">
-        <v>309.8868051258978</v>
+        <v>0.003098868051247916</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-7.819979700184162e-12</v>
+        <v>6.745272321585572e-17</v>
       </c>
       <c r="AR15" t="n">
-        <v>264.6010963744775</v>
+        <v>0.002646010963744572</v>
       </c>
       <c r="AS15" t="n">
-        <v>-264.6010963714798</v>
+        <v>-0.002646010963320955</v>
       </c>
     </row>
     <row r="16">
@@ -5937,124 +5937,124 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>-180</v>
+        <v>-0.0018</v>
       </c>
       <c r="G16" t="n">
-        <v>-30</v>
+        <v>-0.0002999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-28440000</v>
+        <v>-284.3999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-6000000000</v>
+        <v>-59999.99999999998</v>
       </c>
       <c r="J16" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="K16" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="L16" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="P16" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="Q16" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="R16" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="V16" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="W16" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="X16" t="n">
-        <v>119.9916951661173</v>
+        <v>0.001199916951663713</v>
       </c>
       <c r="Y16" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.6603494433643113</v>
+        <v>-6.603494433789558e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="AD16" t="n">
-        <v>120.0013075393042</v>
+        <v>0.001200013075395668</v>
       </c>
       <c r="AE16" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.2383793660978497</v>
+        <v>2.383793660920645e-06</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-309.8868051217396</v>
+        <v>-0.003098868051177428</v>
       </c>
       <c r="AJ16" t="n">
-        <v>309.8868051242207</v>
+        <v>0.003098868051253503</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.783451216547496e-12</v>
+        <v>-6.803347718465976e-17</v>
       </c>
       <c r="AL16" t="n">
-        <v>-1594.719734376951</v>
+        <v>-0.01594719734383659</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1594.719734367216</v>
+        <v>-0.01594719734361782</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>309.8868051217396</v>
+        <v>0.003098868051177428</v>
       </c>
       <c r="AP16" t="n">
-        <v>-309.8868051242207</v>
+        <v>-0.003098868051253503</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-7.783451216547496e-12</v>
+        <v>6.803347718465976e-17</v>
       </c>
       <c r="AR16" t="n">
-        <v>-264.6010963683948</v>
+        <v>-0.002646010963684871</v>
       </c>
       <c r="AS16" t="n">
-        <v>-264.6010963631998</v>
+        <v>-0.002646010963446743</v>
       </c>
     </row>
     <row r="17">
@@ -6076,124 +6076,124 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-30.00000000000002</v>
+        <v>-0.0003000000000000002</v>
       </c>
       <c r="H17" t="n">
-        <v>-28440000.00000002</v>
+        <v>-284.4000000000002</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000000000.000004</v>
+        <v>-60000.00000000004</v>
       </c>
       <c r="J17" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="K17" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="L17" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="P17" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="Q17" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="R17" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2383793661030328</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="T17" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="V17" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="W17" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="X17" t="n">
-        <v>119.9916951661319</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="Y17" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6603494433638429</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="AB17" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AC17" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="AD17" t="n">
-        <v>120.0013075393354</v>
+        <v>0.001200013075393904</v>
       </c>
       <c r="AE17" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.2383793661030328</v>
+        <v>-2.38379366108843e-06</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.980232238769531e-08</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AI17" t="n">
-        <v>309.8868051283935</v>
+        <v>0.003098868051323977</v>
       </c>
       <c r="AJ17" t="n">
-        <v>309.8868051221543</v>
+        <v>0.003098868051226509</v>
       </c>
       <c r="AK17" t="n">
-        <v>7.860845011439737e-12</v>
+        <v>-6.727537542781763e-17</v>
       </c>
       <c r="AL17" t="n">
-        <v>-1594.719734370112</v>
+        <v>-0.01594719734372643</v>
       </c>
       <c r="AM17" t="n">
-        <v>1594.719734390674</v>
+        <v>0.01594719734396133</v>
       </c>
       <c r="AN17" t="n">
-        <v>-2.980232238769531e-08</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AO17" t="n">
-        <v>-309.8868051283935</v>
+        <v>-0.003098868051323977</v>
       </c>
       <c r="AP17" t="n">
-        <v>-309.8868051221543</v>
+        <v>-0.003098868051226509</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-7.860845011439737e-12</v>
+        <v>6.727537542781763e-17</v>
       </c>
       <c r="AR17" t="n">
-        <v>-264.6010963628069</v>
+        <v>-0.002646010963632412</v>
       </c>
       <c r="AS17" t="n">
-        <v>264.6010963796871</v>
+        <v>0.002646010963982204</v>
       </c>
     </row>
     <row r="18">
@@ -6215,124 +6215,124 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>-239.7689901861587</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G18" t="n">
-        <v>-29.97112377326984</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H18" t="n">
-        <v>-28412625.33705981</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I18" t="n">
-        <v>-5994224754.653967</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J18" t="n">
-        <v>119.8844950930664</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="K18" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="L18" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M18" t="n">
-        <v>-13.2498369309509</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="N18" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="O18" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="P18" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="Q18" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="R18" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S18" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="T18" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="V18" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="W18" t="n">
-        <v>-119.8844950930664</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="X18" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.2498369309509</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AA18" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="AB18" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="AC18" t="n">
-        <v>-119.8844950930735</v>
+        <v>-0.001198844950930051</v>
       </c>
       <c r="AD18" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AE18" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AF18" t="n">
-        <v>-13.24983693093785</v>
+        <v>-0.0001324983693096465</v>
       </c>
       <c r="AG18" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AH18" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018986</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.146407496184111e-10</v>
+        <v>-1.153244166829381e-14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-5.453330231830478e-09</v>
+        <v>1.676783711879182e-13</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.561506562415161e-12</v>
+        <v>1.928795664851712e-16</v>
       </c>
       <c r="AL18" t="n">
-        <v>14707.31899337007</v>
+        <v>0.1470731899328119</v>
       </c>
       <c r="AM18" t="n">
-        <v>8.512870408594608e-10</v>
+        <v>-4.624078897563777e-14</v>
       </c>
       <c r="AN18" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018986</v>
       </c>
       <c r="AO18" t="n">
-        <v>-2.146407496184111e-10</v>
+        <v>1.153244166829381e-14</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.453330231830478e-09</v>
+        <v>-1.676783711879182e-13</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.561506562415161e-12</v>
+        <v>-1.928795664851712e-16</v>
       </c>
       <c r="AR18" t="n">
-        <v>-14707.31899332644</v>
+        <v>-0.1470731899341532</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.585629984736443e-10</v>
+        <v>-4.601874437071274e-14</v>
       </c>
     </row>
     <row r="19">
@@ -6354,124 +6354,124 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861589</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326986</v>
       </c>
       <c r="H19" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705982</v>
       </c>
       <c r="I19" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653971</v>
       </c>
       <c r="J19" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="K19" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="L19" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M19" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="N19" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="P19" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="Q19" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="R19" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="S19" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="V19" t="n">
-        <v>119.8844950930735</v>
+        <v>0.001198844950930051</v>
       </c>
       <c r="W19" t="n">
-        <v>-119.8844950930415</v>
+        <v>-0.001198844950931956</v>
       </c>
       <c r="X19" t="n">
-        <v>-179.9999999999999</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.24983693093785</v>
+        <v>0.0001324983693096465</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.2498369309433</v>
+        <v>0.0001324983693093059</v>
       </c>
       <c r="AA19" t="n">
-        <v>-6.261751098448146e-13</v>
+        <v>4.330075573690295e-17</v>
       </c>
       <c r="AB19" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="AC19" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="AD19" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="AE19" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="AF19" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="AG19" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AH19" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294018418</v>
       </c>
       <c r="AI19" t="n">
-        <v>-2.128217602148652e-10</v>
+        <v>1.16157083951407e-14</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8.74933903105557e-10</v>
+        <v>1.147831829584334e-13</v>
       </c>
       <c r="AK19" t="n">
-        <v>-1.644906433284632e-12</v>
+        <v>7.600257229123386e-17</v>
       </c>
       <c r="AL19" t="n">
-        <v>14707.31899334475</v>
+        <v>0.1470731899330236</v>
       </c>
       <c r="AM19" t="n">
-        <v>-8.512870408594608e-10</v>
+        <v>4.651834473179406e-14</v>
       </c>
       <c r="AN19" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294018418</v>
       </c>
       <c r="AO19" t="n">
-        <v>2.128217602148652e-10</v>
+        <v>-1.16157083951407e-14</v>
       </c>
       <c r="AP19" t="n">
-        <v>-8.74933903105557e-10</v>
+        <v>-1.147831829584334e-13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.644906433284632e-12</v>
+        <v>-7.600257229123386e-17</v>
       </c>
       <c r="AR19" t="n">
-        <v>-14707.31899335176</v>
+        <v>-0.1470731899339416</v>
       </c>
       <c r="AS19" t="n">
-        <v>-8.585629984736443e-10</v>
+        <v>4.64628335805628e-14</v>
       </c>
     </row>
     <row r="20">
@@ -6493,124 +6493,124 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G20" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H20" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I20" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J20" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="K20" t="n">
-        <v>-119.8844950930445</v>
+        <v>-0.001198844950931721</v>
       </c>
       <c r="L20" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="M20" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="N20" t="n">
-        <v>-13.24983693094545</v>
+        <v>-0.0001324983693095816</v>
       </c>
       <c r="O20" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="P20" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="Q20" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="R20" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S20" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="T20" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="V20" t="n">
-        <v>119.8844950930445</v>
+        <v>0.001198844950931721</v>
       </c>
       <c r="W20" t="n">
-        <v>-119.8844950930851</v>
+        <v>-0.001198844950931538</v>
       </c>
       <c r="X20" t="n">
-        <v>-179.9999999999997</v>
+        <v>-0.001799999999999995</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.24983693094545</v>
+        <v>0.0001324983693095816</v>
       </c>
       <c r="Z20" t="n">
-        <v>13.24983693093862</v>
+        <v>0.0001324983693096109</v>
       </c>
       <c r="AA20" t="n">
-        <v>-6.291202605871676e-13</v>
+        <v>4.325256558474486e-17</v>
       </c>
       <c r="AB20" t="n">
-        <v>-119.8844950931142</v>
+        <v>-0.001198844950929866</v>
       </c>
       <c r="AC20" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="AD20" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="AE20" t="n">
-        <v>13.24983693094665</v>
+        <v>0.0001324983693094913</v>
       </c>
       <c r="AF20" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="AG20" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="AH20" t="n">
-        <v>-27374.66294020042</v>
+        <v>-0.2737466294020123</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.110027708113194e-10</v>
+        <v>-1.160183060733289e-14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.825778887607157e-09</v>
+        <v>-1.380145997487148e-13</v>
       </c>
       <c r="AK20" t="n">
-        <v>-2.561506562415161e-12</v>
+        <v>1.92825356376547e-16</v>
       </c>
       <c r="AL20" t="n">
-        <v>14707.31899332895</v>
+        <v>0.1470731899340347</v>
       </c>
       <c r="AM20" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
       <c r="AN20" t="n">
-        <v>27374.66294020042</v>
+        <v>0.2737466294020123</v>
       </c>
       <c r="AO20" t="n">
-        <v>-2.110027708113194e-10</v>
+        <v>1.160183060733289e-14</v>
       </c>
       <c r="AP20" t="n">
-        <v>-4.825778887607157e-09</v>
+        <v>1.380145997487148e-13</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.561506562415161e-12</v>
+        <v>-1.92825356376547e-16</v>
       </c>
       <c r="AR20" t="n">
-        <v>-14707.31899336755</v>
+        <v>-0.1470731899329306</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.629630012686903e-14</v>
       </c>
     </row>
     <row r="21">
@@ -6632,124 +6632,124 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>-239.7689901861586</v>
+        <v>-0.002397689901861588</v>
       </c>
       <c r="G21" t="n">
-        <v>-29.97112377326983</v>
+        <v>-0.0002997112377326985</v>
       </c>
       <c r="H21" t="n">
-        <v>-28412625.3370598</v>
+        <v>-284.1262533705981</v>
       </c>
       <c r="I21" t="n">
-        <v>-5994224754.653966</v>
+        <v>-59942.24754653969</v>
       </c>
       <c r="J21" t="n">
-        <v>-119.8844950930922</v>
+        <v>-0.00119884495093108</v>
       </c>
       <c r="K21" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="L21" t="n">
-        <v>-180</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.24983693095013</v>
+        <v>-0.0001324983693092768</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="O21" t="n">
-        <v>-6.335095483592647e-13</v>
+        <v>4.335300855076827e-17</v>
       </c>
       <c r="P21" t="n">
-        <v>119.8844950930664</v>
+        <v>0.001198844950930508</v>
       </c>
       <c r="Q21" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="R21" t="n">
-        <v>-180.0000000000001</v>
+        <v>-0.001800000000000005</v>
       </c>
       <c r="S21" t="n">
-        <v>-13.2498369309509</v>
+        <v>-0.0001324983693092411</v>
       </c>
       <c r="T21" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.298268134835391e-13</v>
+        <v>4.314413255415275e-17</v>
       </c>
       <c r="V21" t="n">
-        <v>119.8844950930922</v>
+        <v>0.00119884495093108</v>
       </c>
       <c r="W21" t="n">
-        <v>119.8844950931142</v>
+        <v>0.001198844950929866</v>
       </c>
       <c r="X21" t="n">
-        <v>180</v>
+        <v>0.001800000000000005</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.24983693095013</v>
+        <v>0.0001324983693092768</v>
       </c>
       <c r="Z21" t="n">
-        <v>-13.24983693094665</v>
+        <v>-0.0001324983693094913</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.335095483592647e-13</v>
+        <v>-4.335300855076827e-17</v>
       </c>
       <c r="AB21" t="n">
-        <v>-119.8844950930664</v>
+        <v>-0.001198844950930508</v>
       </c>
       <c r="AC21" t="n">
-        <v>119.8844950931172</v>
+        <v>0.001198844950929632</v>
       </c>
       <c r="AD21" t="n">
-        <v>180.0000000000001</v>
+        <v>0.001800000000000005</v>
       </c>
       <c r="AE21" t="n">
-        <v>13.2498369309509</v>
+        <v>0.0001324983693092411</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.2498369309421</v>
+        <v>0.0001324983693093962</v>
       </c>
       <c r="AG21" t="n">
-        <v>6.298268134835391e-13</v>
+        <v>-4.314413255415275e-17</v>
       </c>
       <c r="AH21" t="n">
-        <v>-27374.66294019669</v>
+        <v>-0.2737466294019555</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.110027708113194e-10</v>
+        <v>-1.162958618294851e-14</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.886292011477053e-09</v>
+        <v>3.953781746446339e-14</v>
       </c>
       <c r="AK21" t="n">
-        <v>-1.63424829224823e-12</v>
+        <v>7.605678239985814e-17</v>
       </c>
       <c r="AL21" t="n">
-        <v>-14707.3189933558</v>
+        <v>-0.1470731899336408</v>
       </c>
       <c r="AM21" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.668487818548783e-14</v>
       </c>
       <c r="AN21" t="n">
-        <v>27374.66294019669</v>
+        <v>0.2737466294019555</v>
       </c>
       <c r="AO21" t="n">
-        <v>-2.110027708113194e-10</v>
+        <v>1.162958618294851e-14</v>
       </c>
       <c r="AP21" t="n">
-        <v>-1.886292011477053e-09</v>
+        <v>-3.953781746446339e-14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.63424829224823e-12</v>
+        <v>-7.605678239985814e-17</v>
       </c>
       <c r="AR21" t="n">
-        <v>14707.31899334072</v>
+        <v>0.1470731899333244</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.440110832452774e-10</v>
+        <v>-4.640732242933154e-14</v>
       </c>
     </row>
     <row r="22">
@@ -6771,124 +6771,124 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G22" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H22" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I22" t="n">
-        <v>-6001954935.086894</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J22" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="K22" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="L22" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>2.917176071110052</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="P22" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="R22" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="V22" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="W22" t="n">
-        <v>-120.0390987017059</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="X22" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="Z22" t="n">
-        <v>-2.917176071110052</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AA22" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="AB22" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="AC22" t="n">
-        <v>-120.0390987017214</v>
+        <v>-0.001200390987015382</v>
       </c>
       <c r="AD22" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="AE22" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.917176071123615</v>
+        <v>2.917176071092573e-05</v>
       </c>
       <c r="AG22" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AH22" t="n">
-        <v>9266.392311878502</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.640643838793039e-11</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="AJ22" t="n">
-        <v>-5.697074811905622e-09</v>
+        <v>1.999719834167024e-13</v>
       </c>
       <c r="AK22" t="n">
-        <v>-5.53335155473178e-13</v>
+        <v>1.989104410696219e-16</v>
       </c>
       <c r="AL22" t="n">
-        <v>-3238.065438916907</v>
+        <v>-0.03238065439019683</v>
       </c>
       <c r="AM22" t="n">
-        <v>4.001776687800884e-10</v>
+        <v>-1.563749130184533e-13</v>
       </c>
       <c r="AN22" t="n">
-        <v>-9266.392311878502</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="AO22" t="n">
-        <v>-9.640643838793039e-11</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="AP22" t="n">
-        <v>5.697074811905622e-09</v>
+        <v>-1.999719834167024e-13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.53335155473178e-13</v>
+        <v>-1.989104410696219e-16</v>
       </c>
       <c r="AR22" t="n">
-        <v>3238.065438962483</v>
+        <v>0.03238065438859682</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.783497959375381e-10</v>
+        <v>-1.562638907159908e-13</v>
       </c>
     </row>
     <row r="23">
@@ -6910,124 +6910,124 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G23" t="n">
-        <v>-30.00977467543448</v>
+        <v>-0.0003000977467543447</v>
       </c>
       <c r="H23" t="n">
-        <v>-28449266.39231189</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I23" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086893</v>
       </c>
       <c r="J23" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="K23" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="L23" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="P23" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="Q23" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="R23" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="V23" t="n">
-        <v>120.0390987017214</v>
+        <v>0.001200390987015382</v>
       </c>
       <c r="W23" t="n">
-        <v>-120.0390987016426</v>
+        <v>-0.001200390987020392</v>
       </c>
       <c r="X23" t="n">
-        <v>-359.9999999999998</v>
+        <v>-0.003599999999999991</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.917176071123615</v>
+        <v>-2.917176071092573e-05</v>
       </c>
       <c r="Z23" t="n">
-        <v>-2.917176071118412</v>
+        <v>-2.917176071130497e-05</v>
       </c>
       <c r="AA23" t="n">
-        <v>-1.838581571782945e-12</v>
+        <v>1.176370009479116e-16</v>
       </c>
       <c r="AB23" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="AC23" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="AD23" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="AE23" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="AG23" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AH23" t="n">
-        <v>9266.392311885953</v>
+        <v>0.09266392311866412</v>
       </c>
       <c r="AI23" t="n">
-        <v>-1.01863406598568e-10</v>
+        <v>3.909372825461332e-14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.280568540096283e-09</v>
+        <v>1.138637795161657e-13</v>
       </c>
       <c r="AK23" t="n">
-        <v>-4.352962434950314e-12</v>
+        <v>1.280984866791623e-16</v>
       </c>
       <c r="AL23" t="n">
-        <v>-3238.065438944817</v>
+        <v>-0.03238065438985234</v>
       </c>
       <c r="AM23" t="n">
-        <v>-4.220055416226387e-10</v>
+        <v>1.564859353209158e-13</v>
       </c>
       <c r="AN23" t="n">
-        <v>-9266.392311885953</v>
+        <v>-0.09266392311866412</v>
       </c>
       <c r="AO23" t="n">
-        <v>1.01863406598568e-10</v>
+        <v>-3.909372825461332e-14</v>
       </c>
       <c r="AP23" t="n">
-        <v>-1.280568540096283e-09</v>
+        <v>-1.138637795161657e-13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.352962434950314e-12</v>
+        <v>-1.280984866791623e-16</v>
       </c>
       <c r="AR23" t="n">
-        <v>3238.065438934573</v>
+        <v>0.03238065438894119</v>
       </c>
       <c r="AS23" t="n">
-        <v>-3.856257535517216e-10</v>
+        <v>1.56319401867222e-13</v>
       </c>
     </row>
     <row r="24">
@@ -7049,124 +7049,124 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034759</v>
       </c>
       <c r="G24" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543449</v>
       </c>
       <c r="H24" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231189</v>
       </c>
       <c r="I24" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086897</v>
       </c>
       <c r="J24" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.0390987016563</v>
+        <v>-0.001200390987019827</v>
       </c>
       <c r="L24" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="N24" t="n">
-        <v>2.917176071115255</v>
+        <v>2.917176071103165e-05</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="P24" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="Q24" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="R24" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="V24" t="n">
-        <v>120.0390987016563</v>
+        <v>0.001200390987019827</v>
       </c>
       <c r="W24" t="n">
-        <v>-120.0390987017544</v>
+        <v>-0.001200390987019375</v>
       </c>
       <c r="X24" t="n">
-        <v>-359.9999999999994</v>
+        <v>-0.003599999999999993</v>
       </c>
       <c r="Y24" t="n">
-        <v>-2.917176071115255</v>
+        <v>-2.917176071103165e-05</v>
       </c>
       <c r="Z24" t="n">
-        <v>-2.917176071121575</v>
+        <v>-2.917176071098574e-05</v>
       </c>
       <c r="AA24" t="n">
-        <v>-1.804880584799103e-12</v>
+        <v>1.175166403845245e-16</v>
       </c>
       <c r="AB24" t="n">
-        <v>-120.0390987018195</v>
+        <v>-0.001200390987014932</v>
       </c>
       <c r="AC24" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="AD24" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>-2.917176071114994</v>
+        <v>-2.917176071112471e-05</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="AG24" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="AH24" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311883465</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.036823960021138e-10</v>
+        <v>-3.903821710338207e-14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.009052645415068e-09</v>
+        <v>-1.501750113153122e-13</v>
       </c>
       <c r="AK24" t="n">
-        <v>-5.568878691519785e-13</v>
+        <v>1.986393905265005e-16</v>
       </c>
       <c r="AL24" t="n">
-        <v>-3238.065438955702</v>
+        <v>-0.032380654388796</v>
       </c>
       <c r="AM24" t="n">
-        <v>4.292814992368221e-10</v>
+        <v>-1.562083795647595e-13</v>
       </c>
       <c r="AN24" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311883465</v>
       </c>
       <c r="AO24" t="n">
-        <v>-1.036823960021138e-10</v>
+        <v>3.903821710338207e-14</v>
       </c>
       <c r="AP24" t="n">
-        <v>-4.009052645415068e-09</v>
+        <v>1.501750113153122e-13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.568878691519785e-13</v>
+        <v>-1.986393905265005e-16</v>
       </c>
       <c r="AR24" t="n">
-        <v>3238.065438923659</v>
+        <v>0.03238065438999761</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.074536263942719e-10</v>
+        <v>-1.560418461110658e-13</v>
       </c>
     </row>
     <row r="25">
@@ -7188,124 +7188,124 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>-240.0781974034758</v>
+        <v>-0.002400781974034758</v>
       </c>
       <c r="G25" t="n">
-        <v>-30.00977467543447</v>
+        <v>-0.0003000977467543448</v>
       </c>
       <c r="H25" t="n">
-        <v>-28449266.39231188</v>
+        <v>-284.4926639231188</v>
       </c>
       <c r="I25" t="n">
-        <v>-6001954935.086895</v>
+        <v>-60019.54935086895</v>
       </c>
       <c r="J25" t="n">
-        <v>-120.0390987017699</v>
+        <v>-0.00120039098701806</v>
       </c>
       <c r="K25" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="L25" t="n">
-        <v>-360</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>2.917176071112084</v>
+        <v>2.917176071135098e-05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.825339387183125e-12</v>
+        <v>1.176627274838199e-16</v>
       </c>
       <c r="P25" t="n">
-        <v>120.0390987017059</v>
+        <v>0.001200390987016698</v>
       </c>
       <c r="Q25" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="R25" t="n">
-        <v>-360.0000000000002</v>
+        <v>-0.00360000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>2.917176071110052</v>
+        <v>2.917176071141088e-05</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.822148453449026e-12</v>
+        <v>1.176001070613948e-16</v>
       </c>
       <c r="V25" t="n">
-        <v>120.0390987017699</v>
+        <v>0.00120039098701806</v>
       </c>
       <c r="W25" t="n">
-        <v>120.0390987018195</v>
+        <v>0.001200390987014932</v>
       </c>
       <c r="X25" t="n">
-        <v>360</v>
+        <v>0.00360000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>-2.917176071112084</v>
+        <v>-2.917176071135098e-05</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.917176071114994</v>
+        <v>2.917176071112471e-05</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.825339387183125e-12</v>
+        <v>-1.176627274838199e-16</v>
       </c>
       <c r="AB25" t="n">
-        <v>-120.0390987017059</v>
+        <v>-0.001200390987016698</v>
       </c>
       <c r="AC25" t="n">
-        <v>120.0390987018331</v>
+        <v>0.001200390987014366</v>
       </c>
       <c r="AD25" t="n">
-        <v>360.0000000000002</v>
+        <v>0.00360000000000001</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.917176071110052</v>
+        <v>-2.917176071141088e-05</v>
       </c>
       <c r="AF25" t="n">
-        <v>-2.917176071118671</v>
+        <v>-2.917176071121179e-05</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.822148453449026e-12</v>
+        <v>-1.176001070613948e-16</v>
       </c>
       <c r="AH25" t="n">
-        <v>9266.392311882228</v>
+        <v>0.09266392311872096</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.073203748092055e-10</v>
+        <v>-3.907985046680551e-14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.506123226135969e-09</v>
+        <v>3.622623034882366e-14</v>
       </c>
       <c r="AK25" t="n">
-        <v>-4.338751580235112e-12</v>
+        <v>1.278680937175092e-16</v>
       </c>
       <c r="AL25" t="n">
-        <v>3238.065438933641</v>
+        <v>0.03238065438925182</v>
       </c>
       <c r="AM25" t="n">
-        <v>4.292814992368221e-10</v>
+        <v>-1.564304241696846e-13</v>
       </c>
       <c r="AN25" t="n">
-        <v>-9266.392311882228</v>
+        <v>-0.09266392311872096</v>
       </c>
       <c r="AO25" t="n">
-        <v>-1.073203748092055e-10</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="AP25" t="n">
-        <v>-1.506123226135969e-09</v>
+        <v>-3.622623034882366e-14</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.338751580235112e-12</v>
+        <v>-1.278680937175092e-16</v>
       </c>
       <c r="AR25" t="n">
-        <v>-3238.06543894572</v>
+        <v>-0.03238065438954182</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.220055416226387e-10</v>
+        <v>-1.56319401867222e-13</v>
       </c>
     </row>
     <row r="26">
@@ -7327,124 +7327,124 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321729</v>
       </c>
       <c r="G26" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.0002999792379152161</v>
       </c>
       <c r="H26" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436249</v>
       </c>
       <c r="I26" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304321</v>
       </c>
       <c r="J26" t="n">
-        <v>119.9916951660409</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="K26" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="L26" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6603494433671542</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="P26" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="Q26" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="R26" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="V26" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="W26" t="n">
-        <v>-119.9916951660409</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="X26" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6603494433671542</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AA26" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="AB26" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="AC26" t="n">
-        <v>-119.9916951660554</v>
+        <v>-0.001199916951658015</v>
       </c>
       <c r="AD26" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.6603494433610113</v>
+        <v>-6.603494433862078e-06</v>
       </c>
       <c r="AG26" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AH26" t="n">
-        <v>-1968.245637536049</v>
+        <v>-0.01968245637522159</v>
       </c>
       <c r="AI26" t="n">
-        <v>-1.153239281848073e-09</v>
+        <v>-3.372302437298913e-14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>-2.65572452917695e-09</v>
+        <v>1.817729994302297e-13</v>
       </c>
       <c r="AK26" t="n">
-        <v>-1.999733711954832e-12</v>
+        <v>4.984280674823205e-17</v>
       </c>
       <c r="AL26" t="n">
-        <v>732.9878821447492</v>
+        <v>0.007329878820614492</v>
       </c>
       <c r="AM26" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.35003119794419e-13</v>
       </c>
       <c r="AN26" t="n">
-        <v>1968.245637536049</v>
+        <v>0.01968245637522159</v>
       </c>
       <c r="AO26" t="n">
-        <v>1.153239281848073e-09</v>
+        <v>3.372302437298913e-14</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.65572452917695e-09</v>
+        <v>-1.817729994302297e-13</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.999733711954832e-12</v>
+        <v>-4.984280674823205e-17</v>
       </c>
       <c r="AR26" t="n">
-        <v>-732.9878821235034</v>
+        <v>-0.007329878822068229</v>
       </c>
       <c r="AS26" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.348365863407253e-13</v>
       </c>
     </row>
     <row r="27">
@@ -7466,124 +7466,124 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>-239.9833903321726</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G27" t="n">
-        <v>-29.99792379152158</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H27" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I27" t="n">
-        <v>-5999584758.304316</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J27" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="K27" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="L27" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="M27" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="P27" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="Q27" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="R27" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="V27" t="n">
-        <v>119.9916951660554</v>
+        <v>0.001199916951658015</v>
       </c>
       <c r="W27" t="n">
-        <v>-119.9916951659443</v>
+        <v>-0.001199916951665896</v>
       </c>
       <c r="X27" t="n">
-        <v>-539.9999999999995</v>
+        <v>-0.005399999999999988</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.6603494433610113</v>
+        <v>6.603494433862078e-06</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.6603494433624342</v>
+        <v>6.603494433580178e-06</v>
       </c>
       <c r="AA27" t="n">
-        <v>-3.202814053526971e-12</v>
+        <v>1.907344758392897e-16</v>
       </c>
       <c r="AB27" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="AC27" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="AD27" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="AG27" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AH27" t="n">
-        <v>-1968.245637543499</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.142325345426798e-09</v>
+        <v>3.37924133120282e-14</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.346052158623934e-09</v>
+        <v>5.07484679279635e-14</v>
       </c>
       <c r="AK27" t="n">
-        <v>-7.044365091246618e-12</v>
+        <v>1.548037414401959e-16</v>
       </c>
       <c r="AL27" t="n">
-        <v>732.9878821287421</v>
+        <v>0.00732987882113827</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.583853296935558e-09</v>
+        <v>1.352806755505753e-13</v>
       </c>
       <c r="AN27" t="n">
-        <v>1968.245637543499</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO27" t="n">
-        <v>-1.142325345426798e-09</v>
+        <v>-3.37924133120282e-14</v>
       </c>
       <c r="AP27" t="n">
-        <v>-1.346052158623934e-09</v>
+        <v>-5.07484679279635e-14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.044365091246618e-12</v>
+        <v>-1.548037414401959e-16</v>
       </c>
       <c r="AR27" t="n">
-        <v>-732.9878821395105</v>
+        <v>-0.007329878821544254</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.562025424093008e-09</v>
+        <v>1.35003119794419e-13</v>
       </c>
     </row>
     <row r="28">
@@ -7605,124 +7605,124 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G28" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H28" t="n">
-        <v>-28438031.75436246</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I28" t="n">
-        <v>-5999584758.304317</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J28" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="K28" t="n">
-        <v>-119.991695165981</v>
+        <v>-0.001199916951664696</v>
       </c>
       <c r="L28" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.660349443365725</v>
+        <v>-6.603494433701469e-06</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="P28" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="Q28" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="R28" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="U28" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="V28" t="n">
-        <v>119.991695165981</v>
+        <v>0.001199916951664696</v>
       </c>
       <c r="W28" t="n">
-        <v>-119.9916951661173</v>
+        <v>-0.001199916951663713</v>
       </c>
       <c r="X28" t="n">
-        <v>-539.9999999999993</v>
+        <v>-0.005399999999999991</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.660349443365725</v>
+        <v>6.603494433701469e-06</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.6603494433643113</v>
+        <v>6.603494433789558e-06</v>
       </c>
       <c r="AA28" t="n">
-        <v>-3.218484248254603e-12</v>
+        <v>1.904605835800995e-16</v>
       </c>
       <c r="AB28" t="n">
-        <v>-119.9916951661917</v>
+        <v>-0.001199916951657032</v>
       </c>
       <c r="AC28" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="AD28" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.6603494433666658</v>
+        <v>6.603494433678052e-06</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="AG28" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="AH28" t="n">
-        <v>-1968.245637536049</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI28" t="n">
-        <v>-1.144144334830344e-09</v>
+        <v>-3.380629109983602e-14</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-1.091393642127514e-10</v>
+        <v>-1.213413050593637e-13</v>
       </c>
       <c r="AK28" t="n">
-        <v>-2.008393451546908e-12</v>
+        <v>4.998680234926528e-17</v>
       </c>
       <c r="AL28" t="n">
-        <v>732.9878821345628</v>
+        <v>0.00732987882182677</v>
       </c>
       <c r="AM28" t="n">
-        <v>-4.591129254549742e-09</v>
+        <v>-1.353361867018066e-13</v>
       </c>
       <c r="AN28" t="n">
-        <v>1968.245637536049</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO28" t="n">
-        <v>1.144144334830344e-09</v>
+        <v>3.380629109983602e-14</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.091393642127514e-10</v>
+        <v>1.213413050593637e-13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2.008393451546908e-12</v>
+        <v>-4.998680234926528e-17</v>
       </c>
       <c r="AR28" t="n">
-        <v>-732.9878821336897</v>
+        <v>-0.007329878820855593</v>
       </c>
       <c r="AS28" t="n">
-        <v>-4.562025424093008e-09</v>
+        <v>-1.351141420968816e-13</v>
       </c>
     </row>
     <row r="29">
@@ -7744,124 +7744,124 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>-239.9833903321727</v>
+        <v>-0.002399833903321728</v>
       </c>
       <c r="G29" t="n">
-        <v>-29.99792379152159</v>
+        <v>-0.000299979237915216</v>
       </c>
       <c r="H29" t="n">
-        <v>-28438031.75436247</v>
+        <v>-284.3803175436248</v>
       </c>
       <c r="I29" t="n">
-        <v>-5999584758.304318</v>
+        <v>-59995.84758304319</v>
       </c>
       <c r="J29" t="n">
-        <v>-119.9916951661319</v>
+        <v>-0.001199916951661864</v>
       </c>
       <c r="K29" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="L29" t="n">
-        <v>-540.0000000000001</v>
+        <v>-0.005400000000000014</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6603494433638429</v>
+        <v>-6.603494433492081e-06</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="O29" t="n">
-        <v>-3.191754473673499e-12</v>
+        <v>1.906780182197915e-16</v>
       </c>
       <c r="P29" t="n">
-        <v>119.9916951660409</v>
+        <v>0.001199916951659864</v>
       </c>
       <c r="Q29" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="R29" t="n">
-        <v>-540.0000000000005</v>
+        <v>-0.005400000000000012</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.6603494433671542</v>
+        <v>-6.603494433419627e-06</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="U29" t="n">
-        <v>-3.202095367613299e-12</v>
+        <v>1.905941100274659e-16</v>
       </c>
       <c r="V29" t="n">
-        <v>119.9916951661319</v>
+        <v>0.001199916951661864</v>
       </c>
       <c r="W29" t="n">
-        <v>119.9916951661917</v>
+        <v>0.001199916951657032</v>
       </c>
       <c r="X29" t="n">
-        <v>540.0000000000001</v>
+        <v>0.005400000000000014</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6603494433638429</v>
+        <v>6.603494433492081e-06</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.6603494433666658</v>
+        <v>-6.603494433678052e-06</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.191754473673499e-12</v>
+        <v>-1.906780182197915e-16</v>
       </c>
       <c r="AB29" t="n">
-        <v>-119.9916951660409</v>
+        <v>-0.001199916951659864</v>
       </c>
       <c r="AC29" t="n">
-        <v>119.9916951662284</v>
+        <v>0.001199916951655833</v>
       </c>
       <c r="AD29" t="n">
-        <v>540.0000000000005</v>
+        <v>0.005400000000000012</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.6603494433671542</v>
+        <v>6.603494433419627e-06</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.6603494433614974</v>
+        <v>6.603494433603528e-06</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.202095367613299e-12</v>
+        <v>-1.905941100274659e-16</v>
       </c>
       <c r="AH29" t="n">
-        <v>-1968.245637528598</v>
+        <v>-0.01968245637533528</v>
       </c>
       <c r="AI29" t="n">
-        <v>-1.153239281848073e-09</v>
+        <v>-3.393119119010635e-14</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.117303665727377e-09</v>
+        <v>3.120854269456075e-14</v>
       </c>
       <c r="AK29" t="n">
-        <v>-7.068345908578522e-12</v>
+        <v>1.546631339709517e-16</v>
       </c>
       <c r="AL29" t="n">
-        <v>-732.9878821425955</v>
+        <v>-0.007329878821466364</v>
       </c>
       <c r="AM29" t="n">
-        <v>-4.612957127392292e-09</v>
+        <v>-1.357802759116566e-13</v>
       </c>
       <c r="AN29" t="n">
-        <v>1968.245637528598</v>
+        <v>0.01968245637533528</v>
       </c>
       <c r="AO29" t="n">
-        <v>1.153239281848073e-09</v>
+        <v>3.393119119010635e-14</v>
       </c>
       <c r="AP29" t="n">
-        <v>-2.117303665727377e-09</v>
+        <v>-3.120854269456075e-14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.068345908578522e-12</v>
+        <v>-1.546631339709517e-16</v>
       </c>
       <c r="AR29" t="n">
-        <v>732.9878821256571</v>
+        <v>0.007329878821216248</v>
       </c>
       <c r="AS29" t="n">
-        <v>-4.605681169778109e-09</v>
+        <v>-1.356692536091941e-13</v>
       </c>
     </row>
     <row r="30">
@@ -7883,124 +7883,124 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785245</v>
       </c>
       <c r="G30" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481556</v>
       </c>
       <c r="H30" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680515</v>
       </c>
       <c r="I30" t="n">
-        <v>-6000065376.963104</v>
+        <v>-60000.65376963112</v>
       </c>
       <c r="J30" t="n">
-        <v>120.0013075391888</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="K30" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="L30" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2383793661006169</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="P30" t="n">
-        <v>120.0013075392201</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="Q30" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="R30" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.2383793661002568</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="T30" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="U30" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="V30" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="W30" t="n">
-        <v>-120.0013075391888</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="X30" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.2383793661006169</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AA30" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="AB30" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="AC30" t="n">
-        <v>-120.0013075392201</v>
+        <v>-0.001200013075389576</v>
       </c>
       <c r="AD30" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.2383793661002568</v>
+        <v>2.383793660882689e-06</v>
       </c>
       <c r="AG30" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AH30" t="n">
-        <v>309.8868051171303</v>
+        <v>0.00309886805143833</v>
       </c>
       <c r="AI30" t="n">
-        <v>-1.702574081718922e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>9.846290449644357e-14</v>
       </c>
       <c r="AK30" t="n">
-        <v>-3.771205570046732e-12</v>
+        <v>-3.246761990120459e-17</v>
       </c>
       <c r="AL30" t="n">
-        <v>-264.6010963714798</v>
+        <v>-0.002646010964108621</v>
       </c>
       <c r="AM30" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
       <c r="AN30" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.00309886805143833</v>
       </c>
       <c r="AO30" t="n">
-        <v>1.702574081718922e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="AP30" t="n">
-        <v>-1.455191522836685e-11</v>
+        <v>-9.846290449644357e-14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.771205570046732e-12</v>
+        <v>3.246761990120459e-17</v>
       </c>
       <c r="AR30" t="n">
-        <v>264.6010963714798</v>
+        <v>0.002646010963320918</v>
       </c>
       <c r="AS30" t="n">
-        <v>-6.803020369261503e-09</v>
+        <v>-2.015054789694659e-14</v>
       </c>
     </row>
     <row r="31">
@@ -8022,124 +8022,124 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785244</v>
       </c>
       <c r="G31" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481555</v>
       </c>
       <c r="H31" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680514</v>
       </c>
       <c r="I31" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963108</v>
       </c>
       <c r="J31" t="n">
-        <v>120.0013075392201</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="K31" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="L31" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2383793661002568</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="P31" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="Q31" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="R31" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="U31" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="V31" t="n">
-        <v>120.0013075392201</v>
+        <v>0.001200013075389576</v>
       </c>
       <c r="W31" t="n">
-        <v>-120.0013075391147</v>
+        <v>-0.001200013075399115</v>
       </c>
       <c r="X31" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.007199999999999989</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.2383793661002568</v>
+        <v>-2.383793660882689e-06</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.2383793661013742</v>
+        <v>-2.383793661013147e-06</v>
       </c>
       <c r="AA31" t="n">
-        <v>-5.950374488726812e-12</v>
+        <v>2.144340812935092e-16</v>
       </c>
       <c r="AB31" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="AC31" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="AD31" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="AG31" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AH31" t="n">
-        <v>309.8868051208556</v>
+        <v>0.003098868051324644</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.709850039333105e-09</v>
+        <v>5.023759186428833e-15</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7.712515071034431e-10</v>
+        <v>7.490102288398859e-15</v>
       </c>
       <c r="AK31" t="n">
-        <v>-5.13833420257015e-12</v>
+        <v>8.102124250371559e-17</v>
       </c>
       <c r="AL31" t="n">
-        <v>-264.6010963745648</v>
+        <v>-0.002646010963744791</v>
       </c>
       <c r="AM31" t="n">
-        <v>6.83940015733242e-09</v>
+        <v>2.009503674571533e-14</v>
       </c>
       <c r="AN31" t="n">
-        <v>-309.8868051208556</v>
+        <v>-0.003098868051324644</v>
       </c>
       <c r="AO31" t="n">
-        <v>-1.709850039333105e-09</v>
+        <v>-5.023759186428833e-15</v>
       </c>
       <c r="AP31" t="n">
-        <v>-7.712515071034431e-10</v>
+        <v>-7.490102288398859e-15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>5.13833420257015e-12</v>
+        <v>-8.102124250371559e-17</v>
       </c>
       <c r="AR31" t="n">
-        <v>264.6010963683948</v>
+        <v>0.00264601096368487</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.83940015733242e-09</v>
+        <v>2.003952559448408e-14</v>
       </c>
     </row>
     <row r="32">
@@ -8161,124 +8161,124 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G32" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481553</v>
       </c>
       <c r="H32" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680512</v>
       </c>
       <c r="I32" t="n">
-        <v>-6000065376.963105</v>
+        <v>-60000.65376963106</v>
       </c>
       <c r="J32" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="K32" t="n">
-        <v>-120.0013075391787</v>
+        <v>-0.001200013075397448</v>
       </c>
       <c r="L32" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2383793660995157</v>
+        <v>2.383793660995621e-06</v>
       </c>
       <c r="O32" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="P32" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="Q32" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="R32" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S32" t="n">
-        <v>0.2383793661030328</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="T32" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="U32" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="V32" t="n">
-        <v>120.0013075391787</v>
+        <v>0.001200013075397448</v>
       </c>
       <c r="W32" t="n">
-        <v>-120.0013075393042</v>
+        <v>-0.001200013075395668</v>
       </c>
       <c r="X32" t="n">
-        <v>-719.9999999999993</v>
+        <v>-0.00719999999999999</v>
       </c>
       <c r="Y32" t="n">
-        <v>-0.2383793660995157</v>
+        <v>-2.383793660995621e-06</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.2383793660978497</v>
+        <v>-2.383793660920645e-06</v>
       </c>
       <c r="AA32" t="n">
-        <v>-5.953210351365886e-12</v>
+        <v>2.143642377260611e-16</v>
       </c>
       <c r="AB32" t="n">
-        <v>-120.0013075393455</v>
+        <v>-0.001200013075387795</v>
       </c>
       <c r="AC32" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="AD32" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.238379366097723</v>
+        <v>-2.383793660980112e-06</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.2383793661030328</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="AG32" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="AH32" t="n">
-        <v>309.8868051245809</v>
+        <v>0.003098868051154113</v>
       </c>
       <c r="AI32" t="n">
-        <v>-1.704393071122468e-09</v>
+        <v>-5.079270337660091e-15</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-2.066371962428093e-09</v>
+        <v>-6.722400414105323e-14</v>
       </c>
       <c r="AK32" t="n">
-        <v>-3.82671672127799e-12</v>
+        <v>-3.310458867753982e-17</v>
       </c>
       <c r="AL32" t="n">
-        <v>-264.6010963632143</v>
+        <v>-0.002646010963446374</v>
       </c>
       <c r="AM32" t="n">
-        <v>-6.81757228448987e-09</v>
+        <v>-2.031708135064036e-14</v>
       </c>
       <c r="AN32" t="n">
-        <v>-309.8868051245809</v>
+        <v>-0.003098868051154113</v>
       </c>
       <c r="AO32" t="n">
-        <v>1.704393071122468e-09</v>
+        <v>5.079270337660091e-15</v>
       </c>
       <c r="AP32" t="n">
-        <v>2.066371962428093e-09</v>
+        <v>6.722400414105323e-14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.82671672127799e-12</v>
+        <v>3.310458867753982e-17</v>
       </c>
       <c r="AR32" t="n">
-        <v>264.6010963797453</v>
+        <v>0.00264601096398372</v>
       </c>
       <c r="AS32" t="n">
-        <v>-6.824848242104053e-09</v>
+        <v>-2.037259250187162e-14</v>
       </c>
     </row>
     <row r="33">
@@ -8300,124 +8300,124 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>-240.0026150785242</v>
+        <v>-0.002400026150785243</v>
       </c>
       <c r="G33" t="n">
-        <v>-30.00032688481553</v>
+        <v>-0.0003000032688481554</v>
       </c>
       <c r="H33" t="n">
-        <v>-28440309.88680512</v>
+        <v>-284.4030988680513</v>
       </c>
       <c r="I33" t="n">
-        <v>-6000065376.963104</v>
+        <v>-60000.65376963107</v>
       </c>
       <c r="J33" t="n">
-        <v>-120.0013075393354</v>
+        <v>-0.001200013075393904</v>
       </c>
       <c r="K33" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="L33" t="n">
-        <v>-720.0000000000002</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2383793661030328</v>
+        <v>2.38379366108843e-06</v>
       </c>
       <c r="N33" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="O33" t="n">
-        <v>-5.95367299120638e-12</v>
+        <v>2.143153122890248e-16</v>
       </c>
       <c r="P33" t="n">
-        <v>120.0013075391888</v>
+        <v>0.001200013075391339</v>
       </c>
       <c r="Q33" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="R33" t="n">
-        <v>-720.0000000000007</v>
+        <v>-0.007200000000000015</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2383793661006169</v>
+        <v>2.383793661125953e-06</v>
       </c>
       <c r="T33" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="U33" t="n">
-        <v>-5.954773371978419e-12</v>
+        <v>2.14221674225249e-16</v>
       </c>
       <c r="V33" t="n">
-        <v>120.0013075393354</v>
+        <v>0.001200013075393904</v>
       </c>
       <c r="W33" t="n">
-        <v>120.0013075393455</v>
+        <v>0.001200013075387795</v>
       </c>
       <c r="X33" t="n">
-        <v>720.0000000000002</v>
+        <v>0.007200000000000015</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.2383793661030328</v>
+        <v>-2.38379366108843e-06</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.238379366097723</v>
+        <v>2.383793660980112e-06</v>
       </c>
       <c r="AA33" t="n">
-        <v>5.95367299120638e-12</v>
+        <v>-2.143153122890248e-16</v>
       </c>
       <c r="AB33" t="n">
-        <v>-120.0013075391888</v>
+        <v>-0.001200013075391339</v>
       </c>
       <c r="AC33" t="n">
-        <v>120.0013075394095</v>
+        <v>0.00120001307538613</v>
       </c>
       <c r="AD33" t="n">
-        <v>720.0000000000007</v>
+        <v>0.007200000000000015</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.2383793661006169</v>
+        <v>-2.383793661125953e-06</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.2383793661031409</v>
+        <v>-2.383793661028357e-06</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.954773371978419e-12</v>
+        <v>-2.14221674225249e-16</v>
       </c>
       <c r="AH33" t="n">
-        <v>309.8868051171303</v>
+        <v>0.0030988680512678</v>
       </c>
       <c r="AI33" t="n">
-        <v>-1.702574081718922e-09</v>
+        <v>-5.120903701083535e-15</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.197339199483395e-09</v>
+        <v>2.023619986857295e-14</v>
       </c>
       <c r="AK33" t="n">
-        <v>-5.157096971686315e-12</v>
+        <v>8.009628252531389e-17</v>
       </c>
       <c r="AL33" t="n">
-        <v>264.6010963626322</v>
+        <v>0.002646010963633847</v>
       </c>
       <c r="AM33" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.059463710679665e-14</v>
       </c>
       <c r="AN33" t="n">
-        <v>-309.8868051171303</v>
+        <v>-0.0030988680512678</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.702574081718922e-09</v>
+        <v>5.120903701083535e-15</v>
       </c>
       <c r="AP33" t="n">
-        <v>-2.197339199483395e-09</v>
+        <v>-2.023619986857295e-14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.157096971686315e-12</v>
+        <v>-8.009628252531389e-17</v>
       </c>
       <c r="AR33" t="n">
-        <v>-264.6010963802692</v>
+        <v>-0.002646010963795291</v>
       </c>
       <c r="AS33" t="n">
-        <v>-6.810296326875687e-09</v>
+        <v>-2.042810365310288e-14</v>
       </c>
     </row>
   </sheetData>
